--- a/files/九龙-何文田-VAU Residence.xlsx
+++ b/files/九龙-何文田-VAU Residence.xlsx
@@ -8,7 +8,6 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="销控汇总明细" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VAU Residence 销控表" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20,7 +19,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="14">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -42,65 +41,8 @@
       <name val="Microsoft YaHei"/>
       <sz val="10"/>
     </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <color rgb="007F7F7F"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="007F7F7F"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00004D00"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00004D00"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <color rgb="00002060"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00002060"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <color rgb="00660000"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00660000"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00000000"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00000000"/>
-      <sz val="11"/>
-    </font>
   </fonts>
-  <fills count="9">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
@@ -111,42 +53,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="00F2F2F2"/>
         <bgColor rgb="00F2F2F2"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFFFFF"/>
-        <bgColor rgb="00FFFFFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00A9F5A9"/>
-        <bgColor rgb="00A9F5A9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00A9D0F5"/>
-        <bgColor rgb="00A9D0F5"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F5A9A9"/>
-        <bgColor rgb="00F5A9A9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFC000"/>
-        <bgColor rgb="00FFC000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00E5E5E5"/>
-        <bgColor rgb="00E5E5E5"/>
       </patternFill>
     </fill>
   </fills>
@@ -176,7 +82,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -192,51 +98,6 @@
     </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -708,7 +569,7 @@
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-07-14</t>
         </is>
       </c>
       <c r="H3" s="5" t="n">
@@ -754,7 +615,7 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-07-13</t>
         </is>
       </c>
       <c r="H4" s="5" t="n">
@@ -1046,7 +907,7 @@
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-07-10</t>
         </is>
       </c>
       <c r="H10" s="5" t="n">
@@ -1092,7 +953,7 @@
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-07-08</t>
         </is>
       </c>
       <c r="H11" s="5" t="n">
@@ -1138,7 +999,7 @@
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="H12" s="5" t="n">
@@ -1184,7 +1045,7 @@
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="H13" s="5" t="n">
@@ -1230,7 +1091,7 @@
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="H14" s="5" t="n">
@@ -1276,7 +1137,7 @@
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="H15" s="5" t="n">
@@ -1322,7 +1183,7 @@
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="H16" s="5" t="n">
@@ -1414,7 +1275,7 @@
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="H18" s="5" t="n">
@@ -1460,7 +1321,7 @@
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-08-24</t>
         </is>
       </c>
       <c r="H19" s="5" t="n">
@@ -1506,7 +1367,7 @@
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="H20" s="5" t="n">
@@ -1552,7 +1413,7 @@
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="H21" s="5" t="n">
@@ -1598,7 +1459,7 @@
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="H22" s="5" t="n">
@@ -1690,7 +1551,7 @@
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-10-31</t>
         </is>
       </c>
       <c r="H24" s="5" t="n">
@@ -1736,7 +1597,7 @@
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="H25" s="5" t="n">
@@ -1782,7 +1643,7 @@
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-05-11</t>
         </is>
       </c>
       <c r="H26" s="5" t="n">
@@ -1828,7 +1689,7 @@
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-04-07</t>
         </is>
       </c>
       <c r="H27" s="5" t="n">
@@ -1874,7 +1735,7 @@
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-04-15</t>
         </is>
       </c>
       <c r="H28" s="5" t="n">
@@ -1920,7 +1781,7 @@
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-05-20</t>
         </is>
       </c>
       <c r="H29" s="5" t="n">
@@ -1966,7 +1827,7 @@
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-10-17</t>
         </is>
       </c>
       <c r="H30" s="5" t="n">
@@ -2012,7 +1873,7 @@
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="H31" s="5" t="n">
@@ -2058,7 +1919,7 @@
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-02-20</t>
         </is>
       </c>
       <c r="H32" s="5" t="n">
@@ -2104,7 +1965,7 @@
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-02-03</t>
         </is>
       </c>
       <c r="H33" s="5" t="n">
@@ -2150,7 +2011,7 @@
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-04-09</t>
         </is>
       </c>
       <c r="H34" s="5" t="n">
@@ -2196,7 +2057,7 @@
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-07-23</t>
         </is>
       </c>
       <c r="H35" s="5" t="n">
@@ -2242,7 +2103,7 @@
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-07-23</t>
         </is>
       </c>
       <c r="H36" s="5" t="n">
@@ -2288,7 +2149,7 @@
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-03-30</t>
         </is>
       </c>
       <c r="H37" s="5" t="n">
@@ -2334,7 +2195,7 @@
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="H38" s="5" t="n">
@@ -2380,7 +2241,7 @@
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-05-22</t>
         </is>
       </c>
       <c r="H39" s="5" t="n">
@@ -2426,7 +2287,7 @@
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-01-25</t>
         </is>
       </c>
       <c r="H40" s="5" t="n">
@@ -2472,7 +2333,7 @@
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="H41" s="5" t="n">
@@ -2518,7 +2379,7 @@
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="H42" s="5" t="n">
@@ -2564,7 +2425,7 @@
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="H43" s="5" t="n">
@@ -2610,7 +2471,7 @@
       </c>
       <c r="G44" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-03-19</t>
         </is>
       </c>
       <c r="H44" s="5" t="n">
@@ -2656,7 +2517,7 @@
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-06-19</t>
         </is>
       </c>
       <c r="H45" s="5" t="n">
@@ -2702,7 +2563,7 @@
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="H46" s="5" t="n">
@@ -2794,7 +2655,7 @@
       </c>
       <c r="G48" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-04-08</t>
         </is>
       </c>
       <c r="H48" s="5" t="n">
@@ -2840,7 +2701,7 @@
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-04-09</t>
         </is>
       </c>
       <c r="H49" s="5" t="n">
@@ -2886,7 +2747,7 @@
       </c>
       <c r="G50" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-03-27</t>
         </is>
       </c>
       <c r="H50" s="5" t="n">
@@ -2932,7 +2793,7 @@
       </c>
       <c r="G51" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-08-07</t>
         </is>
       </c>
       <c r="H51" s="5" t="n">
@@ -2978,7 +2839,7 @@
       </c>
       <c r="G52" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-01-22</t>
         </is>
       </c>
       <c r="H52" s="5" t="n">
@@ -3024,7 +2885,7 @@
       </c>
       <c r="G53" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-10-22</t>
         </is>
       </c>
       <c r="H53" s="5" t="n">
@@ -3070,7 +2931,7 @@
       </c>
       <c r="G54" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-08-25</t>
         </is>
       </c>
       <c r="H54" s="5" t="n">
@@ -3116,7 +2977,7 @@
       </c>
       <c r="G55" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-04-08</t>
         </is>
       </c>
       <c r="H55" s="5" t="n">
@@ -3162,7 +3023,7 @@
       </c>
       <c r="G56" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-01-23</t>
         </is>
       </c>
       <c r="H56" s="5" t="n">
@@ -3208,7 +3069,7 @@
       </c>
       <c r="G57" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-05-09</t>
         </is>
       </c>
       <c r="H57" s="5" t="n">
@@ -3254,7 +3115,7 @@
       </c>
       <c r="G58" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-05-02</t>
         </is>
       </c>
       <c r="H58" s="5" t="n">
@@ -3300,7 +3161,7 @@
       </c>
       <c r="G59" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-07-06</t>
         </is>
       </c>
       <c r="H59" s="5" t="n">
@@ -3346,7 +3207,7 @@
       </c>
       <c r="G60" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-01-12</t>
         </is>
       </c>
       <c r="H60" s="5" t="n">
@@ -3392,7 +3253,7 @@
       </c>
       <c r="G61" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-04-21</t>
         </is>
       </c>
       <c r="H61" s="5" t="n">
@@ -3438,7 +3299,7 @@
       </c>
       <c r="G62" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-11-23</t>
         </is>
       </c>
       <c r="H62" s="5" t="n">
@@ -3484,7 +3345,7 @@
       </c>
       <c r="G63" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="H63" s="5" t="n">
@@ -3530,7 +3391,7 @@
       </c>
       <c r="G64" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-08-11</t>
         </is>
       </c>
       <c r="H64" s="5" t="n">
@@ -3576,7 +3437,7 @@
       </c>
       <c r="G65" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-01-18</t>
         </is>
       </c>
       <c r="H65" s="5" t="n">
@@ -3622,7 +3483,7 @@
       </c>
       <c r="G66" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-01-10</t>
         </is>
       </c>
       <c r="H66" s="5" t="n">
@@ -3668,7 +3529,7 @@
       </c>
       <c r="G67" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-02-08</t>
         </is>
       </c>
       <c r="H67" s="5" t="n">
@@ -3714,7 +3575,7 @@
       </c>
       <c r="G68" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-07-03</t>
         </is>
       </c>
       <c r="H68" s="5" t="n">
@@ -3760,7 +3621,7 @@
       </c>
       <c r="G69" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-11-16</t>
         </is>
       </c>
       <c r="H69" s="5" t="n">
@@ -3806,7 +3667,7 @@
       </c>
       <c r="G70" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="H70" s="5" t="n">
@@ -3852,7 +3713,7 @@
       </c>
       <c r="G71" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="H71" s="5" t="n">
@@ -3898,7 +3759,7 @@
       </c>
       <c r="G72" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-07-18</t>
         </is>
       </c>
       <c r="H72" s="5" t="n">
@@ -3944,7 +3805,7 @@
       </c>
       <c r="G73" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-04-09</t>
         </is>
       </c>
       <c r="H73" s="5" t="n">
@@ -3990,7 +3851,7 @@
       </c>
       <c r="G74" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="H74" s="5" t="n">
@@ -4036,7 +3897,7 @@
       </c>
       <c r="G75" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="H75" s="5" t="n">
@@ -4082,7 +3943,7 @@
       </c>
       <c r="G76" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-07-01</t>
         </is>
       </c>
       <c r="H76" s="5" t="n">
@@ -4128,7 +3989,7 @@
       </c>
       <c r="G77" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-03-25</t>
         </is>
       </c>
       <c r="H77" s="5" t="n">
@@ -4174,7 +4035,7 @@
       </c>
       <c r="G78" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-11-14</t>
         </is>
       </c>
       <c r="H78" s="5" t="n">
@@ -4220,7 +4081,7 @@
       </c>
       <c r="G79" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-06-29</t>
         </is>
       </c>
       <c r="H79" s="5" t="n">
@@ -4266,7 +4127,7 @@
       </c>
       <c r="G80" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-02-23</t>
         </is>
       </c>
       <c r="H80" s="5" t="n">
@@ -4312,7 +4173,7 @@
       </c>
       <c r="G81" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-04-09</t>
         </is>
       </c>
       <c r="H81" s="5" t="n">
@@ -4358,7 +4219,7 @@
       </c>
       <c r="G82" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="H82" s="5" t="n">
@@ -4404,7 +4265,7 @@
       </c>
       <c r="G83" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-12-16</t>
         </is>
       </c>
       <c r="H83" s="5" t="n">
@@ -4450,7 +4311,7 @@
       </c>
       <c r="G84" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-02-20</t>
         </is>
       </c>
       <c r="H84" s="5" t="n">
@@ -4496,7 +4357,7 @@
       </c>
       <c r="G85" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-12-05</t>
         </is>
       </c>
       <c r="H85" s="5" t="n">
@@ -4542,7 +4403,7 @@
       </c>
       <c r="G86" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="H86" s="5" t="n">
@@ -4588,7 +4449,7 @@
       </c>
       <c r="G87" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="H87" s="5" t="n">
@@ -4634,7 +4495,7 @@
       </c>
       <c r="G88" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-07-06</t>
         </is>
       </c>
       <c r="H88" s="5" t="n">
@@ -4680,7 +4541,7 @@
       </c>
       <c r="G89" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-07-23</t>
         </is>
       </c>
       <c r="H89" s="5" t="n">
@@ -4726,7 +4587,7 @@
       </c>
       <c r="G90" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-07-13</t>
         </is>
       </c>
       <c r="H90" s="5" t="n">
@@ -4772,7 +4633,7 @@
       </c>
       <c r="G91" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-01-14</t>
         </is>
       </c>
       <c r="H91" s="5" t="n">
@@ -4818,7 +4679,7 @@
       </c>
       <c r="G92" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="H92" s="5" t="n">
@@ -4910,7 +4771,7 @@
       </c>
       <c r="G94" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-10-10</t>
         </is>
       </c>
       <c r="H94" s="5" t="n">
@@ -4956,7 +4817,7 @@
       </c>
       <c r="G95" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-10-23</t>
         </is>
       </c>
       <c r="H95" s="5" t="n">
@@ -5002,7 +4863,7 @@
       </c>
       <c r="G96" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-07-07</t>
         </is>
       </c>
       <c r="H96" s="5" t="n">
@@ -5048,7 +4909,7 @@
       </c>
       <c r="G97" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-07-23</t>
         </is>
       </c>
       <c r="H97" s="5" t="n">
@@ -5094,7 +4955,7 @@
       </c>
       <c r="G98" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-07-12</t>
         </is>
       </c>
       <c r="H98" s="5" t="n">
@@ -5140,7 +5001,7 @@
       </c>
       <c r="G99" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-03-19</t>
         </is>
       </c>
       <c r="H99" s="5" t="n">
@@ -5186,7 +5047,7 @@
       </c>
       <c r="G100" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-03-25</t>
         </is>
       </c>
       <c r="H100" s="5" t="n">
@@ -5232,7 +5093,7 @@
       </c>
       <c r="G101" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-07-04</t>
         </is>
       </c>
       <c r="H101" s="5" t="n">
@@ -5278,7 +5139,7 @@
       </c>
       <c r="G102" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-07-14</t>
         </is>
       </c>
       <c r="H102" s="5" t="n">
@@ -5324,7 +5185,7 @@
       </c>
       <c r="G103" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-07-08</t>
         </is>
       </c>
       <c r="H103" s="5" t="n">
@@ -5370,7 +5231,7 @@
       </c>
       <c r="G104" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-07-08</t>
         </is>
       </c>
       <c r="H104" s="5" t="n">
@@ -5416,7 +5277,7 @@
       </c>
       <c r="G105" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-07-08</t>
         </is>
       </c>
       <c r="H105" s="5" t="n">
@@ -5462,7 +5323,7 @@
       </c>
       <c r="G106" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-07-05</t>
         </is>
       </c>
       <c r="H106" s="5" t="n">
@@ -5508,7 +5369,7 @@
       </c>
       <c r="G107" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-10-23</t>
         </is>
       </c>
       <c r="H107" s="5" t="n">
@@ -5554,7 +5415,7 @@
       </c>
       <c r="G108" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-03-24</t>
         </is>
       </c>
       <c r="H108" s="5" t="n">
@@ -5600,7 +5461,7 @@
       </c>
       <c r="G109" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-07-04</t>
         </is>
       </c>
       <c r="H109" s="5" t="n">
@@ -5646,7 +5507,7 @@
       </c>
       <c r="G110" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-07-15</t>
         </is>
       </c>
       <c r="H110" s="5" t="n">
@@ -5692,7 +5553,7 @@
       </c>
       <c r="G111" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-07-12</t>
         </is>
       </c>
       <c r="H111" s="5" t="n">
@@ -5738,7 +5599,7 @@
       </c>
       <c r="G112" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-01-18</t>
         </is>
       </c>
       <c r="H112" s="5" t="n">
@@ -5784,7 +5645,7 @@
       </c>
       <c r="G113" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-07-07</t>
         </is>
       </c>
       <c r="H113" s="5" t="n">
@@ -5830,7 +5691,7 @@
       </c>
       <c r="G114" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-07-08</t>
         </is>
       </c>
       <c r="H114" s="5" t="n">
@@ -5876,7 +5737,7 @@
       </c>
       <c r="G115" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-07-05</t>
         </is>
       </c>
       <c r="H115" s="5" t="n">
@@ -5968,7 +5829,7 @@
       </c>
       <c r="G117" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-07-04</t>
         </is>
       </c>
       <c r="H117" s="5" t="n">
@@ -6014,7 +5875,7 @@
       </c>
       <c r="G118" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-07-08</t>
         </is>
       </c>
       <c r="H118" s="5" t="n">
@@ -6060,7 +5921,7 @@
       </c>
       <c r="G119" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="H119" s="5" t="n">
@@ -6106,7 +5967,7 @@
       </c>
       <c r="G120" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-07-12</t>
         </is>
       </c>
       <c r="H120" s="5" t="n">
@@ -6152,7 +6013,7 @@
       </c>
       <c r="G121" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-10-07</t>
         </is>
       </c>
       <c r="H121" s="5" t="n">
@@ -6244,7 +6105,7 @@
       </c>
       <c r="G123" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-03-24</t>
         </is>
       </c>
       <c r="H123" s="5" t="n">
@@ -6290,7 +6151,7 @@
       </c>
       <c r="G124" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-07-20</t>
         </is>
       </c>
       <c r="H124" s="5" t="n">
@@ -6336,7 +6197,7 @@
       </c>
       <c r="G125" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-03-02</t>
         </is>
       </c>
       <c r="H125" s="5" t="n">
@@ -6382,7 +6243,7 @@
       </c>
       <c r="G126" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-07-12</t>
         </is>
       </c>
       <c r="H126" s="5" t="n">
@@ -6428,7 +6289,7 @@
       </c>
       <c r="G127" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-08-20</t>
         </is>
       </c>
       <c r="H127" s="5" t="n">
@@ -6474,7 +6335,7 @@
       </c>
       <c r="G128" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-07-13</t>
         </is>
       </c>
       <c r="H128" s="5" t="n">
@@ -6520,7 +6381,7 @@
       </c>
       <c r="G129" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-07-12</t>
         </is>
       </c>
       <c r="H129" s="5" t="n">
@@ -6566,7 +6427,7 @@
       </c>
       <c r="G130" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-07-08</t>
         </is>
       </c>
       <c r="H130" s="5" t="n">
@@ -6612,7 +6473,7 @@
       </c>
       <c r="G131" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-07-15</t>
         </is>
       </c>
       <c r="H131" s="5" t="n">
@@ -6658,7 +6519,7 @@
       </c>
       <c r="G132" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-03-24</t>
         </is>
       </c>
       <c r="H132" s="5" t="n">
@@ -6750,7 +6611,7 @@
       </c>
       <c r="G134" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-07-07</t>
         </is>
       </c>
       <c r="H134" s="5" t="n">
@@ -6796,7 +6657,7 @@
       </c>
       <c r="G135" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-01-26</t>
         </is>
       </c>
       <c r="H135" s="5" t="n">
@@ -6842,7 +6703,7 @@
       </c>
       <c r="G136" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-08-08</t>
         </is>
       </c>
       <c r="H136" s="5" t="n">
@@ -6888,7 +6749,7 @@
       </c>
       <c r="G137" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-07-04</t>
         </is>
       </c>
       <c r="H137" s="5" t="n">
@@ -6934,7 +6795,7 @@
       </c>
       <c r="G138" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-07-15</t>
         </is>
       </c>
       <c r="H138" s="5" t="n">
@@ -6980,7 +6841,7 @@
       </c>
       <c r="G139" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-03-19</t>
         </is>
       </c>
       <c r="H139" s="5" t="n">
@@ -7026,7 +6887,7 @@
       </c>
       <c r="G140" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-07-08</t>
         </is>
       </c>
       <c r="H140" s="5" t="n">
@@ -7072,7 +6933,7 @@
       </c>
       <c r="G141" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-07-08</t>
         </is>
       </c>
       <c r="H141" s="5" t="n">
@@ -7118,7 +6979,7 @@
       </c>
       <c r="G142" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-07-12</t>
         </is>
       </c>
       <c r="H142" s="5" t="n">
@@ -7164,7 +7025,7 @@
       </c>
       <c r="G143" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-07-11</t>
         </is>
       </c>
       <c r="H143" s="5" t="n">
@@ -7210,7 +7071,7 @@
       </c>
       <c r="G144" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-07-13</t>
         </is>
       </c>
       <c r="H144" s="5" t="n">
@@ -7302,7 +7163,7 @@
       </c>
       <c r="G146" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-07-05</t>
         </is>
       </c>
       <c r="H146" s="5" t="n">
@@ -7394,7 +7255,7 @@
       </c>
       <c r="G148" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-04-13</t>
         </is>
       </c>
       <c r="H148" s="5" t="n">
@@ -7440,7 +7301,7 @@
       </c>
       <c r="G149" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-07-07</t>
         </is>
       </c>
       <c r="H149" s="5" t="n">
@@ -7486,7 +7347,7 @@
       </c>
       <c r="G150" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-02-13</t>
         </is>
       </c>
       <c r="H150" s="5" t="n">
@@ -7532,7 +7393,7 @@
       </c>
       <c r="G151" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-07-11</t>
         </is>
       </c>
       <c r="H151" s="5" t="n">
@@ -7578,7 +7439,7 @@
       </c>
       <c r="G152" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-07-08</t>
         </is>
       </c>
       <c r="H152" s="5" t="n">
@@ -7624,7 +7485,7 @@
       </c>
       <c r="G153" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-07-05</t>
         </is>
       </c>
       <c r="H153" s="5" t="n">
@@ -7670,7 +7531,7 @@
       </c>
       <c r="G154" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-07-05</t>
         </is>
       </c>
       <c r="H154" s="5" t="n">
@@ -7716,7 +7577,7 @@
       </c>
       <c r="G155" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-03-21</t>
         </is>
       </c>
       <c r="H155" s="5" t="n">
@@ -7762,7 +7623,7 @@
       </c>
       <c r="G156" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-07-07</t>
         </is>
       </c>
       <c r="H156" s="5" t="n">
@@ -7808,7 +7669,7 @@
       </c>
       <c r="G157" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-07-07</t>
         </is>
       </c>
       <c r="H157" s="5" t="n">
@@ -7854,7 +7715,7 @@
       </c>
       <c r="G158" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-07-13</t>
         </is>
       </c>
       <c r="H158" s="5" t="n">
@@ -7900,7 +7761,7 @@
       </c>
       <c r="G159" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-07-11</t>
         </is>
       </c>
       <c r="H159" s="5" t="n">
@@ -7946,7 +7807,7 @@
       </c>
       <c r="G160" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-07-12</t>
         </is>
       </c>
       <c r="H160" s="5" t="n">
@@ -7992,7 +7853,7 @@
       </c>
       <c r="G161" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-07-11</t>
         </is>
       </c>
       <c r="H161" s="5" t="n">
@@ -8038,7 +7899,7 @@
       </c>
       <c r="G162" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-07-13</t>
         </is>
       </c>
       <c r="H162" s="5" t="n">
@@ -8130,7 +7991,7 @@
       </c>
       <c r="G164" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-07-08</t>
         </is>
       </c>
       <c r="H164" s="5" t="n">
@@ -8176,7 +8037,7 @@
       </c>
       <c r="G165" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-07-15</t>
         </is>
       </c>
       <c r="H165" s="5" t="n">
@@ -8222,7 +8083,7 @@
       </c>
       <c r="G166" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-07-08</t>
         </is>
       </c>
       <c r="H166" s="5" t="n">
@@ -8268,7 +8129,7 @@
       </c>
       <c r="G167" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-07-12</t>
         </is>
       </c>
       <c r="H167" s="5" t="n">
@@ -8290,1621 +8151,4 @@
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:I26"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
-    <col width="18" customWidth="1" min="9" max="9"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>VAU Residence - VAU Residence 销控网格图</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>总套数</t>
-        </is>
-      </c>
-      <c r="B2" s="7" t="inlineStr">
-        <is>
-          <t>在售 (Sale)</t>
-        </is>
-      </c>
-      <c r="C2" s="8" t="inlineStr">
-        <is>
-          <t>已定价未售</t>
-        </is>
-      </c>
-      <c r="D2" s="9" t="inlineStr">
-        <is>
-          <t>已售 (Sold)</t>
-        </is>
-      </c>
-      <c r="E2" s="10" t="inlineStr">
-        <is>
-          <t>暂停销售</t>
-        </is>
-      </c>
-      <c r="F2" s="6" t="inlineStr">
-        <is>
-          <t>待售 (Pending)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>165 套</t>
-        </is>
-      </c>
-      <c r="B3" s="12" t="inlineStr">
-        <is>
-          <t>7 套</t>
-        </is>
-      </c>
-      <c r="C3" s="13" t="inlineStr">
-        <is>
-          <t>1 套</t>
-        </is>
-      </c>
-      <c r="D3" s="14" t="inlineStr">
-        <is>
-          <t>155 套</t>
-        </is>
-      </c>
-      <c r="E3" s="15" t="inlineStr">
-        <is>
-          <t>2 套</t>
-        </is>
-      </c>
-      <c r="F3" s="11" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="25" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>楼层\房号</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>E</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>G</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>H</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="65" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>28/F</t>
-        </is>
-      </c>
-      <c r="B6" s="16" t="inlineStr">
-        <is>
-          <t>A | 283呎 (1房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="C6" s="16" t="inlineStr">
-        <is>
-          <t>B | 277呎 (1房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="D6" s="17" t="inlineStr">
-        <is>
-          <t>C | 264呎 (1房)
-$968万
-$36,655/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="E6" s="16" t="inlineStr">
-        <is>
-          <t>D | 210呎 (开放式)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="F6" s="16" t="inlineStr">
-        <is>
-          <t>E | 209呎 (开放式)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="G6" s="18" t="inlineStr">
-        <is>
-          <t>F | 384呎 (2房)
-$1,306万
-$34,000/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H6" s="18" t="inlineStr">
-        <is>
-          <t>G | 499呎 (3房)
-$1,697万
-$34,000/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="I6" s="19" t="inlineStr"/>
-    </row>
-    <row r="7" ht="65" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>27/F</t>
-        </is>
-      </c>
-      <c r="B7" s="18" t="inlineStr">
-        <is>
-          <t>A | 282呎 (1房)
-$778万
-$27,603/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C7" s="18" t="inlineStr">
-        <is>
-          <t>B | 278呎 (1房)
-$766万
-$27,543/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D7" s="18" t="inlineStr">
-        <is>
-          <t>C | 264呎 (1房)
-$779万
-$29,504/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E7" s="18" t="inlineStr">
-        <is>
-          <t>D | 210呎 (开放式)
-$581万
-$27,667/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F7" s="18" t="inlineStr">
-        <is>
-          <t>E | 209呎 (开放式)
-$618万
-$29,589/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G7" s="18" t="inlineStr">
-        <is>
-          <t>F | 384呎 (2房)
-$1,039万
-$27,062/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H7" s="18" t="inlineStr">
-        <is>
-          <t>G | 499呎 (3房)
-$1,272万
-$25,497/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="I7" s="19" t="inlineStr"/>
-    </row>
-    <row r="8" ht="65" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>26/F</t>
-        </is>
-      </c>
-      <c r="B8" s="16" t="inlineStr">
-        <is>
-          <t>A | 283呎 (1房)
-$980万
-$34,622/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="C8" s="18" t="inlineStr">
-        <is>
-          <t>B | 278呎 (1房)
-$670万
-$24,086/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D8" s="18" t="inlineStr">
-        <is>
-          <t>C | 264呎 (1房)
-$714万
-$27,061/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E8" s="18" t="inlineStr">
-        <is>
-          <t>D | 210呎 (开放式)
-$504万
-$24,014/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F8" s="18" t="inlineStr">
-        <is>
-          <t>E | 209呎 (开放式)
-$480万
-$22,967/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G8" s="18" t="inlineStr">
-        <is>
-          <t>F | 384呎 (2房)
-$1,164万
-$30,320/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H8" s="16" t="inlineStr">
-        <is>
-          <t>G | 499呎 (3房)
-$1,658万
-$33,216/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="I8" s="19" t="inlineStr"/>
-    </row>
-    <row r="9" ht="65" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>25/F</t>
-        </is>
-      </c>
-      <c r="B9" s="18" t="inlineStr">
-        <is>
-          <t>A | 282呎 (1房)
-$632万
-$22,429/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C9" s="18" t="inlineStr">
-        <is>
-          <t>B | 278呎 (1房)
-$601万
-$21,615/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D9" s="18" t="inlineStr">
-        <is>
-          <t>C | 264呎 (1房)
-$592万
-$22,420/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E9" s="18" t="inlineStr">
-        <is>
-          <t>D | 210呎 (开放式)
-$470万
-$22,390/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F9" s="18" t="inlineStr">
-        <is>
-          <t>E | 209呎 (开放式)
-$679万
-$32,507/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G9" s="18" t="inlineStr">
-        <is>
-          <t>F | 285呎 (1房)
-$862万
-$30,263/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H9" s="18" t="inlineStr">
-        <is>
-          <t>G | 211呎 (开放式)
-$488万
-$23,147/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="I9" s="18" t="inlineStr">
-        <is>
-          <t>H | 388呎 (2房)
-$855万
-$22,039/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="65" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>23/F</t>
-        </is>
-      </c>
-      <c r="B10" s="18" t="inlineStr">
-        <is>
-          <t>A | 282呎 (1房)
-$591万
-$20,961/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C10" s="18" t="inlineStr">
-        <is>
-          <t>B | 278呎 (1房)
-$592万
-$21,277/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D10" s="18" t="inlineStr">
-        <is>
-          <t>C | 264呎 (1房)
-$579万
-$21,928/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E10" s="18" t="inlineStr">
-        <is>
-          <t>D | 210呎 (开放式)
-$480万
-$22,833/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F10" s="18" t="inlineStr">
-        <is>
-          <t>E | 209呎 (开放式)
-$479万
-$22,900/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G10" s="18" t="inlineStr">
-        <is>
-          <t>F | 285呎 (1房)
-$860万
-$30,172/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H10" s="18" t="inlineStr">
-        <is>
-          <t>G | 211呎 (开放式)
-$522万
-$24,749/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="I10" s="18" t="inlineStr">
-        <is>
-          <t>H | 388呎 (2房)
-$847万
-$21,820/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="65" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>22/F</t>
-        </is>
-      </c>
-      <c r="B11" s="16" t="inlineStr">
-        <is>
-          <t>A | 283呎 (1房)
-$942万
-$33,279/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="C11" s="18" t="inlineStr">
-        <is>
-          <t>B | 278呎 (1房)
-$664万
-$23,874/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D11" s="18" t="inlineStr">
-        <is>
-          <t>C | 264呎 (1房)
-$572万
-$21,667/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E11" s="18" t="inlineStr">
-        <is>
-          <t>D | 210呎 (开放式)
-$456万
-$21,719/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F11" s="18" t="inlineStr">
-        <is>
-          <t>E | 209呎 (开放式)
-$451万
-$21,579/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G11" s="18" t="inlineStr">
-        <is>
-          <t>F | 285呎 (1房)
-$767万
-$26,926/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H11" s="18" t="inlineStr">
-        <is>
-          <t>G | 211呎 (开放式)
-$641万
-$30,370/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="I11" s="18" t="inlineStr">
-        <is>
-          <t>H | 388呎 (2房)
-$875万
-$22,541/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="65" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>21/F</t>
-        </is>
-      </c>
-      <c r="B12" s="18" t="inlineStr">
-        <is>
-          <t>A | 282呎 (1房)
-$577万
-$20,465/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C12" s="18" t="inlineStr">
-        <is>
-          <t>B | 278呎 (1房)
-$578万
-$20,773/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D12" s="18" t="inlineStr">
-        <is>
-          <t>C | 264呎 (1房)
-$565万
-$21,413/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E12" s="18" t="inlineStr">
-        <is>
-          <t>D | 210呎 (开放式)
-$451万
-$21,462/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F12" s="18" t="inlineStr">
-        <is>
-          <t>E | 209呎 (开放式)
-$446万
-$21,316/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G12" s="18" t="inlineStr">
-        <is>
-          <t>F | 285呎 (1房)
-$840万
-$29,488/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H12" s="18" t="inlineStr">
-        <is>
-          <t>G | 211呎 (开放式)
-$468万
-$22,194/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="I12" s="18" t="inlineStr">
-        <is>
-          <t>H | 388呎 (2房)
-$830万
-$21,387/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="65" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>20/F</t>
-        </is>
-      </c>
-      <c r="B13" s="18" t="inlineStr">
-        <is>
-          <t>A | 282呎 (1房)
-$627万
-$22,245/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C13" s="18" t="inlineStr">
-        <is>
-          <t>B | 278呎 (1房)
-$660万
-$23,730/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D13" s="18" t="inlineStr">
-        <is>
-          <t>C | 264呎 (1房)
-$786万
-$29,754/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E13" s="18" t="inlineStr">
-        <is>
-          <t>D | 210呎 (开放式)
-$445万
-$21,210/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F13" s="18" t="inlineStr">
-        <is>
-          <t>E | 209呎 (开放式)
-$474万
-$22,694/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G13" s="18" t="inlineStr">
-        <is>
-          <t>F | 285呎 (1房)
-$786万
-$27,568/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H13" s="18" t="inlineStr">
-        <is>
-          <t>G | 211呎 (开放式)
-$672万
-$31,834/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="I13" s="18" t="inlineStr">
-        <is>
-          <t>H | 388呎 (2房)
-$821万
-$21,170/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="65" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>19/F</t>
-        </is>
-      </c>
-      <c r="B14" s="18" t="inlineStr">
-        <is>
-          <t>A | 282呎 (1房)
-$635万
-$22,511/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C14" s="18" t="inlineStr">
-        <is>
-          <t>B | 278呎 (1房)
-$785万
-$28,248/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D14" s="18" t="inlineStr">
-        <is>
-          <t>C | 264呎 (1房)
-$624万
-$23,652/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E14" s="18" t="inlineStr">
-        <is>
-          <t>D | 210呎 (开放式)
-$474万
-$22,562/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F14" s="18" t="inlineStr">
-        <is>
-          <t>E | 209呎 (开放式)
-$496万
-$23,718/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G14" s="18" t="inlineStr">
-        <is>
-          <t>F | 285呎 (1房)
-$739万
-$25,923/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H14" s="18" t="inlineStr">
-        <is>
-          <t>G | 211呎 (开放式)
-$516万
-$24,455/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="I14" s="18" t="inlineStr">
-        <is>
-          <t>H | 388呎 (2房)
-$821万
-$21,170/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="65" customHeight="1">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>18/F</t>
-        </is>
-      </c>
-      <c r="B15" s="18" t="inlineStr">
-        <is>
-          <t>A | 282呎 (1房)
-$596万
-$21,121/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C15" s="18" t="inlineStr">
-        <is>
-          <t>B | 278呎 (1房)
-$563万
-$20,259/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D15" s="18" t="inlineStr">
-        <is>
-          <t>C | 264呎 (1房)
-$551万
-$20,886/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E15" s="18" t="inlineStr">
-        <is>
-          <t>D | 210呎 (开放式)
-$472万
-$22,495/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F15" s="18" t="inlineStr">
-        <is>
-          <t>E | 209呎 (开放式)
-$471万
-$22,555/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G15" s="18" t="inlineStr">
-        <is>
-          <t>F | 285呎 (1房)
-$730万
-$25,600/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H15" s="18" t="inlineStr">
-        <is>
-          <t>G | 211呎 (开放式)
-$648万
-$30,735/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="I15" s="18" t="inlineStr">
-        <is>
-          <t>H | 388呎 (2房)
-$821万
-$21,170/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="65" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>17/F</t>
-        </is>
-      </c>
-      <c r="B16" s="18" t="inlineStr">
-        <is>
-          <t>A | 282呎 (1房)
-$594万
-$21,057/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C16" s="18" t="inlineStr">
-        <is>
-          <t>B | 278呎 (1房)
-$559万
-$20,119/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D16" s="18" t="inlineStr">
-        <is>
-          <t>C | 264呎 (1房)
-$548万
-$20,742/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E16" s="18" t="inlineStr">
-        <is>
-          <t>D | 210呎 (开放式)
-$430万
-$20,457/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F16" s="18" t="inlineStr">
-        <is>
-          <t>E | 209呎 (开放式)
-$423万
-$20,230/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G16" s="18" t="inlineStr">
-        <is>
-          <t>F | 285呎 (1房)
-$744万
-$26,105/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H16" s="18" t="inlineStr">
-        <is>
-          <t>G | 211呎 (开放式)
-$648万
-$30,711/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="I16" s="18" t="inlineStr">
-        <is>
-          <t>H | 388呎 (2房)
-$930万
-$23,966/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="65" customHeight="1">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>16/F</t>
-        </is>
-      </c>
-      <c r="B17" s="18" t="inlineStr">
-        <is>
-          <t>A | 282呎 (1房)
-$548万
-$19,418/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C17" s="18" t="inlineStr">
-        <is>
-          <t>B | 278呎 (1房)
-$754万
-$27,104/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D17" s="20" t="inlineStr">
-        <is>
-          <t>C | 264呎 (1房)
-$839万
-$31,769/呎
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="E17" s="18" t="inlineStr">
-        <is>
-          <t>D | 210呎 (开放式)
-$428万
-$20,381/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F17" s="18" t="inlineStr">
-        <is>
-          <t>E | 209呎 (开放式)
-$421万
-$20,148/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G17" s="18" t="inlineStr">
-        <is>
-          <t>F | 285呎 (1房)
-$783万
-$27,481/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H17" s="18" t="inlineStr">
-        <is>
-          <t>G | 211呎 (开放式)
-$488万
-$23,114/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="I17" s="18" t="inlineStr">
-        <is>
-          <t>H | 388呎 (2房)
-$991万
-$25,549/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="65" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>15/F</t>
-        </is>
-      </c>
-      <c r="B18" s="18" t="inlineStr">
-        <is>
-          <t>A | 282呎 (1房)
-$734万
-$26,025/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C18" s="18" t="inlineStr">
-        <is>
-          <t>B | 278呎 (1房)
-$735万
-$26,424/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D18" s="18" t="inlineStr">
-        <is>
-          <t>C | 264呎 (1房)
-$706万
-$26,723/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E18" s="18" t="inlineStr">
-        <is>
-          <t>D | 210呎 (开放式)
-$611万
-$29,090/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F18" s="18" t="inlineStr">
-        <is>
-          <t>E | 209呎 (开放式)
-$428万
-$20,478/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G18" s="18" t="inlineStr">
-        <is>
-          <t>F | 285呎 (1房)
-$762万
-$26,737/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H18" s="18" t="inlineStr">
-        <is>
-          <t>G | 211呎 (开放式)
-$486万
-$23,047/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="I18" s="18" t="inlineStr">
-        <is>
-          <t>H | 388呎 (2房)
-$987万
-$25,443/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="65" customHeight="1">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>12/F</t>
-        </is>
-      </c>
-      <c r="B19" s="18" t="inlineStr">
-        <is>
-          <t>A | 282呎 (1房)
-$731万
-$25,918/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C19" s="18" t="inlineStr">
-        <is>
-          <t>B | 277呎 (1房)
-$732万
-$26,408/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D19" s="18" t="inlineStr">
-        <is>
-          <t>C | 264呎 (1房)
-$698万
-$26,458/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E19" s="18" t="inlineStr">
-        <is>
-          <t>D | 210呎 (开放式)
-$603万
-$28,700/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F19" s="18" t="inlineStr">
-        <is>
-          <t>E | 209呎 (开放式)
-$414万
-$19,794/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G19" s="18" t="inlineStr">
-        <is>
-          <t>F | 285呎 (1房)
-$724万
-$25,418/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H19" s="18" t="inlineStr">
-        <is>
-          <t>G | 211呎 (开放式)
-$582万
-$27,607/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="I19" s="18" t="inlineStr">
-        <is>
-          <t>H | 388呎 (2房)
-$934万
-$24,075/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="65" customHeight="1">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>11/F</t>
-        </is>
-      </c>
-      <c r="B20" s="18" t="inlineStr">
-        <is>
-          <t>A | 282呎 (1房)
-$530万
-$18,777/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C20" s="18" t="inlineStr">
-        <is>
-          <t>B | 277呎 (1房)
-$696万
-$25,108/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D20" s="18" t="inlineStr">
-        <is>
-          <t>C | 264呎 (1房)
-$659万
-$24,958/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E20" s="18" t="inlineStr">
-        <is>
-          <t>D | 210呎 (开放式)
-$578万
-$27,543/呎
-(21年-06月)</t>
-        </is>
-      </c>
-      <c r="F20" s="18" t="inlineStr">
-        <is>
-          <t>E | 209呎 (开放式)
-$553万
-$26,450/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G20" s="18" t="inlineStr">
-        <is>
-          <t>F | 285呎 (1房)
-$756万
-$26,523/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H20" s="18" t="inlineStr">
-        <is>
-          <t>G | 211呎 (开放式)
-$592万
-$28,047/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="I20" s="18" t="inlineStr">
-        <is>
-          <t>H | 388呎 (2房)
-$970万
-$24,995/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="65" customHeight="1">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>10/F</t>
-        </is>
-      </c>
-      <c r="B21" s="18" t="inlineStr">
-        <is>
-          <t>A | 282呎 (1房)
-$527万
-$18,699/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C21" s="18" t="inlineStr">
-        <is>
-          <t>B | 277呎 (1房)
-$719万
-$25,942/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D21" s="18" t="inlineStr">
-        <is>
-          <t>C | 264呎 (1房)
-$659万
-$24,951/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E21" s="18" t="inlineStr">
-        <is>
-          <t>D | 210呎 (开放式)
-$570万
-$27,162/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F21" s="18" t="inlineStr">
-        <is>
-          <t>E | 209呎 (开放式)
-$590万
-$28,225/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G21" s="18" t="inlineStr">
-        <is>
-          <t>F | 285呎 (1房)
-$712万
-$24,965/呎
-(21年-06月)</t>
-        </is>
-      </c>
-      <c r="H21" s="18" t="inlineStr">
-        <is>
-          <t>G | 211呎 (开放式)
-$557万
-$26,408/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="I21" s="18" t="inlineStr">
-        <is>
-          <t>H | 388呎 (2房)
-$961万
-$24,771/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="65" customHeight="1">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>9/F</t>
-        </is>
-      </c>
-      <c r="B22" s="18" t="inlineStr">
-        <is>
-          <t>A | 283呎 (1房)
-$689万
-$24,360/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C22" s="18" t="inlineStr">
-        <is>
-          <t>B | 278呎 (1房)
-$683万
-$24,576/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D22" s="18" t="inlineStr">
-        <is>
-          <t>C | 264呎 (1房)
-$610万
-$23,098/呎
-(21年-06月)</t>
-        </is>
-      </c>
-      <c r="E22" s="18" t="inlineStr">
-        <is>
-          <t>D | 210呎 (开放式)
-$581万
-$27,667/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F22" s="18" t="inlineStr">
-        <is>
-          <t>E | 209呎 (开放式)
-$543万
-$25,976/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G22" s="18" t="inlineStr">
-        <is>
-          <t>F | 285呎 (1房)
-$742万
-$26,049/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H22" s="18" t="inlineStr">
-        <is>
-          <t>G | 211呎 (开放式)
-$555万
-$26,303/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="I22" s="18" t="inlineStr">
-        <is>
-          <t>H | 388呎 (2房)
-$957万
-$24,673/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="65" customHeight="1">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>8/F</t>
-        </is>
-      </c>
-      <c r="B23" s="18" t="inlineStr">
-        <is>
-          <t>A | 283呎 (1房)
-$689万
-$24,336/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C23" s="18" t="inlineStr">
-        <is>
-          <t>B | 277呎 (1房)
-$701万
-$25,292/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D23" s="18" t="inlineStr">
-        <is>
-          <t>C | 264呎 (1房)
-$635万
-$24,045/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E23" s="18" t="inlineStr">
-        <is>
-          <t>D | 210呎 (开放式)
-$531万
-$25,281/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F23" s="18" t="inlineStr">
-        <is>
-          <t>E | 209呎 (开放式)
-$570万
-$27,249/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G23" s="18" t="inlineStr">
-        <is>
-          <t>F | 285呎 (1房)
-$708万
-$24,842/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H23" s="18" t="inlineStr">
-        <is>
-          <t>G | 211呎 (开放式)
-$581万
-$27,526/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="I23" s="18" t="inlineStr">
-        <is>
-          <t>H | 388呎 (2房)
-$924万
-$23,807/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="65" customHeight="1">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>7/F</t>
-        </is>
-      </c>
-      <c r="B24" s="18" t="inlineStr">
-        <is>
-          <t>A | 283呎 (1房)
-$716万
-$25,318/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C24" s="18" t="inlineStr">
-        <is>
-          <t>B | 277呎 (1房)
-$672万
-$24,260/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D24" s="18" t="inlineStr">
-        <is>
-          <t>C | 264呎 (1房)
-$660万
-$25,011/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E24" s="18" t="inlineStr">
-        <is>
-          <t>D | 209呎 (开放式)
-$531万
-$25,407/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F24" s="18" t="inlineStr">
-        <is>
-          <t>E | 209呎 (开放式)
-$553万
-$26,459/呎
-(21年-06月)</t>
-        </is>
-      </c>
-      <c r="G24" s="18" t="inlineStr">
-        <is>
-          <t>F | 286呎 (1房)
-$718万
-$25,108/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H24" s="20" t="inlineStr">
-        <is>
-          <t>G | 211呎 (开放式)
-$655万
-$31,057/呎
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="I24" s="18" t="inlineStr">
-        <is>
-          <t>H | 388呎 (2房)
-$950万
-$24,477/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="65" customHeight="1">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>6/F</t>
-        </is>
-      </c>
-      <c r="B25" s="18" t="inlineStr">
-        <is>
-          <t>A | 282呎 (1房)
-$714万
-$25,305/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C25" s="18" t="inlineStr">
-        <is>
-          <t>B | 277呎 (1房)
-$693万
-$25,007/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D25" s="18" t="inlineStr">
-        <is>
-          <t>C | 264呎 (1房)
-$658万
-$24,905/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E25" s="18" t="inlineStr">
-        <is>
-          <t>D | 209呎 (开放式)
-$522万
-$24,995/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F25" s="18" t="inlineStr">
-        <is>
-          <t>E | 209呎 (开放式)
-$563万
-$26,938/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G25" s="18" t="inlineStr">
-        <is>
-          <t>F | 286呎 (1房)
-$703万
-$24,566/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H25" s="18" t="inlineStr">
-        <is>
-          <t>G | 211呎 (开放式)
-$548万
-$25,986/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="I25" s="18" t="inlineStr">
-        <is>
-          <t>H | 388呎 (2房)
-$946万
-$24,376/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="65" customHeight="1">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>5/F</t>
-        </is>
-      </c>
-      <c r="B26" s="18" t="inlineStr">
-        <is>
-          <t>A | 282呎 (1房)
-$711万
-$25,199/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C26" s="18" t="inlineStr">
-        <is>
-          <t>B | 277呎 (1房)
-$658万
-$23,765/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D26" s="18" t="inlineStr">
-        <is>
-          <t>C | 264呎 (1房)
-$655万
-$24,799/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E26" s="18" t="inlineStr">
-        <is>
-          <t>D | 209呎 (开放式)
-$524万
-$25,053/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F26" s="18" t="inlineStr">
-        <is>
-          <t>E | 209呎 (开放式)
-$523万
-$25,033/呎
-(21年-06月)</t>
-        </is>
-      </c>
-      <c r="G26" s="18" t="inlineStr">
-        <is>
-          <t>F | 286呎 (1房)
-$733万
-$25,633/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H26" s="18" t="inlineStr">
-        <is>
-          <t>G | 211呎 (开放式)
-$572万
-$27,109/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="I26" s="18" t="inlineStr">
-        <is>
-          <t>H | 388呎 (2房)
-$899万
-$23,175/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:I1"/>
-  </mergeCells>
-  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
-</worksheet>
 </file>
--- a/files/九龙-何文田-VAU Residence.xlsx
+++ b/files/九龙-何文田-VAU Residence.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="销控汇总明细" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VAU Residence" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -19,7 +20,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="21">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -41,8 +42,102 @@
       <name val="Microsoft YaHei"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00000000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00002060"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00002060"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00660000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00660000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="007F7F7F"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="007F7F7F"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00002060"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00660000"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="8"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -53,6 +148,42 @@
       <patternFill patternType="solid">
         <fgColor rgb="00F2F2F2"/>
         <bgColor rgb="00F2F2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+        <bgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00A9F5A9"/>
+        <bgColor rgb="00A9F5A9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00A9D0F5"/>
+        <bgColor rgb="00A9D0F5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F5A9A9"/>
+        <bgColor rgb="00F5A9A9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC000"/>
+        <bgColor rgb="00FFC000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E8E8E8"/>
+        <bgColor rgb="00E8E8E8"/>
       </patternFill>
     </fill>
   </fills>
@@ -82,7 +213,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -98,6 +229,63 @@
     </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -474,7 +662,7 @@
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
   </cols>
@@ -8151,4 +8339,1621 @@
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:I25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>VAU Residence 销控网格图</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>总套数</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>在售 (Sale)</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>已定价未售</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>已售 (Sold)</t>
+        </is>
+      </c>
+      <c r="E2" s="11" t="inlineStr">
+        <is>
+          <t>暂停销售</t>
+        </is>
+      </c>
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t>待售 (Pending)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>165</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>155</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>楼层</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C4" s="19" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D4" s="19" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E4" s="19" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="F4" s="19" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="G4" s="19" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="H4" s="19" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="I4" s="19" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B5" s="20" t="inlineStr">
+        <is>
+          <t>A | 283呎 (1房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C5" s="20" t="inlineStr">
+        <is>
+          <t>B | 277呎 (1房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="D5" s="21" t="inlineStr">
+        <is>
+          <t>C | 264呎 (1房)
+$968万
+$36,655/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="E5" s="20" t="inlineStr">
+        <is>
+          <t>D | 210呎 (开放式)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="F5" s="20" t="inlineStr">
+        <is>
+          <t>E | 209呎 (开放式)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="G5" s="22" t="inlineStr">
+        <is>
+          <t>F | 384呎 (2房)
+$1306万
+$34,000/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="H5" s="22" t="inlineStr">
+        <is>
+          <t>G | 499呎 (3房)
+$1697万
+$34,000/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="I5" s="23" t="inlineStr"/>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B6" s="22" t="inlineStr">
+        <is>
+          <t>A | 282呎 (1房)
+$778万
+$27,603/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="C6" s="22" t="inlineStr">
+        <is>
+          <t>B | 278呎 (1房)
+$766万
+$27,543/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="D6" s="22" t="inlineStr">
+        <is>
+          <t>C | 264呎 (1房)
+$779万
+$29,504/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="E6" s="22" t="inlineStr">
+        <is>
+          <t>D | 210呎 (开放式)
+$581万
+$27,667/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="F6" s="22" t="inlineStr">
+        <is>
+          <t>E | 209呎 (开放式)
+$618万
+$29,589/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="G6" s="22" t="inlineStr">
+        <is>
+          <t>F | 384呎 (2房)
+$1039万
+$27,062/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="H6" s="22" t="inlineStr">
+        <is>
+          <t>G | 499呎 (3房)
+$1272万
+$25,497/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="I6" s="23" t="inlineStr"/>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B7" s="20" t="inlineStr">
+        <is>
+          <t>A | 283呎 (1房)
+$980万
+$34,622/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="C7" s="22" t="inlineStr">
+        <is>
+          <t>B | 278呎 (1房)
+$670万
+$24,086/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="D7" s="22" t="inlineStr">
+        <is>
+          <t>C | 264呎 (1房)
+$714万
+$27,061/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="E7" s="22" t="inlineStr">
+        <is>
+          <t>D | 210呎 (开放式)
+$504万
+$24,014/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="F7" s="22" t="inlineStr">
+        <is>
+          <t>E | 209呎 (开放式)
+$480万
+$22,967/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="G7" s="22" t="inlineStr">
+        <is>
+          <t>F | 384呎 (2房)
+$1164万
+$30,320/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="H7" s="20" t="inlineStr">
+        <is>
+          <t>G | 499呎 (3房)
+$1658万
+$33,216/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="I7" s="23" t="inlineStr"/>
+    </row>
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B8" s="22" t="inlineStr">
+        <is>
+          <t>A | 282呎 (1房)
+$632万
+$22,429/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="C8" s="22" t="inlineStr">
+        <is>
+          <t>B | 278呎 (1房)
+$601万
+$21,615/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="D8" s="22" t="inlineStr">
+        <is>
+          <t>C | 264呎 (1房)
+$592万
+$22,420/呎
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="E8" s="22" t="inlineStr">
+        <is>
+          <t>D | 210呎 (开放式)
+$470万
+$22,390/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="F8" s="22" t="inlineStr">
+        <is>
+          <t>E | 209呎 (开放式)
+$679万
+$32,507/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="G8" s="22" t="inlineStr">
+        <is>
+          <t>F | 285呎 (1房)
+$862万
+$30,263/呎
+(23年-05月)</t>
+        </is>
+      </c>
+      <c r="H8" s="22" t="inlineStr">
+        <is>
+          <t>G | 211呎 (开放式)
+$488万
+$23,147/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="I8" s="22" t="inlineStr">
+        <is>
+          <t>H | 388呎 (2房)
+$855万
+$22,039/呎
+(24年-10月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B9" s="22" t="inlineStr">
+        <is>
+          <t>A | 282呎 (1房)
+$591万
+$20,961/呎
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="C9" s="22" t="inlineStr">
+        <is>
+          <t>B | 278呎 (1房)
+$592万
+$21,277/呎
+(24年-09月)</t>
+        </is>
+      </c>
+      <c r="D9" s="22" t="inlineStr">
+        <is>
+          <t>C | 264呎 (1房)
+$579万
+$21,928/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="E9" s="22" t="inlineStr">
+        <is>
+          <t>D | 210呎 (开放式)
+$480万
+$22,833/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="F9" s="22" t="inlineStr">
+        <is>
+          <t>E | 209呎 (开放式)
+$479万
+$22,900/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="G9" s="22" t="inlineStr">
+        <is>
+          <t>F | 285呎 (1房)
+$860万
+$30,172/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="H9" s="22" t="inlineStr">
+        <is>
+          <t>G | 211呎 (开放式)
+$522万
+$24,749/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="I9" s="22" t="inlineStr">
+        <is>
+          <t>H | 388呎 (2房)
+$847万
+$21,820/呎
+(25年-02月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B10" s="20" t="inlineStr">
+        <is>
+          <t>A | 283呎 (1房)
+$942万
+$33,279/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="C10" s="22" t="inlineStr">
+        <is>
+          <t>B | 278呎 (1房)
+$664万
+$23,874/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="D10" s="22" t="inlineStr">
+        <is>
+          <t>C | 264呎 (1房)
+$572万
+$21,667/呎
+(24年-06月)</t>
+        </is>
+      </c>
+      <c r="E10" s="22" t="inlineStr">
+        <is>
+          <t>D | 210呎 (开放式)
+$456万
+$21,719/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="F10" s="22" t="inlineStr">
+        <is>
+          <t>E | 209呎 (开放式)
+$451万
+$21,579/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="G10" s="22" t="inlineStr">
+        <is>
+          <t>F | 285呎 (1房)
+$767万
+$26,926/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="H10" s="22" t="inlineStr">
+        <is>
+          <t>G | 211呎 (开放式)
+$641万
+$30,370/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="I10" s="22" t="inlineStr">
+        <is>
+          <t>H | 388呎 (2房)
+$875万
+$22,541/呎
+(26年-01月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="58" customHeight="1">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B11" s="22" t="inlineStr">
+        <is>
+          <t>A | 282呎 (1房)
+$577万
+$20,465/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="C11" s="22" t="inlineStr">
+        <is>
+          <t>B | 278呎 (1房)
+$578万
+$20,773/呎
+(24年-08月)</t>
+        </is>
+      </c>
+      <c r="D11" s="22" t="inlineStr">
+        <is>
+          <t>C | 264呎 (1房)
+$565万
+$21,413/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="E11" s="22" t="inlineStr">
+        <is>
+          <t>D | 210呎 (开放式)
+$451万
+$21,462/呎
+(25年-01月)</t>
+        </is>
+      </c>
+      <c r="F11" s="22" t="inlineStr">
+        <is>
+          <t>E | 209呎 (开放式)
+$446万
+$21,316/呎
+(24年-08月)</t>
+        </is>
+      </c>
+      <c r="G11" s="22" t="inlineStr">
+        <is>
+          <t>F | 285呎 (1房)
+$840万
+$29,488/呎
+(24年-03月)</t>
+        </is>
+      </c>
+      <c r="H11" s="22" t="inlineStr">
+        <is>
+          <t>G | 211呎 (开放式)
+$468万
+$22,194/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="I11" s="22" t="inlineStr">
+        <is>
+          <t>H | 388呎 (2房)
+$830万
+$21,387/呎
+(25年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B12" s="22" t="inlineStr">
+        <is>
+          <t>A | 282呎 (1房)
+$627万
+$22,245/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="C12" s="22" t="inlineStr">
+        <is>
+          <t>B | 278呎 (1房)
+$660万
+$23,730/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="D12" s="22" t="inlineStr">
+        <is>
+          <t>C | 264呎 (1房)
+$786万
+$29,754/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="E12" s="22" t="inlineStr">
+        <is>
+          <t>D | 210呎 (开放式)
+$445万
+$21,210/呎
+(25年-01月)</t>
+        </is>
+      </c>
+      <c r="F12" s="22" t="inlineStr">
+        <is>
+          <t>E | 209呎 (开放式)
+$474万
+$22,694/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="G12" s="22" t="inlineStr">
+        <is>
+          <t>F | 285呎 (1房)
+$786万
+$27,568/呎
+(22年-05月)</t>
+        </is>
+      </c>
+      <c r="H12" s="22" t="inlineStr">
+        <is>
+          <t>G | 211呎 (开放式)
+$672万
+$31,834/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="I12" s="22" t="inlineStr">
+        <is>
+          <t>H | 388呎 (2房)
+$821万
+$21,170/呎
+(25年-01月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B13" s="22" t="inlineStr">
+        <is>
+          <t>A | 282呎 (1房)
+$635万
+$22,511/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="C13" s="22" t="inlineStr">
+        <is>
+          <t>B | 278呎 (1房)
+$785万
+$28,248/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="D13" s="22" t="inlineStr">
+        <is>
+          <t>C | 264呎 (1房)
+$624万
+$23,652/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="E13" s="22" t="inlineStr">
+        <is>
+          <t>D | 210呎 (开放式)
+$474万
+$22,562/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="F13" s="22" t="inlineStr">
+        <is>
+          <t>E | 209呎 (开放式)
+$496万
+$23,718/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="G13" s="22" t="inlineStr">
+        <is>
+          <t>F | 285呎 (1房)
+$739万
+$25,923/呎
+(23年-01月)</t>
+        </is>
+      </c>
+      <c r="H13" s="22" t="inlineStr">
+        <is>
+          <t>G | 211呎 (开放式)
+$516万
+$24,455/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="I13" s="22" t="inlineStr">
+        <is>
+          <t>H | 388呎 (2房)
+$821万
+$21,170/呎
+(24年-08月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B14" s="22" t="inlineStr">
+        <is>
+          <t>A | 282呎 (1房)
+$596万
+$21,121/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="C14" s="22" t="inlineStr">
+        <is>
+          <t>B | 278呎 (1房)
+$563万
+$20,259/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="D14" s="22" t="inlineStr">
+        <is>
+          <t>C | 264呎 (1房)
+$551万
+$20,886/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="E14" s="22" t="inlineStr">
+        <is>
+          <t>D | 210呎 (开放式)
+$472万
+$22,495/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="F14" s="22" t="inlineStr">
+        <is>
+          <t>E | 209呎 (开放式)
+$471万
+$22,555/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="G14" s="22" t="inlineStr">
+        <is>
+          <t>F | 285呎 (1房)
+$730万
+$25,600/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="H14" s="22" t="inlineStr">
+        <is>
+          <t>G | 211呎 (开放式)
+$648万
+$30,735/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="I14" s="22" t="inlineStr">
+        <is>
+          <t>H | 388呎 (2房)
+$821万
+$21,170/呎
+(24年-07月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B15" s="22" t="inlineStr">
+        <is>
+          <t>A | 282呎 (1房)
+$594万
+$21,057/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="C15" s="22" t="inlineStr">
+        <is>
+          <t>B | 278呎 (1房)
+$559万
+$20,119/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="D15" s="22" t="inlineStr">
+        <is>
+          <t>C | 264呎 (1房)
+$548万
+$20,742/呎
+(24年-12月)</t>
+        </is>
+      </c>
+      <c r="E15" s="22" t="inlineStr">
+        <is>
+          <t>D | 210呎 (开放式)
+$430万
+$20,457/呎
+(25年-02月)</t>
+        </is>
+      </c>
+      <c r="F15" s="22" t="inlineStr">
+        <is>
+          <t>E | 209呎 (开放式)
+$423万
+$20,230/呎
+(24年-12月)</t>
+        </is>
+      </c>
+      <c r="G15" s="22" t="inlineStr">
+        <is>
+          <t>F | 285呎 (1房)
+$744万
+$26,105/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="H15" s="22" t="inlineStr">
+        <is>
+          <t>G | 211呎 (开放式)
+$648万
+$30,711/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="I15" s="22" t="inlineStr">
+        <is>
+          <t>H | 388呎 (2房)
+$930万
+$23,966/呎
+(23年-02月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B16" s="22" t="inlineStr">
+        <is>
+          <t>A | 282呎 (1房)
+$548万
+$19,418/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="C16" s="22" t="inlineStr">
+        <is>
+          <t>B | 278呎 (1房)
+$754万
+$27,104/呎
+(21年-10月)</t>
+        </is>
+      </c>
+      <c r="D16" s="24" t="inlineStr">
+        <is>
+          <t>C | 264呎 (1房)
+$839万
+$31,769/呎
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="E16" s="22" t="inlineStr">
+        <is>
+          <t>D | 210呎 (开放式)
+$428万
+$20,381/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="F16" s="22" t="inlineStr">
+        <is>
+          <t>E | 209呎 (开放式)
+$421万
+$20,148/呎
+(25年-01月)</t>
+        </is>
+      </c>
+      <c r="G16" s="22" t="inlineStr">
+        <is>
+          <t>F | 285呎 (1房)
+$783万
+$27,481/呎
+(21年-07月)</t>
+        </is>
+      </c>
+      <c r="H16" s="22" t="inlineStr">
+        <is>
+          <t>G | 211呎 (开放式)
+$488万
+$23,114/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="I16" s="22" t="inlineStr">
+        <is>
+          <t>H | 388呎 (2房)
+$991万
+$25,549/呎
+(21年-07月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="58" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B17" s="22" t="inlineStr">
+        <is>
+          <t>A | 282呎 (1房)
+$734万
+$26,025/呎
+(21年-07月)</t>
+        </is>
+      </c>
+      <c r="C17" s="22" t="inlineStr">
+        <is>
+          <t>B | 278呎 (1房)
+$735万
+$26,424/呎
+(21年-07月)</t>
+        </is>
+      </c>
+      <c r="D17" s="22" t="inlineStr">
+        <is>
+          <t>C | 264呎 (1房)
+$706万
+$26,723/呎
+(21年-07月)</t>
+        </is>
+      </c>
+      <c r="E17" s="22" t="inlineStr">
+        <is>
+          <t>D | 210呎 (开放式)
+$611万
+$29,090/呎
+(24年-03月)</t>
+        </is>
+      </c>
+      <c r="F17" s="22" t="inlineStr">
+        <is>
+          <t>E | 209呎 (开放式)
+$428万
+$20,478/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="G17" s="22" t="inlineStr">
+        <is>
+          <t>F | 285呎 (1房)
+$762万
+$26,737/呎
+(21年-07月)</t>
+        </is>
+      </c>
+      <c r="H17" s="22" t="inlineStr">
+        <is>
+          <t>G | 211呎 (开放式)
+$486万
+$23,047/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="I17" s="22" t="inlineStr">
+        <is>
+          <t>H | 388呎 (2房)
+$987万
+$25,443/呎
+(21年-07月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="58" customHeight="1">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B18" s="22" t="inlineStr">
+        <is>
+          <t>A | 282呎 (1房)
+$731万
+$25,918/呎
+(21年-07月)</t>
+        </is>
+      </c>
+      <c r="C18" s="22" t="inlineStr">
+        <is>
+          <t>B | 277呎 (1房)
+$732万
+$26,408/呎
+(21年-07月)</t>
+        </is>
+      </c>
+      <c r="D18" s="22" t="inlineStr">
+        <is>
+          <t>C | 264呎 (1房)
+$698万
+$26,458/呎
+(21年-07月)</t>
+        </is>
+      </c>
+      <c r="E18" s="22" t="inlineStr">
+        <is>
+          <t>D | 210呎 (开放式)
+$603万
+$28,700/呎
+(24年-03月)</t>
+        </is>
+      </c>
+      <c r="F18" s="22" t="inlineStr">
+        <is>
+          <t>E | 209呎 (开放式)
+$414万
+$19,794/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="G18" s="22" t="inlineStr">
+        <is>
+          <t>F | 285呎 (1房)
+$724万
+$25,418/呎
+(21年-07月)</t>
+        </is>
+      </c>
+      <c r="H18" s="22" t="inlineStr">
+        <is>
+          <t>G | 211呎 (开放式)
+$582万
+$27,607/呎
+(21年-07月)</t>
+        </is>
+      </c>
+      <c r="I18" s="22" t="inlineStr">
+        <is>
+          <t>H | 388呎 (2房)
+$934万
+$24,075/呎
+(21年-07月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="58" customHeight="1">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B19" s="22" t="inlineStr">
+        <is>
+          <t>A | 282呎 (1房)
+$530万
+$18,777/呎
+(24年-08月)</t>
+        </is>
+      </c>
+      <c r="C19" s="22" t="inlineStr">
+        <is>
+          <t>B | 277呎 (1房)
+$696万
+$25,108/呎
+(21年-07月)</t>
+        </is>
+      </c>
+      <c r="D19" s="22" t="inlineStr">
+        <is>
+          <t>C | 264呎 (1房)
+$659万
+$24,958/呎
+(21年-07月)</t>
+        </is>
+      </c>
+      <c r="E19" s="22" t="inlineStr">
+        <is>
+          <t>D | 210呎 (开放式)
+$578万
+$27,543/呎
+(21年-06月)</t>
+        </is>
+      </c>
+      <c r="F19" s="22" t="inlineStr">
+        <is>
+          <t>E | 209呎 (开放式)
+$553万
+$26,450/呎
+(21年-07月)</t>
+        </is>
+      </c>
+      <c r="G19" s="22" t="inlineStr">
+        <is>
+          <t>F | 285呎 (1房)
+$756万
+$26,523/呎
+(21年-07月)</t>
+        </is>
+      </c>
+      <c r="H19" s="22" t="inlineStr">
+        <is>
+          <t>G | 211呎 (开放式)
+$592万
+$28,047/呎
+(21年-07月)</t>
+        </is>
+      </c>
+      <c r="I19" s="22" t="inlineStr">
+        <is>
+          <t>H | 388呎 (2房)
+$970万
+$24,995/呎
+(22年-01月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="58" customHeight="1">
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B20" s="22" t="inlineStr">
+        <is>
+          <t>A | 282呎 (1房)
+$527万
+$18,699/呎
+(24年-08月)</t>
+        </is>
+      </c>
+      <c r="C20" s="22" t="inlineStr">
+        <is>
+          <t>B | 277呎 (1房)
+$719万
+$25,942/呎
+(21年-07月)</t>
+        </is>
+      </c>
+      <c r="D20" s="22" t="inlineStr">
+        <is>
+          <t>C | 264呎 (1房)
+$659万
+$24,951/呎
+(22年-03月)</t>
+        </is>
+      </c>
+      <c r="E20" s="22" t="inlineStr">
+        <is>
+          <t>D | 210呎 (开放式)
+$570万
+$27,162/呎
+(21年-07月)</t>
+        </is>
+      </c>
+      <c r="F20" s="22" t="inlineStr">
+        <is>
+          <t>E | 209呎 (开放式)
+$590万
+$28,225/呎
+(24年-03月)</t>
+        </is>
+      </c>
+      <c r="G20" s="22" t="inlineStr">
+        <is>
+          <t>F | 285呎 (1房)
+$712万
+$24,965/呎
+(21年-06月)</t>
+        </is>
+      </c>
+      <c r="H20" s="22" t="inlineStr">
+        <is>
+          <t>G | 211呎 (开放式)
+$557万
+$26,408/呎
+(21年-10月)</t>
+        </is>
+      </c>
+      <c r="I20" s="22" t="inlineStr">
+        <is>
+          <t>H | 388呎 (2房)
+$961万
+$24,771/呎
+(21年-07月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="58" customHeight="1">
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B21" s="22" t="inlineStr">
+        <is>
+          <t>A | 283呎 (1房)
+$689万
+$24,360/呎
+(22年-01月)</t>
+        </is>
+      </c>
+      <c r="C21" s="22" t="inlineStr">
+        <is>
+          <t>B | 278呎 (1房)
+$683万
+$24,576/呎
+(21年-07月)</t>
+        </is>
+      </c>
+      <c r="D21" s="22" t="inlineStr">
+        <is>
+          <t>C | 264呎 (1房)
+$610万
+$23,098/呎
+(21年-06月)</t>
+        </is>
+      </c>
+      <c r="E21" s="22" t="inlineStr">
+        <is>
+          <t>D | 210呎 (开放式)
+$581万
+$27,667/呎
+(24年-03月)</t>
+        </is>
+      </c>
+      <c r="F21" s="22" t="inlineStr">
+        <is>
+          <t>E | 209呎 (开放式)
+$543万
+$25,976/呎
+(21年-07月)</t>
+        </is>
+      </c>
+      <c r="G21" s="22" t="inlineStr">
+        <is>
+          <t>F | 285呎 (1房)
+$742万
+$26,049/呎
+(21年-07月)</t>
+        </is>
+      </c>
+      <c r="H21" s="22" t="inlineStr">
+        <is>
+          <t>G | 211呎 (开放式)
+$555万
+$26,303/呎
+(21年-07月)</t>
+        </is>
+      </c>
+      <c r="I21" s="22" t="inlineStr">
+        <is>
+          <t>H | 388呎 (2房)
+$957万
+$24,673/呎
+(21年-07月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="58" customHeight="1">
+      <c r="A22" s="19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B22" s="22" t="inlineStr">
+        <is>
+          <t>A | 283呎 (1房)
+$689万
+$24,336/呎
+(21年-07月)</t>
+        </is>
+      </c>
+      <c r="C22" s="22" t="inlineStr">
+        <is>
+          <t>B | 277呎 (1房)
+$701万
+$25,292/呎
+(21年-07月)</t>
+        </is>
+      </c>
+      <c r="D22" s="22" t="inlineStr">
+        <is>
+          <t>C | 264呎 (1房)
+$635万
+$24,045/呎
+(21年-07月)</t>
+        </is>
+      </c>
+      <c r="E22" s="22" t="inlineStr">
+        <is>
+          <t>D | 210呎 (开放式)
+$531万
+$25,281/呎
+(21年-07月)</t>
+        </is>
+      </c>
+      <c r="F22" s="22" t="inlineStr">
+        <is>
+          <t>E | 209呎 (开放式)
+$570万
+$27,249/呎
+(24年-03月)</t>
+        </is>
+      </c>
+      <c r="G22" s="22" t="inlineStr">
+        <is>
+          <t>F | 285呎 (1房)
+$708万
+$24,842/呎
+(21年-07月)</t>
+        </is>
+      </c>
+      <c r="H22" s="22" t="inlineStr">
+        <is>
+          <t>G | 211呎 (开放式)
+$581万
+$27,526/呎
+(21年-07月)</t>
+        </is>
+      </c>
+      <c r="I22" s="22" t="inlineStr">
+        <is>
+          <t>H | 388呎 (2房)
+$924万
+$23,807/呎
+(22年-08月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="58" customHeight="1">
+      <c r="A23" s="19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B23" s="22" t="inlineStr">
+        <is>
+          <t>A | 283呎 (1房)
+$716万
+$25,318/呎
+(21年-07月)</t>
+        </is>
+      </c>
+      <c r="C23" s="22" t="inlineStr">
+        <is>
+          <t>B | 277呎 (1房)
+$672万
+$24,260/呎
+(22年-02月)</t>
+        </is>
+      </c>
+      <c r="D23" s="22" t="inlineStr">
+        <is>
+          <t>C | 264呎 (1房)
+$660万
+$25,011/呎
+(21年-07月)</t>
+        </is>
+      </c>
+      <c r="E23" s="22" t="inlineStr">
+        <is>
+          <t>D | 209呎 (开放式)
+$531万
+$25,407/呎
+(22年-04月)</t>
+        </is>
+      </c>
+      <c r="F23" s="22" t="inlineStr">
+        <is>
+          <t>E | 209呎 (开放式)
+$553万
+$26,459/呎
+(21年-06月)</t>
+        </is>
+      </c>
+      <c r="G23" s="22" t="inlineStr">
+        <is>
+          <t>F | 286呎 (1房)
+$718万
+$25,108/呎
+(21年-07月)</t>
+        </is>
+      </c>
+      <c r="H23" s="24" t="inlineStr">
+        <is>
+          <t>G | 211呎 (开放式)
+$655万
+$31,057/呎
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="I23" s="22" t="inlineStr">
+        <is>
+          <t>H | 388呎 (2房)
+$950万
+$24,477/呎
+(21年-07月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="58" customHeight="1">
+      <c r="A24" s="19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B24" s="22" t="inlineStr">
+        <is>
+          <t>A | 282呎 (1房)
+$714万
+$25,305/呎
+(21年-07月)</t>
+        </is>
+      </c>
+      <c r="C24" s="22" t="inlineStr">
+        <is>
+          <t>B | 277呎 (1房)
+$693万
+$25,007/呎
+(21年-07月)</t>
+        </is>
+      </c>
+      <c r="D24" s="22" t="inlineStr">
+        <is>
+          <t>C | 264呎 (1房)
+$658万
+$24,905/呎
+(21年-07月)</t>
+        </is>
+      </c>
+      <c r="E24" s="22" t="inlineStr">
+        <is>
+          <t>D | 209呎 (开放式)
+$522万
+$24,995/呎
+(21年-07月)</t>
+        </is>
+      </c>
+      <c r="F24" s="22" t="inlineStr">
+        <is>
+          <t>E | 209呎 (开放式)
+$563万
+$26,938/呎
+(24年-03月)</t>
+        </is>
+      </c>
+      <c r="G24" s="22" t="inlineStr">
+        <is>
+          <t>F | 286呎 (1房)
+$703万
+$24,566/呎
+(21年-07月)</t>
+        </is>
+      </c>
+      <c r="H24" s="22" t="inlineStr">
+        <is>
+          <t>G | 211呎 (开放式)
+$548万
+$25,986/呎
+(21年-07月)</t>
+        </is>
+      </c>
+      <c r="I24" s="22" t="inlineStr">
+        <is>
+          <t>H | 388呎 (2房)
+$946万
+$24,376/呎
+(21年-07月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="58" customHeight="1">
+      <c r="A25" s="19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B25" s="22" t="inlineStr">
+        <is>
+          <t>A | 282呎 (1房)
+$711万
+$25,199/呎
+(21年-07月)</t>
+        </is>
+      </c>
+      <c r="C25" s="22" t="inlineStr">
+        <is>
+          <t>B | 277呎 (1房)
+$658万
+$23,765/呎
+(21年-07月)</t>
+        </is>
+      </c>
+      <c r="D25" s="22" t="inlineStr">
+        <is>
+          <t>C | 264呎 (1房)
+$655万
+$24,799/呎
+(21年-07月)</t>
+        </is>
+      </c>
+      <c r="E25" s="22" t="inlineStr">
+        <is>
+          <t>D | 209呎 (开放式)
+$524万
+$25,053/呎
+(21年-07月)</t>
+        </is>
+      </c>
+      <c r="F25" s="22" t="inlineStr">
+        <is>
+          <t>E | 209呎 (开放式)
+$523万
+$25,033/呎
+(21年-06月)</t>
+        </is>
+      </c>
+      <c r="G25" s="22" t="inlineStr">
+        <is>
+          <t>F | 286呎 (1房)
+$733万
+$25,633/呎
+(21年-07月)</t>
+        </is>
+      </c>
+      <c r="H25" s="22" t="inlineStr">
+        <is>
+          <t>G | 211呎 (开放式)
+$572万
+$27,109/呎
+(21年-07月)</t>
+        </is>
+      </c>
+      <c r="I25" s="22" t="inlineStr">
+        <is>
+          <t>H | 388呎 (2房)
+$899万
+$23,175/呎
+(21年-07月)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
 </file>
--- a/files/九龙-何文田-VAU Residence.xlsx
+++ b/files/九龙-何文田-VAU Residence.xlsx
@@ -662,7 +662,7 @@
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
   </cols>

--- a/files/九龙-何文田-VAU Residence.xlsx
+++ b/files/九龙-何文田-VAU Residence.xlsx
@@ -652,7 +652,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J167"/>
+  <dimension ref="A1:N167"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
@@ -665,6 +665,10 @@
     <col width="13" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="13" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1" ht="40" customHeight="1">
@@ -722,6 +726,26 @@
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
+          <t>最高折扣</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>折实总价 (港币)</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>折实呎价 (港币/呎)</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>付款办法</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
           <t>是否招标</t>
         </is>
       </c>
@@ -768,6 +792,22 @@
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K3" s="5" t="n">
+        <v>16966000</v>
+      </c>
+      <c r="L3" s="5" t="n">
+        <v>34000</v>
+      </c>
+      <c r="M3" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N3" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -814,6 +854,22 @@
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K4" s="5" t="n">
+        <v>13056000</v>
+      </c>
+      <c r="L4" s="5" t="n">
+        <v>34000</v>
+      </c>
+      <c r="M4" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N4" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -864,6 +920,26 @@
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L5" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M5" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N5" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -914,6 +990,26 @@
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K6" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L6" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M6" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N6" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -960,6 +1056,22 @@
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
+          <t>38%</t>
+        </is>
+      </c>
+      <c r="K7" s="5" t="n">
+        <v>5999740</v>
+      </c>
+      <c r="L7" s="5" t="n">
+        <v>22726</v>
+      </c>
+      <c r="M7" s="3" t="inlineStr">
+        <is>
+          <t>120天即供付款計劃</t>
+        </is>
+      </c>
+      <c r="N7" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1010,6 +1122,26 @@
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K8" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L8" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M8" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N8" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -1060,6 +1192,26 @@
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K9" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L9" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M9" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N9" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -1106,6 +1258,22 @@
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K10" s="5" t="n">
+        <v>12723000</v>
+      </c>
+      <c r="L10" s="5" t="n">
+        <v>25497</v>
+      </c>
+      <c r="M10" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N10" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1152,6 +1320,22 @@
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K11" s="5" t="n">
+        <v>10392000</v>
+      </c>
+      <c r="L11" s="5" t="n">
+        <v>27062</v>
+      </c>
+      <c r="M11" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N11" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1198,6 +1382,22 @@
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K12" s="5" t="n">
+        <v>6184000</v>
+      </c>
+      <c r="L12" s="5" t="n">
+        <v>29589</v>
+      </c>
+      <c r="M12" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N12" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1244,6 +1444,22 @@
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K13" s="5" t="n">
+        <v>5810000</v>
+      </c>
+      <c r="L13" s="5" t="n">
+        <v>27667</v>
+      </c>
+      <c r="M13" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N13" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1290,6 +1506,22 @@
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K14" s="5" t="n">
+        <v>7789000</v>
+      </c>
+      <c r="L14" s="5" t="n">
+        <v>29504</v>
+      </c>
+      <c r="M14" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N14" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1336,6 +1568,22 @@
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K15" s="5" t="n">
+        <v>7657000</v>
+      </c>
+      <c r="L15" s="5" t="n">
+        <v>27543</v>
+      </c>
+      <c r="M15" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N15" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1382,6 +1630,22 @@
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K16" s="5" t="n">
+        <v>7784000</v>
+      </c>
+      <c r="L16" s="5" t="n">
+        <v>27603</v>
+      </c>
+      <c r="M16" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N16" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1428,6 +1692,22 @@
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
+          <t>38%</t>
+        </is>
+      </c>
+      <c r="K17" s="5" t="n">
+        <v>10276500</v>
+      </c>
+      <c r="L17" s="5" t="n">
+        <v>20594</v>
+      </c>
+      <c r="M17" s="3" t="inlineStr">
+        <is>
+          <t>120天即供付款計劃</t>
+        </is>
+      </c>
+      <c r="N17" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1474,6 +1754,22 @@
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K18" s="5" t="n">
+        <v>11643000</v>
+      </c>
+      <c r="L18" s="5" t="n">
+        <v>30320</v>
+      </c>
+      <c r="M18" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N18" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1520,6 +1816,22 @@
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K19" s="5" t="n">
+        <v>4800000</v>
+      </c>
+      <c r="L19" s="5" t="n">
+        <v>22967</v>
+      </c>
+      <c r="M19" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N19" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1566,6 +1878,22 @@
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K20" s="5" t="n">
+        <v>5043000</v>
+      </c>
+      <c r="L20" s="5" t="n">
+        <v>24014</v>
+      </c>
+      <c r="M20" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N20" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1612,6 +1940,22 @@
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K21" s="5" t="n">
+        <v>7144000</v>
+      </c>
+      <c r="L21" s="5" t="n">
+        <v>27061</v>
+      </c>
+      <c r="M21" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N21" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1658,6 +2002,22 @@
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K22" s="5" t="n">
+        <v>6696000</v>
+      </c>
+      <c r="L22" s="5" t="n">
+        <v>24086</v>
+      </c>
+      <c r="M22" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N22" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1704,6 +2064,22 @@
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
+          <t>38%</t>
+        </is>
+      </c>
+      <c r="K23" s="5" t="n">
+        <v>6074760</v>
+      </c>
+      <c r="L23" s="5" t="n">
+        <v>21466</v>
+      </c>
+      <c r="M23" s="3" t="inlineStr">
+        <is>
+          <t>120天即供付款計劃</t>
+        </is>
+      </c>
+      <c r="N23" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1750,6 +2126,22 @@
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K24" s="5" t="n">
+        <v>8551000</v>
+      </c>
+      <c r="L24" s="5" t="n">
+        <v>22039</v>
+      </c>
+      <c r="M24" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N24" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1796,6 +2188,22 @@
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K25" s="5" t="n">
+        <v>4884000</v>
+      </c>
+      <c r="L25" s="5" t="n">
+        <v>23147</v>
+      </c>
+      <c r="M25" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N25" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1842,6 +2250,22 @@
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K26" s="5" t="n">
+        <v>8625000</v>
+      </c>
+      <c r="L26" s="5" t="n">
+        <v>30263</v>
+      </c>
+      <c r="M26" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N26" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1888,6 +2312,22 @@
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K27" s="5" t="n">
+        <v>6794000</v>
+      </c>
+      <c r="L27" s="5" t="n">
+        <v>32507</v>
+      </c>
+      <c r="M27" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N27" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1934,6 +2374,22 @@
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K28" s="5" t="n">
+        <v>4702000</v>
+      </c>
+      <c r="L28" s="5" t="n">
+        <v>22390</v>
+      </c>
+      <c r="M28" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N28" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1980,6 +2436,22 @@
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K29" s="5" t="n">
+        <v>5919000</v>
+      </c>
+      <c r="L29" s="5" t="n">
+        <v>22420</v>
+      </c>
+      <c r="M29" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N29" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2026,6 +2498,22 @@
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K30" s="5" t="n">
+        <v>6009000</v>
+      </c>
+      <c r="L30" s="5" t="n">
+        <v>21615</v>
+      </c>
+      <c r="M30" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N30" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2072,6 +2560,22 @@
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K31" s="5" t="n">
+        <v>6325000</v>
+      </c>
+      <c r="L31" s="5" t="n">
+        <v>22429</v>
+      </c>
+      <c r="M31" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N31" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2118,6 +2622,22 @@
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K32" s="5" t="n">
+        <v>8466000</v>
+      </c>
+      <c r="L32" s="5" t="n">
+        <v>21820</v>
+      </c>
+      <c r="M32" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N32" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2164,6 +2684,22 @@
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K33" s="5" t="n">
+        <v>5222000</v>
+      </c>
+      <c r="L33" s="5" t="n">
+        <v>24749</v>
+      </c>
+      <c r="M33" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N33" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2210,6 +2746,22 @@
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K34" s="5" t="n">
+        <v>8599000</v>
+      </c>
+      <c r="L34" s="5" t="n">
+        <v>30172</v>
+      </c>
+      <c r="M34" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N34" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2256,6 +2808,22 @@
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K35" s="5" t="n">
+        <v>4786000</v>
+      </c>
+      <c r="L35" s="5" t="n">
+        <v>22900</v>
+      </c>
+      <c r="M35" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N35" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2302,6 +2870,22 @@
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K36" s="5" t="n">
+        <v>4795000</v>
+      </c>
+      <c r="L36" s="5" t="n">
+        <v>22833</v>
+      </c>
+      <c r="M36" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N36" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2348,6 +2932,22 @@
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K37" s="5" t="n">
+        <v>5789000</v>
+      </c>
+      <c r="L37" s="5" t="n">
+        <v>21928</v>
+      </c>
+      <c r="M37" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N37" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2394,6 +2994,22 @@
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K38" s="5" t="n">
+        <v>5915000</v>
+      </c>
+      <c r="L38" s="5" t="n">
+        <v>21277</v>
+      </c>
+      <c r="M38" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N38" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2440,6 +3056,22 @@
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K39" s="5" t="n">
+        <v>5911000</v>
+      </c>
+      <c r="L39" s="5" t="n">
+        <v>20961</v>
+      </c>
+      <c r="M39" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N39" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2486,6 +3118,22 @@
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K40" s="5" t="n">
+        <v>8746000</v>
+      </c>
+      <c r="L40" s="5" t="n">
+        <v>22541</v>
+      </c>
+      <c r="M40" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N40" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2532,6 +3180,22 @@
       </c>
       <c r="J41" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K41" s="5" t="n">
+        <v>6408000</v>
+      </c>
+      <c r="L41" s="5" t="n">
+        <v>30370</v>
+      </c>
+      <c r="M41" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N41" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2578,6 +3242,22 @@
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K42" s="5" t="n">
+        <v>7674000</v>
+      </c>
+      <c r="L42" s="5" t="n">
+        <v>26926</v>
+      </c>
+      <c r="M42" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N42" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2624,6 +3304,22 @@
       </c>
       <c r="J43" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K43" s="5" t="n">
+        <v>4510000</v>
+      </c>
+      <c r="L43" s="5" t="n">
+        <v>21579</v>
+      </c>
+      <c r="M43" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N43" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2670,6 +3366,22 @@
       </c>
       <c r="J44" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K44" s="5" t="n">
+        <v>4561000</v>
+      </c>
+      <c r="L44" s="5" t="n">
+        <v>21719</v>
+      </c>
+      <c r="M44" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N44" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2716,6 +3428,22 @@
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K45" s="5" t="n">
+        <v>5720000</v>
+      </c>
+      <c r="L45" s="5" t="n">
+        <v>21667</v>
+      </c>
+      <c r="M45" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N45" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2762,6 +3490,22 @@
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K46" s="5" t="n">
+        <v>6637000</v>
+      </c>
+      <c r="L46" s="5" t="n">
+        <v>23874</v>
+      </c>
+      <c r="M46" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N46" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2808,6 +3552,22 @@
       </c>
       <c r="J47" s="3" t="inlineStr">
         <is>
+          <t>38%</t>
+        </is>
+      </c>
+      <c r="K47" s="5" t="n">
+        <v>5839160</v>
+      </c>
+      <c r="L47" s="5" t="n">
+        <v>20633</v>
+      </c>
+      <c r="M47" s="3" t="inlineStr">
+        <is>
+          <t>120天即供付款計劃</t>
+        </is>
+      </c>
+      <c r="N47" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2854,6 +3614,22 @@
       </c>
       <c r="J48" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K48" s="5" t="n">
+        <v>8298000</v>
+      </c>
+      <c r="L48" s="5" t="n">
+        <v>21387</v>
+      </c>
+      <c r="M48" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N48" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2900,6 +3676,22 @@
       </c>
       <c r="J49" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K49" s="5" t="n">
+        <v>4683000</v>
+      </c>
+      <c r="L49" s="5" t="n">
+        <v>22194</v>
+      </c>
+      <c r="M49" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N49" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2946,6 +3738,22 @@
       </c>
       <c r="J50" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K50" s="5" t="n">
+        <v>8404000</v>
+      </c>
+      <c r="L50" s="5" t="n">
+        <v>29488</v>
+      </c>
+      <c r="M50" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N50" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2992,6 +3800,22 @@
       </c>
       <c r="J51" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K51" s="5" t="n">
+        <v>4455000</v>
+      </c>
+      <c r="L51" s="5" t="n">
+        <v>21316</v>
+      </c>
+      <c r="M51" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N51" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3038,6 +3862,22 @@
       </c>
       <c r="J52" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K52" s="5" t="n">
+        <v>4507000</v>
+      </c>
+      <c r="L52" s="5" t="n">
+        <v>21462</v>
+      </c>
+      <c r="M52" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N52" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3084,6 +3924,22 @@
       </c>
       <c r="J53" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K53" s="5" t="n">
+        <v>5653000</v>
+      </c>
+      <c r="L53" s="5" t="n">
+        <v>21413</v>
+      </c>
+      <c r="M53" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N53" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3130,6 +3986,22 @@
       </c>
       <c r="J54" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K54" s="5" t="n">
+        <v>5775000</v>
+      </c>
+      <c r="L54" s="5" t="n">
+        <v>20773</v>
+      </c>
+      <c r="M54" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N54" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3176,6 +4048,22 @@
       </c>
       <c r="J55" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K55" s="5" t="n">
+        <v>5771000</v>
+      </c>
+      <c r="L55" s="5" t="n">
+        <v>20465</v>
+      </c>
+      <c r="M55" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N55" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3222,6 +4110,22 @@
       </c>
       <c r="J56" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K56" s="5" t="n">
+        <v>8214000</v>
+      </c>
+      <c r="L56" s="5" t="n">
+        <v>21170</v>
+      </c>
+      <c r="M56" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N56" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3268,6 +4172,22 @@
       </c>
       <c r="J57" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K57" s="5" t="n">
+        <v>6717000</v>
+      </c>
+      <c r="L57" s="5" t="n">
+        <v>31834</v>
+      </c>
+      <c r="M57" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N57" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3314,6 +4234,22 @@
       </c>
       <c r="J58" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K58" s="5" t="n">
+        <v>7857000</v>
+      </c>
+      <c r="L58" s="5" t="n">
+        <v>27568</v>
+      </c>
+      <c r="M58" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N58" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3360,6 +4296,22 @@
       </c>
       <c r="J59" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K59" s="5" t="n">
+        <v>4743000</v>
+      </c>
+      <c r="L59" s="5" t="n">
+        <v>22694</v>
+      </c>
+      <c r="M59" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N59" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3406,6 +4358,22 @@
       </c>
       <c r="J60" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K60" s="5" t="n">
+        <v>4454000</v>
+      </c>
+      <c r="L60" s="5" t="n">
+        <v>21210</v>
+      </c>
+      <c r="M60" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N60" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3452,6 +4420,22 @@
       </c>
       <c r="J61" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K61" s="5" t="n">
+        <v>7855000</v>
+      </c>
+      <c r="L61" s="5" t="n">
+        <v>29754</v>
+      </c>
+      <c r="M61" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N61" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3498,6 +4482,22 @@
       </c>
       <c r="J62" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K62" s="5" t="n">
+        <v>6597000</v>
+      </c>
+      <c r="L62" s="5" t="n">
+        <v>23730</v>
+      </c>
+      <c r="M62" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N62" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3544,6 +4544,22 @@
       </c>
       <c r="J63" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K63" s="5" t="n">
+        <v>6273000</v>
+      </c>
+      <c r="L63" s="5" t="n">
+        <v>22245</v>
+      </c>
+      <c r="M63" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N63" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3590,6 +4606,22 @@
       </c>
       <c r="J64" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K64" s="5" t="n">
+        <v>8214000</v>
+      </c>
+      <c r="L64" s="5" t="n">
+        <v>21170</v>
+      </c>
+      <c r="M64" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N64" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3636,6 +4668,22 @@
       </c>
       <c r="J65" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K65" s="5" t="n">
+        <v>5160000</v>
+      </c>
+      <c r="L65" s="5" t="n">
+        <v>24455</v>
+      </c>
+      <c r="M65" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N65" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3682,6 +4730,22 @@
       </c>
       <c r="J66" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K66" s="5" t="n">
+        <v>7388000</v>
+      </c>
+      <c r="L66" s="5" t="n">
+        <v>25923</v>
+      </c>
+      <c r="M66" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N66" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3728,6 +4792,22 @@
       </c>
       <c r="J67" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K67" s="5" t="n">
+        <v>4957000</v>
+      </c>
+      <c r="L67" s="5" t="n">
+        <v>23718</v>
+      </c>
+      <c r="M67" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N67" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3774,6 +4854,22 @@
       </c>
       <c r="J68" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K68" s="5" t="n">
+        <v>4738000</v>
+      </c>
+      <c r="L68" s="5" t="n">
+        <v>22562</v>
+      </c>
+      <c r="M68" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N68" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3820,6 +4916,22 @@
       </c>
       <c r="J69" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K69" s="5" t="n">
+        <v>6244000</v>
+      </c>
+      <c r="L69" s="5" t="n">
+        <v>23652</v>
+      </c>
+      <c r="M69" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N69" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3866,6 +4978,22 @@
       </c>
       <c r="J70" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K70" s="5" t="n">
+        <v>7853000</v>
+      </c>
+      <c r="L70" s="5" t="n">
+        <v>28248</v>
+      </c>
+      <c r="M70" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N70" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3912,6 +5040,22 @@
       </c>
       <c r="J71" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K71" s="5" t="n">
+        <v>6348000</v>
+      </c>
+      <c r="L71" s="5" t="n">
+        <v>22511</v>
+      </c>
+      <c r="M71" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N71" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3958,6 +5102,22 @@
       </c>
       <c r="J72" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K72" s="5" t="n">
+        <v>8214000</v>
+      </c>
+      <c r="L72" s="5" t="n">
+        <v>21170</v>
+      </c>
+      <c r="M72" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N72" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4004,6 +5164,22 @@
       </c>
       <c r="J73" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K73" s="5" t="n">
+        <v>6485000</v>
+      </c>
+      <c r="L73" s="5" t="n">
+        <v>30735</v>
+      </c>
+      <c r="M73" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N73" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4050,6 +5226,22 @@
       </c>
       <c r="J74" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K74" s="5" t="n">
+        <v>7296000</v>
+      </c>
+      <c r="L74" s="5" t="n">
+        <v>25600</v>
+      </c>
+      <c r="M74" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N74" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4096,6 +5288,22 @@
       </c>
       <c r="J75" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K75" s="5" t="n">
+        <v>4714000</v>
+      </c>
+      <c r="L75" s="5" t="n">
+        <v>22555</v>
+      </c>
+      <c r="M75" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N75" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4142,6 +5350,22 @@
       </c>
       <c r="J76" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K76" s="5" t="n">
+        <v>4724000</v>
+      </c>
+      <c r="L76" s="5" t="n">
+        <v>22495</v>
+      </c>
+      <c r="M76" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N76" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4188,6 +5412,22 @@
       </c>
       <c r="J77" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K77" s="5" t="n">
+        <v>5514000</v>
+      </c>
+      <c r="L77" s="5" t="n">
+        <v>20886</v>
+      </c>
+      <c r="M77" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N77" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4234,6 +5474,22 @@
       </c>
       <c r="J78" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K78" s="5" t="n">
+        <v>5632000</v>
+      </c>
+      <c r="L78" s="5" t="n">
+        <v>20259</v>
+      </c>
+      <c r="M78" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N78" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4280,6 +5536,22 @@
       </c>
       <c r="J79" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K79" s="5" t="n">
+        <v>5956000</v>
+      </c>
+      <c r="L79" s="5" t="n">
+        <v>21121</v>
+      </c>
+      <c r="M79" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N79" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4326,6 +5598,22 @@
       </c>
       <c r="J80" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K80" s="5" t="n">
+        <v>9299000</v>
+      </c>
+      <c r="L80" s="5" t="n">
+        <v>23966</v>
+      </c>
+      <c r="M80" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N80" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4372,6 +5660,22 @@
       </c>
       <c r="J81" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K81" s="5" t="n">
+        <v>6480000</v>
+      </c>
+      <c r="L81" s="5" t="n">
+        <v>30711</v>
+      </c>
+      <c r="M81" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N81" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4418,6 +5722,22 @@
       </c>
       <c r="J82" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K82" s="5" t="n">
+        <v>7440000</v>
+      </c>
+      <c r="L82" s="5" t="n">
+        <v>26105</v>
+      </c>
+      <c r="M82" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N82" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4464,6 +5784,22 @@
       </c>
       <c r="J83" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K83" s="5" t="n">
+        <v>4228000</v>
+      </c>
+      <c r="L83" s="5" t="n">
+        <v>20230</v>
+      </c>
+      <c r="M83" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N83" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4510,6 +5846,22 @@
       </c>
       <c r="J84" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K84" s="5" t="n">
+        <v>4296000</v>
+      </c>
+      <c r="L84" s="5" t="n">
+        <v>20457</v>
+      </c>
+      <c r="M84" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N84" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4556,6 +5908,22 @@
       </c>
       <c r="J85" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K85" s="5" t="n">
+        <v>5476000</v>
+      </c>
+      <c r="L85" s="5" t="n">
+        <v>20742</v>
+      </c>
+      <c r="M85" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N85" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4602,6 +5970,22 @@
       </c>
       <c r="J86" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K86" s="5" t="n">
+        <v>5593000</v>
+      </c>
+      <c r="L86" s="5" t="n">
+        <v>20119</v>
+      </c>
+      <c r="M86" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N86" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4648,6 +6032,22 @@
       </c>
       <c r="J87" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K87" s="5" t="n">
+        <v>5938000</v>
+      </c>
+      <c r="L87" s="5" t="n">
+        <v>21057</v>
+      </c>
+      <c r="M87" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N87" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4694,6 +6094,22 @@
       </c>
       <c r="J88" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K88" s="5" t="n">
+        <v>9913000</v>
+      </c>
+      <c r="L88" s="5" t="n">
+        <v>25549</v>
+      </c>
+      <c r="M88" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N88" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4740,6 +6156,22 @@
       </c>
       <c r="J89" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K89" s="5" t="n">
+        <v>4877000</v>
+      </c>
+      <c r="L89" s="5" t="n">
+        <v>23114</v>
+      </c>
+      <c r="M89" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N89" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4786,6 +6218,22 @@
       </c>
       <c r="J90" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K90" s="5" t="n">
+        <v>7832000</v>
+      </c>
+      <c r="L90" s="5" t="n">
+        <v>27481</v>
+      </c>
+      <c r="M90" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N90" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4832,6 +6280,22 @@
       </c>
       <c r="J91" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K91" s="5" t="n">
+        <v>4211000</v>
+      </c>
+      <c r="L91" s="5" t="n">
+        <v>20148</v>
+      </c>
+      <c r="M91" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N91" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4878,6 +6342,22 @@
       </c>
       <c r="J92" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K92" s="5" t="n">
+        <v>4280000</v>
+      </c>
+      <c r="L92" s="5" t="n">
+        <v>20381</v>
+      </c>
+      <c r="M92" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N92" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4924,6 +6404,22 @@
       </c>
       <c r="J93" s="3" t="inlineStr">
         <is>
+          <t>38%</t>
+        </is>
+      </c>
+      <c r="K93" s="5" t="n">
+        <v>5199940</v>
+      </c>
+      <c r="L93" s="5" t="n">
+        <v>19697</v>
+      </c>
+      <c r="M93" s="3" t="inlineStr">
+        <is>
+          <t>120天即供付款計劃</t>
+        </is>
+      </c>
+      <c r="N93" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4970,6 +6466,22 @@
       </c>
       <c r="J94" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K94" s="5" t="n">
+        <v>7535000</v>
+      </c>
+      <c r="L94" s="5" t="n">
+        <v>27104</v>
+      </c>
+      <c r="M94" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N94" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5016,6 +6528,22 @@
       </c>
       <c r="J95" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K95" s="5" t="n">
+        <v>5476000</v>
+      </c>
+      <c r="L95" s="5" t="n">
+        <v>19418</v>
+      </c>
+      <c r="M95" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N95" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5062,6 +6590,22 @@
       </c>
       <c r="J96" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K96" s="5" t="n">
+        <v>9872000</v>
+      </c>
+      <c r="L96" s="5" t="n">
+        <v>25443</v>
+      </c>
+      <c r="M96" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N96" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5108,6 +6652,22 @@
       </c>
       <c r="J97" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K97" s="5" t="n">
+        <v>4863000</v>
+      </c>
+      <c r="L97" s="5" t="n">
+        <v>23047</v>
+      </c>
+      <c r="M97" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N97" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5154,6 +6714,22 @@
       </c>
       <c r="J98" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K98" s="5" t="n">
+        <v>7620000</v>
+      </c>
+      <c r="L98" s="5" t="n">
+        <v>26737</v>
+      </c>
+      <c r="M98" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N98" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5200,6 +6776,22 @@
       </c>
       <c r="J99" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K99" s="5" t="n">
+        <v>4280000</v>
+      </c>
+      <c r="L99" s="5" t="n">
+        <v>20478</v>
+      </c>
+      <c r="M99" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N99" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5246,6 +6838,22 @@
       </c>
       <c r="J100" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K100" s="5" t="n">
+        <v>6109000</v>
+      </c>
+      <c r="L100" s="5" t="n">
+        <v>29090</v>
+      </c>
+      <c r="M100" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N100" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5292,6 +6900,22 @@
       </c>
       <c r="J101" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K101" s="5" t="n">
+        <v>7055000</v>
+      </c>
+      <c r="L101" s="5" t="n">
+        <v>26723</v>
+      </c>
+      <c r="M101" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N101" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5338,6 +6962,22 @@
       </c>
       <c r="J102" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K102" s="5" t="n">
+        <v>7346000</v>
+      </c>
+      <c r="L102" s="5" t="n">
+        <v>26424</v>
+      </c>
+      <c r="M102" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N102" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5384,6 +7024,22 @@
       </c>
       <c r="J103" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K103" s="5" t="n">
+        <v>7339000</v>
+      </c>
+      <c r="L103" s="5" t="n">
+        <v>26025</v>
+      </c>
+      <c r="M103" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N103" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5430,6 +7086,22 @@
       </c>
       <c r="J104" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K104" s="5" t="n">
+        <v>9341000</v>
+      </c>
+      <c r="L104" s="5" t="n">
+        <v>24075</v>
+      </c>
+      <c r="M104" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N104" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5476,6 +7148,22 @@
       </c>
       <c r="J105" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K105" s="5" t="n">
+        <v>5825000</v>
+      </c>
+      <c r="L105" s="5" t="n">
+        <v>27607</v>
+      </c>
+      <c r="M105" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N105" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5522,6 +7210,22 @@
       </c>
       <c r="J106" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K106" s="5" t="n">
+        <v>7244000</v>
+      </c>
+      <c r="L106" s="5" t="n">
+        <v>25418</v>
+      </c>
+      <c r="M106" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N106" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5568,6 +7272,22 @@
       </c>
       <c r="J107" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K107" s="5" t="n">
+        <v>4137000</v>
+      </c>
+      <c r="L107" s="5" t="n">
+        <v>19794</v>
+      </c>
+      <c r="M107" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N107" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5614,6 +7334,22 @@
       </c>
       <c r="J108" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K108" s="5" t="n">
+        <v>6027000</v>
+      </c>
+      <c r="L108" s="5" t="n">
+        <v>28700</v>
+      </c>
+      <c r="M108" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N108" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5660,6 +7396,22 @@
       </c>
       <c r="J109" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K109" s="5" t="n">
+        <v>6985000</v>
+      </c>
+      <c r="L109" s="5" t="n">
+        <v>26458</v>
+      </c>
+      <c r="M109" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N109" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5706,6 +7458,22 @@
       </c>
       <c r="J110" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K110" s="5" t="n">
+        <v>7315000</v>
+      </c>
+      <c r="L110" s="5" t="n">
+        <v>26408</v>
+      </c>
+      <c r="M110" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N110" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5752,6 +7520,22 @@
       </c>
       <c r="J111" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K111" s="5" t="n">
+        <v>7309000</v>
+      </c>
+      <c r="L111" s="5" t="n">
+        <v>25918</v>
+      </c>
+      <c r="M111" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N111" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5798,6 +7582,22 @@
       </c>
       <c r="J112" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K112" s="5" t="n">
+        <v>9698000</v>
+      </c>
+      <c r="L112" s="5" t="n">
+        <v>24995</v>
+      </c>
+      <c r="M112" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N112" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5844,6 +7644,22 @@
       </c>
       <c r="J113" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K113" s="5" t="n">
+        <v>5918000</v>
+      </c>
+      <c r="L113" s="5" t="n">
+        <v>28047</v>
+      </c>
+      <c r="M113" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N113" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5890,6 +7706,22 @@
       </c>
       <c r="J114" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K114" s="5" t="n">
+        <v>7559000</v>
+      </c>
+      <c r="L114" s="5" t="n">
+        <v>26523</v>
+      </c>
+      <c r="M114" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N114" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5936,6 +7768,22 @@
       </c>
       <c r="J115" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K115" s="5" t="n">
+        <v>5528000</v>
+      </c>
+      <c r="L115" s="5" t="n">
+        <v>26450</v>
+      </c>
+      <c r="M115" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N115" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5982,6 +7830,22 @@
       </c>
       <c r="J116" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K116" s="5" t="n">
+        <v>5784000</v>
+      </c>
+      <c r="L116" s="5" t="n">
+        <v>27543</v>
+      </c>
+      <c r="M116" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N116" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6028,6 +7892,22 @@
       </c>
       <c r="J117" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K117" s="5" t="n">
+        <v>6589000</v>
+      </c>
+      <c r="L117" s="5" t="n">
+        <v>24958</v>
+      </c>
+      <c r="M117" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N117" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6074,6 +7954,22 @@
       </c>
       <c r="J118" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K118" s="5" t="n">
+        <v>6955000</v>
+      </c>
+      <c r="L118" s="5" t="n">
+        <v>25108</v>
+      </c>
+      <c r="M118" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N118" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6120,6 +8016,22 @@
       </c>
       <c r="J119" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K119" s="5" t="n">
+        <v>5295000</v>
+      </c>
+      <c r="L119" s="5" t="n">
+        <v>18777</v>
+      </c>
+      <c r="M119" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N119" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6166,6 +8078,22 @@
       </c>
       <c r="J120" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K120" s="5" t="n">
+        <v>9611000</v>
+      </c>
+      <c r="L120" s="5" t="n">
+        <v>24771</v>
+      </c>
+      <c r="M120" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N120" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6212,6 +8140,22 @@
       </c>
       <c r="J121" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K121" s="5" t="n">
+        <v>5572000</v>
+      </c>
+      <c r="L121" s="5" t="n">
+        <v>26408</v>
+      </c>
+      <c r="M121" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N121" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6258,6 +8202,22 @@
       </c>
       <c r="J122" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K122" s="5" t="n">
+        <v>7115000</v>
+      </c>
+      <c r="L122" s="5" t="n">
+        <v>24965</v>
+      </c>
+      <c r="M122" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N122" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6304,6 +8264,22 @@
       </c>
       <c r="J123" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K123" s="5" t="n">
+        <v>5899000</v>
+      </c>
+      <c r="L123" s="5" t="n">
+        <v>28225</v>
+      </c>
+      <c r="M123" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N123" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6350,6 +8326,22 @@
       </c>
       <c r="J124" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K124" s="5" t="n">
+        <v>5704000</v>
+      </c>
+      <c r="L124" s="5" t="n">
+        <v>27162</v>
+      </c>
+      <c r="M124" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N124" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6396,6 +8388,22 @@
       </c>
       <c r="J125" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K125" s="5" t="n">
+        <v>6587000</v>
+      </c>
+      <c r="L125" s="5" t="n">
+        <v>24951</v>
+      </c>
+      <c r="M125" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N125" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6442,6 +8450,22 @@
       </c>
       <c r="J126" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K126" s="5" t="n">
+        <v>7186000</v>
+      </c>
+      <c r="L126" s="5" t="n">
+        <v>25942</v>
+      </c>
+      <c r="M126" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N126" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6488,6 +8512,22 @@
       </c>
       <c r="J127" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K127" s="5" t="n">
+        <v>5273000</v>
+      </c>
+      <c r="L127" s="5" t="n">
+        <v>18699</v>
+      </c>
+      <c r="M127" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N127" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6534,6 +8574,22 @@
       </c>
       <c r="J128" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K128" s="5" t="n">
+        <v>9573000</v>
+      </c>
+      <c r="L128" s="5" t="n">
+        <v>24673</v>
+      </c>
+      <c r="M128" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N128" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6580,6 +8636,22 @@
       </c>
       <c r="J129" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K129" s="5" t="n">
+        <v>5550000</v>
+      </c>
+      <c r="L129" s="5" t="n">
+        <v>26303</v>
+      </c>
+      <c r="M129" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N129" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6626,6 +8698,22 @@
       </c>
       <c r="J130" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K130" s="5" t="n">
+        <v>7424000</v>
+      </c>
+      <c r="L130" s="5" t="n">
+        <v>26049</v>
+      </c>
+      <c r="M130" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N130" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6672,6 +8760,22 @@
       </c>
       <c r="J131" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K131" s="5" t="n">
+        <v>5429000</v>
+      </c>
+      <c r="L131" s="5" t="n">
+        <v>25976</v>
+      </c>
+      <c r="M131" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N131" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6718,6 +8822,22 @@
       </c>
       <c r="J132" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K132" s="5" t="n">
+        <v>5810000</v>
+      </c>
+      <c r="L132" s="5" t="n">
+        <v>27667</v>
+      </c>
+      <c r="M132" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N132" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6764,6 +8884,22 @@
       </c>
       <c r="J133" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K133" s="5" t="n">
+        <v>6098000</v>
+      </c>
+      <c r="L133" s="5" t="n">
+        <v>23098</v>
+      </c>
+      <c r="M133" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N133" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6810,6 +8946,22 @@
       </c>
       <c r="J134" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K134" s="5" t="n">
+        <v>6832000</v>
+      </c>
+      <c r="L134" s="5" t="n">
+        <v>24576</v>
+      </c>
+      <c r="M134" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N134" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6856,6 +9008,22 @@
       </c>
       <c r="J135" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K135" s="5" t="n">
+        <v>6894000</v>
+      </c>
+      <c r="L135" s="5" t="n">
+        <v>24360</v>
+      </c>
+      <c r="M135" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N135" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6902,6 +9070,22 @@
       </c>
       <c r="J136" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K136" s="5" t="n">
+        <v>9237000</v>
+      </c>
+      <c r="L136" s="5" t="n">
+        <v>23807</v>
+      </c>
+      <c r="M136" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N136" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6948,6 +9132,22 @@
       </c>
       <c r="J137" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K137" s="5" t="n">
+        <v>5808000</v>
+      </c>
+      <c r="L137" s="5" t="n">
+        <v>27526</v>
+      </c>
+      <c r="M137" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N137" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6994,6 +9194,22 @@
       </c>
       <c r="J138" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K138" s="5" t="n">
+        <v>7080000</v>
+      </c>
+      <c r="L138" s="5" t="n">
+        <v>24842</v>
+      </c>
+      <c r="M138" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N138" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7040,6 +9256,22 @@
       </c>
       <c r="J139" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K139" s="5" t="n">
+        <v>5695000</v>
+      </c>
+      <c r="L139" s="5" t="n">
+        <v>27249</v>
+      </c>
+      <c r="M139" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N139" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7086,6 +9318,22 @@
       </c>
       <c r="J140" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K140" s="5" t="n">
+        <v>5309000</v>
+      </c>
+      <c r="L140" s="5" t="n">
+        <v>25281</v>
+      </c>
+      <c r="M140" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N140" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7132,6 +9380,22 @@
       </c>
       <c r="J141" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K141" s="5" t="n">
+        <v>6348000</v>
+      </c>
+      <c r="L141" s="5" t="n">
+        <v>24045</v>
+      </c>
+      <c r="M141" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N141" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7178,6 +9442,22 @@
       </c>
       <c r="J142" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K142" s="5" t="n">
+        <v>7006000</v>
+      </c>
+      <c r="L142" s="5" t="n">
+        <v>25292</v>
+      </c>
+      <c r="M142" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N142" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7224,6 +9504,22 @@
       </c>
       <c r="J143" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K143" s="5" t="n">
+        <v>6887000</v>
+      </c>
+      <c r="L143" s="5" t="n">
+        <v>24336</v>
+      </c>
+      <c r="M143" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N143" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7270,6 +9566,22 @@
       </c>
       <c r="J144" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K144" s="5" t="n">
+        <v>9497000</v>
+      </c>
+      <c r="L144" s="5" t="n">
+        <v>24477</v>
+      </c>
+      <c r="M144" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N144" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7316,6 +9628,22 @@
       </c>
       <c r="J145" s="3" t="inlineStr">
         <is>
+          <t>38%</t>
+        </is>
+      </c>
+      <c r="K145" s="5" t="n">
+        <v>4062860</v>
+      </c>
+      <c r="L145" s="5" t="n">
+        <v>19255</v>
+      </c>
+      <c r="M145" s="3" t="inlineStr">
+        <is>
+          <t>120天即供付款計劃</t>
+        </is>
+      </c>
+      <c r="N145" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7362,6 +9690,22 @@
       </c>
       <c r="J146" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K146" s="5" t="n">
+        <v>7181000</v>
+      </c>
+      <c r="L146" s="5" t="n">
+        <v>25108</v>
+      </c>
+      <c r="M146" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N146" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7408,6 +9752,22 @@
       </c>
       <c r="J147" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K147" s="5" t="n">
+        <v>5530000</v>
+      </c>
+      <c r="L147" s="5" t="n">
+        <v>26459</v>
+      </c>
+      <c r="M147" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N147" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7454,6 +9814,22 @@
       </c>
       <c r="J148" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K148" s="5" t="n">
+        <v>5310000</v>
+      </c>
+      <c r="L148" s="5" t="n">
+        <v>25407</v>
+      </c>
+      <c r="M148" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N148" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7500,6 +9876,22 @@
       </c>
       <c r="J149" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K149" s="5" t="n">
+        <v>6603000</v>
+      </c>
+      <c r="L149" s="5" t="n">
+        <v>25011</v>
+      </c>
+      <c r="M149" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N149" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7546,6 +9938,22 @@
       </c>
       <c r="J150" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K150" s="5" t="n">
+        <v>6720000</v>
+      </c>
+      <c r="L150" s="5" t="n">
+        <v>24260</v>
+      </c>
+      <c r="M150" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N150" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7592,6 +10000,22 @@
       </c>
       <c r="J151" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K151" s="5" t="n">
+        <v>7165000</v>
+      </c>
+      <c r="L151" s="5" t="n">
+        <v>25318</v>
+      </c>
+      <c r="M151" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N151" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7638,6 +10062,22 @@
       </c>
       <c r="J152" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K152" s="5" t="n">
+        <v>9458000</v>
+      </c>
+      <c r="L152" s="5" t="n">
+        <v>24376</v>
+      </c>
+      <c r="M152" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N152" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7684,6 +10124,22 @@
       </c>
       <c r="J153" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K153" s="5" t="n">
+        <v>5483000</v>
+      </c>
+      <c r="L153" s="5" t="n">
+        <v>25986</v>
+      </c>
+      <c r="M153" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N153" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7730,6 +10186,22 @@
       </c>
       <c r="J154" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K154" s="5" t="n">
+        <v>7026000</v>
+      </c>
+      <c r="L154" s="5" t="n">
+        <v>24566</v>
+      </c>
+      <c r="M154" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N154" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7776,6 +10248,22 @@
       </c>
       <c r="J155" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K155" s="5" t="n">
+        <v>5630000</v>
+      </c>
+      <c r="L155" s="5" t="n">
+        <v>26938</v>
+      </c>
+      <c r="M155" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N155" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7822,6 +10310,22 @@
       </c>
       <c r="J156" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K156" s="5" t="n">
+        <v>5224000</v>
+      </c>
+      <c r="L156" s="5" t="n">
+        <v>24995</v>
+      </c>
+      <c r="M156" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N156" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7868,6 +10372,22 @@
       </c>
       <c r="J157" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K157" s="5" t="n">
+        <v>6575000</v>
+      </c>
+      <c r="L157" s="5" t="n">
+        <v>24905</v>
+      </c>
+      <c r="M157" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N157" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7914,6 +10434,22 @@
       </c>
       <c r="J158" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K158" s="5" t="n">
+        <v>6927000</v>
+      </c>
+      <c r="L158" s="5" t="n">
+        <v>25007</v>
+      </c>
+      <c r="M158" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N158" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7960,6 +10496,22 @@
       </c>
       <c r="J159" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K159" s="5" t="n">
+        <v>7136000</v>
+      </c>
+      <c r="L159" s="5" t="n">
+        <v>25305</v>
+      </c>
+      <c r="M159" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N159" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8006,6 +10558,22 @@
       </c>
       <c r="J160" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K160" s="5" t="n">
+        <v>8992000</v>
+      </c>
+      <c r="L160" s="5" t="n">
+        <v>23175</v>
+      </c>
+      <c r="M160" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N160" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8052,6 +10620,22 @@
       </c>
       <c r="J161" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K161" s="5" t="n">
+        <v>5720000</v>
+      </c>
+      <c r="L161" s="5" t="n">
+        <v>27109</v>
+      </c>
+      <c r="M161" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N161" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8098,6 +10682,22 @@
       </c>
       <c r="J162" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K162" s="5" t="n">
+        <v>7331000</v>
+      </c>
+      <c r="L162" s="5" t="n">
+        <v>25633</v>
+      </c>
+      <c r="M162" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N162" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8144,6 +10744,22 @@
       </c>
       <c r="J163" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K163" s="5" t="n">
+        <v>5232000</v>
+      </c>
+      <c r="L163" s="5" t="n">
+        <v>25033</v>
+      </c>
+      <c r="M163" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N163" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8190,6 +10806,22 @@
       </c>
       <c r="J164" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K164" s="5" t="n">
+        <v>5236000</v>
+      </c>
+      <c r="L164" s="5" t="n">
+        <v>25053</v>
+      </c>
+      <c r="M164" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N164" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8236,6 +10868,22 @@
       </c>
       <c r="J165" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K165" s="5" t="n">
+        <v>6547000</v>
+      </c>
+      <c r="L165" s="5" t="n">
+        <v>24799</v>
+      </c>
+      <c r="M165" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N165" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8282,6 +10930,22 @@
       </c>
       <c r="J166" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K166" s="5" t="n">
+        <v>6583000</v>
+      </c>
+      <c r="L166" s="5" t="n">
+        <v>23765</v>
+      </c>
+      <c r="M166" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N166" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8328,13 +10992,29 @@
       </c>
       <c r="J167" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K167" s="5" t="n">
+        <v>7106000</v>
+      </c>
+      <c r="L167" s="5" t="n">
+        <v>25199</v>
+      </c>
+      <c r="M167" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N167" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A1:N1"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
@@ -8530,7 +11210,7 @@
           <t>F | 384呎 (2房)
 $1306万
 $34,000/呎
-(25年-07月)</t>
+(25年-07月-13日)</t>
         </is>
       </c>
       <c r="H5" s="22" t="inlineStr">
@@ -8538,7 +11218,7 @@
           <t>G | 499呎 (3房)
 $1697万
 $34,000/呎
-(25年-07月)</t>
+(25年-07月-14日)</t>
         </is>
       </c>
       <c r="I5" s="23" t="inlineStr"/>
@@ -8554,7 +11234,7 @@
           <t>A | 282呎 (1房)
 $778万
 $27,603/呎
-(26年-05月)</t>
+(26年-05月-04日)</t>
         </is>
       </c>
       <c r="C6" s="22" t="inlineStr">
@@ -8562,7 +11242,7 @@
           <t>B | 278呎 (1房)
 $766万
 $27,543/呎
-(26年-05月)</t>
+(26年-05月-04日)</t>
         </is>
       </c>
       <c r="D6" s="22" t="inlineStr">
@@ -8570,7 +11250,7 @@
           <t>C | 264呎 (1房)
 $779万
 $29,504/呎
-(26年-05月)</t>
+(26年-05月-19日)</t>
         </is>
       </c>
       <c r="E6" s="22" t="inlineStr">
@@ -8578,7 +11258,7 @@
           <t>D | 210呎 (开放式)
 $581万
 $27,667/呎
-(26年-04月)</t>
+(26年-04月-16日)</t>
         </is>
       </c>
       <c r="F6" s="22" t="inlineStr">
@@ -8586,7 +11266,7 @@
           <t>E | 209呎 (开放式)
 $618万
 $29,589/呎
-(26年-06月)</t>
+(26年-06月-01日)</t>
         </is>
       </c>
       <c r="G6" s="22" t="inlineStr">
@@ -8594,7 +11274,7 @@
           <t>F | 384呎 (2房)
 $1039万
 $27,062/呎
-(25年-07月)</t>
+(25年-07月-08日)</t>
         </is>
       </c>
       <c r="H6" s="22" t="inlineStr">
@@ -8602,7 +11282,7 @@
           <t>G | 499呎 (3房)
 $1272万
 $25,497/呎
-(25年-07月)</t>
+(25年-07月-10日)</t>
         </is>
       </c>
       <c r="I6" s="23" t="inlineStr"/>
@@ -8626,7 +11306,7 @@
           <t>B | 278呎 (1房)
 $670万
 $24,086/呎
-(26年-01月)</t>
+(26年-01月-08日)</t>
         </is>
       </c>
       <c r="D7" s="22" t="inlineStr">
@@ -8634,7 +11314,7 @@
           <t>C | 264呎 (1房)
 $714万
 $27,061/呎
-(26年-04月)</t>
+(26年-04月-26日)</t>
         </is>
       </c>
       <c r="E7" s="22" t="inlineStr">
@@ -8642,7 +11322,7 @@
           <t>D | 210呎 (开放式)
 $504万
 $24,014/呎
-(26年-02月)</t>
+(26年-02月-10日)</t>
         </is>
       </c>
       <c r="F7" s="22" t="inlineStr">
@@ -8650,7 +11330,7 @@
           <t>E | 209呎 (开放式)
 $480万
 $22,967/呎
-(25年-08月)</t>
+(25年-08月-24日)</t>
         </is>
       </c>
       <c r="G7" s="22" t="inlineStr">
@@ -8658,7 +11338,7 @@
           <t>F | 384呎 (2房)
 $1164万
 $30,320/呎
-(26年-04月)</t>
+(26年-04月-27日)</t>
         </is>
       </c>
       <c r="H7" s="20" t="inlineStr">
@@ -8682,7 +11362,7 @@
           <t>A | 282呎 (1房)
 $632万
 $22,429/呎
-(25年-11月)</t>
+(25年-11月-25日)</t>
         </is>
       </c>
       <c r="C8" s="22" t="inlineStr">
@@ -8690,7 +11370,7 @@
           <t>B | 278呎 (1房)
 $601万
 $21,615/呎
-(24年-10月)</t>
+(24年-10月-17日)</t>
         </is>
       </c>
       <c r="D8" s="22" t="inlineStr">
@@ -8698,7 +11378,7 @@
           <t>C | 264呎 (1房)
 $592万
 $22,420/呎
-(25年-05月)</t>
+(25年-05月-20日)</t>
         </is>
       </c>
       <c r="E8" s="22" t="inlineStr">
@@ -8706,7 +11386,7 @@
           <t>D | 210呎 (开放式)
 $470万
 $22,390/呎
-(25年-04月)</t>
+(25年-04月-15日)</t>
         </is>
       </c>
       <c r="F8" s="22" t="inlineStr">
@@ -8714,7 +11394,7 @@
           <t>E | 209呎 (开放式)
 $679万
 $32,507/呎
-(24年-04月)</t>
+(24年-04月-07日)</t>
         </is>
       </c>
       <c r="G8" s="22" t="inlineStr">
@@ -8722,7 +11402,7 @@
           <t>F | 285呎 (1房)
 $862万
 $30,263/呎
-(23年-05月)</t>
+(23年-05月-11日)</t>
         </is>
       </c>
       <c r="H8" s="22" t="inlineStr">
@@ -8730,7 +11410,7 @@
           <t>G | 211呎 (开放式)
 $488万
 $23,147/呎
-(25年-06月)</t>
+(25年-06月-15日)</t>
         </is>
       </c>
       <c r="I8" s="22" t="inlineStr">
@@ -8738,7 +11418,7 @@
           <t>H | 388呎 (2房)
 $855万
 $22,039/呎
-(24年-10月)</t>
+(24年-10月-31日)</t>
         </is>
       </c>
     </row>
@@ -8753,7 +11433,7 @@
           <t>A | 282呎 (1房)
 $591万
 $20,961/呎
-(25年-05月)</t>
+(25年-05月-22日)</t>
         </is>
       </c>
       <c r="C9" s="22" t="inlineStr">
@@ -8761,7 +11441,7 @@
           <t>B | 278呎 (1房)
 $592万
 $21,277/呎
-(24年-09月)</t>
+(24年-09月-02日)</t>
         </is>
       </c>
       <c r="D9" s="22" t="inlineStr">
@@ -8769,7 +11449,7 @@
           <t>C | 264呎 (1房)
 $579万
 $21,928/呎
-(25年-03月)</t>
+(25年-03月-30日)</t>
         </is>
       </c>
       <c r="E9" s="22" t="inlineStr">
@@ -8777,7 +11457,7 @@
           <t>D | 210呎 (开放式)
 $480万
 $22,833/呎
-(25年-07月)</t>
+(25年-07月-23日)</t>
         </is>
       </c>
       <c r="F9" s="22" t="inlineStr">
@@ -8785,7 +11465,7 @@
           <t>E | 209呎 (开放式)
 $479万
 $22,900/呎
-(25年-07月)</t>
+(25年-07月-23日)</t>
         </is>
       </c>
       <c r="G9" s="22" t="inlineStr">
@@ -8793,7 +11473,7 @@
           <t>F | 285呎 (1房)
 $860万
 $30,172/呎
-(24年-04月)</t>
+(24年-04月-09日)</t>
         </is>
       </c>
       <c r="H9" s="22" t="inlineStr">
@@ -8801,7 +11481,7 @@
           <t>G | 211呎 (开放式)
 $522万
 $24,749/呎
-(26年-02月)</t>
+(26年-02月-03日)</t>
         </is>
       </c>
       <c r="I9" s="22" t="inlineStr">
@@ -8809,7 +11489,7 @@
           <t>H | 388呎 (2房)
 $847万
 $21,820/呎
-(25年-02月)</t>
+(25年-02月-20日)</t>
         </is>
       </c>
     </row>
@@ -8832,7 +11512,7 @@
           <t>B | 278呎 (1房)
 $664万
 $23,874/呎
-(25年-11月)</t>
+(25年-11月-18日)</t>
         </is>
       </c>
       <c r="D10" s="22" t="inlineStr">
@@ -8840,7 +11520,7 @@
           <t>C | 264呎 (1房)
 $572万
 $21,667/呎
-(24年-06月)</t>
+(24年-06月-19日)</t>
         </is>
       </c>
       <c r="E10" s="22" t="inlineStr">
@@ -8848,7 +11528,7 @@
           <t>D | 210呎 (开放式)
 $456万
 $21,719/呎
-(25年-03月)</t>
+(25年-03月-19日)</t>
         </is>
       </c>
       <c r="F10" s="22" t="inlineStr">
@@ -8856,7 +11536,7 @@
           <t>E | 209呎 (开放式)
 $451万
 $21,579/呎
-(24年-11月)</t>
+(24年-11月-21日)</t>
         </is>
       </c>
       <c r="G10" s="22" t="inlineStr">
@@ -8864,7 +11544,7 @@
           <t>F | 285呎 (1房)
 $767万
 $26,926/呎
-(26年-02月)</t>
+(26年-02月-10日)</t>
         </is>
       </c>
       <c r="H10" s="22" t="inlineStr">
@@ -8872,7 +11552,7 @@
           <t>G | 211呎 (开放式)
 $641万
 $30,370/呎
-(26年-05月)</t>
+(26年-05月-28日)</t>
         </is>
       </c>
       <c r="I10" s="22" t="inlineStr">
@@ -8880,7 +11560,7 @@
           <t>H | 388呎 (2房)
 $875万
 $22,541/呎
-(26年-01月)</t>
+(26年-01月-25日)</t>
         </is>
       </c>
     </row>
@@ -8895,7 +11575,7 @@
           <t>A | 282呎 (1房)
 $577万
 $20,465/呎
-(25年-04月)</t>
+(25年-04月-08日)</t>
         </is>
       </c>
       <c r="C11" s="22" t="inlineStr">
@@ -8903,7 +11583,7 @@
           <t>B | 278呎 (1房)
 $578万
 $20,773/呎
-(24年-08月)</t>
+(24年-08月-25日)</t>
         </is>
       </c>
       <c r="D11" s="22" t="inlineStr">
@@ -8911,7 +11591,7 @@
           <t>C | 264呎 (1房)
 $565万
 $21,413/呎
-(24年-10月)</t>
+(24年-10月-22日)</t>
         </is>
       </c>
       <c r="E11" s="22" t="inlineStr">
@@ -8919,7 +11599,7 @@
           <t>D | 210呎 (开放式)
 $451万
 $21,462/呎
-(25年-01月)</t>
+(25年-01月-22日)</t>
         </is>
       </c>
       <c r="F11" s="22" t="inlineStr">
@@ -8927,7 +11607,7 @@
           <t>E | 209呎 (开放式)
 $446万
 $21,316/呎
-(24年-08月)</t>
+(24年-08月-07日)</t>
         </is>
       </c>
       <c r="G11" s="22" t="inlineStr">
@@ -8935,7 +11615,7 @@
           <t>F | 285呎 (1房)
 $840万
 $29,488/呎
-(24年-03月)</t>
+(24年-03月-27日)</t>
         </is>
       </c>
       <c r="H11" s="22" t="inlineStr">
@@ -8943,7 +11623,7 @@
           <t>G | 211呎 (开放式)
 $468万
 $22,194/呎
-(25年-04月)</t>
+(25年-04月-09日)</t>
         </is>
       </c>
       <c r="I11" s="22" t="inlineStr">
@@ -8951,7 +11631,7 @@
           <t>H | 388呎 (2房)
 $830万
 $21,387/呎
-(25年-04月)</t>
+(25年-04月-08日)</t>
         </is>
       </c>
     </row>
@@ -8966,7 +11646,7 @@
           <t>A | 282呎 (1房)
 $627万
 $22,245/呎
-(25年-11月)</t>
+(25年-11月-24日)</t>
         </is>
       </c>
       <c r="C12" s="22" t="inlineStr">
@@ -8974,7 +11654,7 @@
           <t>B | 278呎 (1房)
 $660万
 $23,730/呎
-(25年-11月)</t>
+(25年-11月-23日)</t>
         </is>
       </c>
       <c r="D12" s="22" t="inlineStr">
@@ -8982,7 +11662,7 @@
           <t>C | 264呎 (1房)
 $786万
 $29,754/呎
-(24年-04月)</t>
+(24年-04月-21日)</t>
         </is>
       </c>
       <c r="E12" s="22" t="inlineStr">
@@ -8990,7 +11670,7 @@
           <t>D | 210呎 (开放式)
 $445万
 $21,210/呎
-(25年-01月)</t>
+(25年-01月-12日)</t>
         </is>
       </c>
       <c r="F12" s="22" t="inlineStr">
@@ -8998,7 +11678,7 @@
           <t>E | 209呎 (开放式)
 $474万
 $22,694/呎
-(25年-07月)</t>
+(25年-07月-06日)</t>
         </is>
       </c>
       <c r="G12" s="22" t="inlineStr">
@@ -9006,7 +11686,7 @@
           <t>F | 285呎 (1房)
 $786万
 $27,568/呎
-(22年-05月)</t>
+(22年-05月-02日)</t>
         </is>
       </c>
       <c r="H12" s="22" t="inlineStr">
@@ -9014,7 +11694,7 @@
           <t>G | 211呎 (开放式)
 $672万
 $31,834/呎
-(24年-05月)</t>
+(24年-05月-09日)</t>
         </is>
       </c>
       <c r="I12" s="22" t="inlineStr">
@@ -9022,7 +11702,7 @@
           <t>H | 388呎 (2房)
 $821万
 $21,170/呎
-(25年-01月)</t>
+(25年-01月-23日)</t>
         </is>
       </c>
     </row>
@@ -9037,7 +11717,7 @@
           <t>A | 282呎 (1房)
 $635万
 $22,511/呎
-(26年-02月)</t>
+(26年-02月-23日)</t>
         </is>
       </c>
       <c r="C13" s="22" t="inlineStr">
@@ -9045,7 +11725,7 @@
           <t>B | 278呎 (1房)
 $785万
 $28,248/呎
-(26年-06月)</t>
+(26年-06月-14日)</t>
         </is>
       </c>
       <c r="D13" s="22" t="inlineStr">
@@ -9053,7 +11733,7 @@
           <t>C | 264呎 (1房)
 $624万
 $23,652/呎
-(25年-11月)</t>
+(25年-11月-16日)</t>
         </is>
       </c>
       <c r="E13" s="22" t="inlineStr">
@@ -9061,7 +11741,7 @@
           <t>D | 210呎 (开放式)
 $474万
 $22,562/呎
-(25年-07月)</t>
+(25年-07月-03日)</t>
         </is>
       </c>
       <c r="F13" s="22" t="inlineStr">
@@ -9069,7 +11749,7 @@
           <t>E | 209呎 (开放式)
 $496万
 $23,718/呎
-(26年-02月)</t>
+(26年-02月-08日)</t>
         </is>
       </c>
       <c r="G13" s="22" t="inlineStr">
@@ -9077,7 +11757,7 @@
           <t>F | 285呎 (1房)
 $739万
 $25,923/呎
-(23年-01月)</t>
+(23年-01月-10日)</t>
         </is>
       </c>
       <c r="H13" s="22" t="inlineStr">
@@ -9085,7 +11765,7 @@
           <t>G | 211呎 (开放式)
 $516万
 $24,455/呎
-(26年-01月)</t>
+(26年-01月-18日)</t>
         </is>
       </c>
       <c r="I13" s="22" t="inlineStr">
@@ -9093,7 +11773,7 @@
           <t>H | 388呎 (2房)
 $821万
 $21,170/呎
-(24年-08月)</t>
+(24年-08月-11日)</t>
         </is>
       </c>
     </row>
@@ -9108,7 +11788,7 @@
           <t>A | 282呎 (1房)
 $596万
 $21,121/呎
-(25年-06月)</t>
+(25年-06月-29日)</t>
         </is>
       </c>
       <c r="C14" s="22" t="inlineStr">
@@ -9116,7 +11796,7 @@
           <t>B | 278呎 (1房)
 $563万
 $20,259/呎
-(24年-11月)</t>
+(24年-11月-14日)</t>
         </is>
       </c>
       <c r="D14" s="22" t="inlineStr">
@@ -9124,7 +11804,7 @@
           <t>C | 264呎 (1房)
 $551万
 $20,886/呎
-(25年-03月)</t>
+(25年-03月-25日)</t>
         </is>
       </c>
       <c r="E14" s="22" t="inlineStr">
@@ -9132,7 +11812,7 @@
           <t>D | 210呎 (开放式)
 $472万
 $22,495/呎
-(25年-07月)</t>
+(25年-07月-01日)</t>
         </is>
       </c>
       <c r="F14" s="22" t="inlineStr">
@@ -9140,7 +11820,7 @@
           <t>E | 209呎 (开放式)
 $471万
 $22,555/呎
-(25年-07月)</t>
+(25年-07月-02日)</t>
         </is>
       </c>
       <c r="G14" s="22" t="inlineStr">
@@ -9148,7 +11828,7 @@
           <t>F | 285呎 (1房)
 $730万
 $25,600/呎
-(26年-02月)</t>
+(26年-02月-02日)</t>
         </is>
       </c>
       <c r="H14" s="22" t="inlineStr">
@@ -9156,7 +11836,7 @@
           <t>G | 211呎 (开放式)
 $648万
 $30,735/呎
-(24年-04月)</t>
+(24年-04月-09日)</t>
         </is>
       </c>
       <c r="I14" s="22" t="inlineStr">
@@ -9164,7 +11844,7 @@
           <t>H | 388呎 (2房)
 $821万
 $21,170/呎
-(24年-07月)</t>
+(24年-07月-18日)</t>
         </is>
       </c>
     </row>
@@ -9179,7 +11859,7 @@
           <t>A | 282呎 (1房)
 $594万
 $21,057/呎
-(25年-06月)</t>
+(25年-06月-26日)</t>
         </is>
       </c>
       <c r="C15" s="22" t="inlineStr">
@@ -9187,7 +11867,7 @@
           <t>B | 278呎 (1房)
 $559万
 $20,119/呎
-(24年-11月)</t>
+(24年-11月-21日)</t>
         </is>
       </c>
       <c r="D15" s="22" t="inlineStr">
@@ -9195,7 +11875,7 @@
           <t>C | 264呎 (1房)
 $548万
 $20,742/呎
-(24年-12月)</t>
+(24年-12月-05日)</t>
         </is>
       </c>
       <c r="E15" s="22" t="inlineStr">
@@ -9203,7 +11883,7 @@
           <t>D | 210呎 (开放式)
 $430万
 $20,457/呎
-(25年-02月)</t>
+(25年-02月-20日)</t>
         </is>
       </c>
       <c r="F15" s="22" t="inlineStr">
@@ -9211,7 +11891,7 @@
           <t>E | 209呎 (开放式)
 $423万
 $20,230/呎
-(24年-12月)</t>
+(24年-12月-16日)</t>
         </is>
       </c>
       <c r="G15" s="22" t="inlineStr">
@@ -9219,7 +11899,7 @@
           <t>F | 285呎 (1房)
 $744万
 $26,105/呎
-(26年-01月)</t>
+(26年-01月-29日)</t>
         </is>
       </c>
       <c r="H15" s="22" t="inlineStr">
@@ -9227,7 +11907,7 @@
           <t>G | 211呎 (开放式)
 $648万
 $30,711/呎
-(24年-04月)</t>
+(24年-04月-09日)</t>
         </is>
       </c>
       <c r="I15" s="22" t="inlineStr">
@@ -9235,7 +11915,7 @@
           <t>H | 388呎 (2房)
 $930万
 $23,966/呎
-(23年-02月)</t>
+(23年-02月-23日)</t>
         </is>
       </c>
     </row>
@@ -9250,7 +11930,7 @@
           <t>A | 282呎 (1房)
 $548万
 $19,418/呎
-(24年-10月)</t>
+(24年-10月-23日)</t>
         </is>
       </c>
       <c r="C16" s="22" t="inlineStr">
@@ -9258,7 +11938,7 @@
           <t>B | 278呎 (1房)
 $754万
 $27,104/呎
-(21年-10月)</t>
+(21年-10月-10日)</t>
         </is>
       </c>
       <c r="D16" s="24" t="inlineStr">
@@ -9274,7 +11954,7 @@
           <t>D | 210呎 (开放式)
 $428万
 $20,381/呎
-(24年-11月)</t>
+(24年-11月-17日)</t>
         </is>
       </c>
       <c r="F16" s="22" t="inlineStr">
@@ -9282,7 +11962,7 @@
           <t>E | 209呎 (开放式)
 $421万
 $20,148/呎
-(25年-01月)</t>
+(25年-01月-14日)</t>
         </is>
       </c>
       <c r="G16" s="22" t="inlineStr">
@@ -9290,7 +11970,7 @@
           <t>F | 285呎 (1房)
 $783万
 $27,481/呎
-(21年-07月)</t>
+(21年-07月-13日)</t>
         </is>
       </c>
       <c r="H16" s="22" t="inlineStr">
@@ -9298,7 +11978,7 @@
           <t>G | 211呎 (开放式)
 $488万
 $23,114/呎
-(25年-07月)</t>
+(25年-07月-23日)</t>
         </is>
       </c>
       <c r="I16" s="22" t="inlineStr">
@@ -9306,7 +11986,7 @@
           <t>H | 388呎 (2房)
 $991万
 $25,549/呎
-(21年-07月)</t>
+(21年-07月-06日)</t>
         </is>
       </c>
     </row>
@@ -9321,7 +12001,7 @@
           <t>A | 282呎 (1房)
 $734万
 $26,025/呎
-(21年-07月)</t>
+(21年-07月-08日)</t>
         </is>
       </c>
       <c r="C17" s="22" t="inlineStr">
@@ -9329,7 +12009,7 @@
           <t>B | 278呎 (1房)
 $735万
 $26,424/呎
-(21年-07月)</t>
+(21年-07月-14日)</t>
         </is>
       </c>
       <c r="D17" s="22" t="inlineStr">
@@ -9337,7 +12017,7 @@
           <t>C | 264呎 (1房)
 $706万
 $26,723/呎
-(21年-07月)</t>
+(21年-07月-04日)</t>
         </is>
       </c>
       <c r="E17" s="22" t="inlineStr">
@@ -9345,7 +12025,7 @@
           <t>D | 210呎 (开放式)
 $611万
 $29,090/呎
-(24年-03月)</t>
+(24年-03月-25日)</t>
         </is>
       </c>
       <c r="F17" s="22" t="inlineStr">
@@ -9353,7 +12033,7 @@
           <t>E | 209呎 (开放式)
 $428万
 $20,478/呎
-(25年-03月)</t>
+(25年-03月-19日)</t>
         </is>
       </c>
       <c r="G17" s="22" t="inlineStr">
@@ -9361,7 +12041,7 @@
           <t>F | 285呎 (1房)
 $762万
 $26,737/呎
-(21年-07月)</t>
+(21年-07月-12日)</t>
         </is>
       </c>
       <c r="H17" s="22" t="inlineStr">
@@ -9369,7 +12049,7 @@
           <t>G | 211呎 (开放式)
 $486万
 $23,047/呎
-(25年-07月)</t>
+(25年-07月-23日)</t>
         </is>
       </c>
       <c r="I17" s="22" t="inlineStr">
@@ -9377,7 +12057,7 @@
           <t>H | 388呎 (2房)
 $987万
 $25,443/呎
-(21年-07月)</t>
+(21年-07月-07日)</t>
         </is>
       </c>
     </row>
@@ -9392,7 +12072,7 @@
           <t>A | 282呎 (1房)
 $731万
 $25,918/呎
-(21年-07月)</t>
+(21年-07月-12日)</t>
         </is>
       </c>
       <c r="C18" s="22" t="inlineStr">
@@ -9400,7 +12080,7 @@
           <t>B | 277呎 (1房)
 $732万
 $26,408/呎
-(21年-07月)</t>
+(21年-07月-15日)</t>
         </is>
       </c>
       <c r="D18" s="22" t="inlineStr">
@@ -9408,7 +12088,7 @@
           <t>C | 264呎 (1房)
 $698万
 $26,458/呎
-(21年-07月)</t>
+(21年-07月-04日)</t>
         </is>
       </c>
       <c r="E18" s="22" t="inlineStr">
@@ -9416,7 +12096,7 @@
           <t>D | 210呎 (开放式)
 $603万
 $28,700/呎
-(24年-03月)</t>
+(24年-03月-24日)</t>
         </is>
       </c>
       <c r="F18" s="22" t="inlineStr">
@@ -9424,7 +12104,7 @@
           <t>E | 209呎 (开放式)
 $414万
 $19,794/呎
-(24年-10月)</t>
+(24年-10月-23日)</t>
         </is>
       </c>
       <c r="G18" s="22" t="inlineStr">
@@ -9432,7 +12112,7 @@
           <t>F | 285呎 (1房)
 $724万
 $25,418/呎
-(21年-07月)</t>
+(21年-07月-05日)</t>
         </is>
       </c>
       <c r="H18" s="22" t="inlineStr">
@@ -9440,7 +12120,7 @@
           <t>G | 211呎 (开放式)
 $582万
 $27,607/呎
-(21年-07月)</t>
+(21年-07月-08日)</t>
         </is>
       </c>
       <c r="I18" s="22" t="inlineStr">
@@ -9448,7 +12128,7 @@
           <t>H | 388呎 (2房)
 $934万
 $24,075/呎
-(21年-07月)</t>
+(21年-07月-08日)</t>
         </is>
       </c>
     </row>
@@ -9463,7 +12143,7 @@
           <t>A | 282呎 (1房)
 $530万
 $18,777/呎
-(24年-08月)</t>
+(24年-08月-29日)</t>
         </is>
       </c>
       <c r="C19" s="22" t="inlineStr">
@@ -9471,7 +12151,7 @@
           <t>B | 277呎 (1房)
 $696万
 $25,108/呎
-(21年-07月)</t>
+(21年-07月-08日)</t>
         </is>
       </c>
       <c r="D19" s="22" t="inlineStr">
@@ -9479,7 +12159,7 @@
           <t>C | 264呎 (1房)
 $659万
 $24,958/呎
-(21年-07月)</t>
+(21年-07月-04日)</t>
         </is>
       </c>
       <c r="E19" s="22" t="inlineStr">
@@ -9487,7 +12167,7 @@
           <t>D | 210呎 (开放式)
 $578万
 $27,543/呎
-(21年-06月)</t>
+(21年-06月-18日)</t>
         </is>
       </c>
       <c r="F19" s="22" t="inlineStr">
@@ -9495,7 +12175,7 @@
           <t>E | 209呎 (开放式)
 $553万
 $26,450/呎
-(21年-07月)</t>
+(21年-07月-05日)</t>
         </is>
       </c>
       <c r="G19" s="22" t="inlineStr">
@@ -9503,7 +12183,7 @@
           <t>F | 285呎 (1房)
 $756万
 $26,523/呎
-(21年-07月)</t>
+(21年-07月-08日)</t>
         </is>
       </c>
       <c r="H19" s="22" t="inlineStr">
@@ -9511,7 +12191,7 @@
           <t>G | 211呎 (开放式)
 $592万
 $28,047/呎
-(21年-07月)</t>
+(21年-07月-07日)</t>
         </is>
       </c>
       <c r="I19" s="22" t="inlineStr">
@@ -9519,7 +12199,7 @@
           <t>H | 388呎 (2房)
 $970万
 $24,995/呎
-(22年-01月)</t>
+(22年-01月-18日)</t>
         </is>
       </c>
     </row>
@@ -9534,7 +12214,7 @@
           <t>A | 282呎 (1房)
 $527万
 $18,699/呎
-(24年-08月)</t>
+(24年-08月-20日)</t>
         </is>
       </c>
       <c r="C20" s="22" t="inlineStr">
@@ -9542,7 +12222,7 @@
           <t>B | 277呎 (1房)
 $719万
 $25,942/呎
-(21年-07月)</t>
+(21年-07月-12日)</t>
         </is>
       </c>
       <c r="D20" s="22" t="inlineStr">
@@ -9550,7 +12230,7 @@
           <t>C | 264呎 (1房)
 $659万
 $24,951/呎
-(22年-03月)</t>
+(22年-03月-02日)</t>
         </is>
       </c>
       <c r="E20" s="22" t="inlineStr">
@@ -9558,7 +12238,7 @@
           <t>D | 210呎 (开放式)
 $570万
 $27,162/呎
-(21年-07月)</t>
+(21年-07月-20日)</t>
         </is>
       </c>
       <c r="F20" s="22" t="inlineStr">
@@ -9566,7 +12246,7 @@
           <t>E | 209呎 (开放式)
 $590万
 $28,225/呎
-(24年-03月)</t>
+(24年-03月-24日)</t>
         </is>
       </c>
       <c r="G20" s="22" t="inlineStr">
@@ -9574,7 +12254,7 @@
           <t>F | 285呎 (1房)
 $712万
 $24,965/呎
-(21年-06月)</t>
+(21年-06月-18日)</t>
         </is>
       </c>
       <c r="H20" s="22" t="inlineStr">
@@ -9582,7 +12262,7 @@
           <t>G | 211呎 (开放式)
 $557万
 $26,408/呎
-(21年-10月)</t>
+(21年-10月-07日)</t>
         </is>
       </c>
       <c r="I20" s="22" t="inlineStr">
@@ -9590,7 +12270,7 @@
           <t>H | 388呎 (2房)
 $961万
 $24,771/呎
-(21年-07月)</t>
+(21年-07月-12日)</t>
         </is>
       </c>
     </row>
@@ -9605,7 +12285,7 @@
           <t>A | 283呎 (1房)
 $689万
 $24,360/呎
-(22年-01月)</t>
+(22年-01月-26日)</t>
         </is>
       </c>
       <c r="C21" s="22" t="inlineStr">
@@ -9613,7 +12293,7 @@
           <t>B | 278呎 (1房)
 $683万
 $24,576/呎
-(21年-07月)</t>
+(21年-07月-07日)</t>
         </is>
       </c>
       <c r="D21" s="22" t="inlineStr">
@@ -9621,7 +12301,7 @@
           <t>C | 264呎 (1房)
 $610万
 $23,098/呎
-(21年-06月)</t>
+(21年-06月-18日)</t>
         </is>
       </c>
       <c r="E21" s="22" t="inlineStr">
@@ -9629,7 +12309,7 @@
           <t>D | 210呎 (开放式)
 $581万
 $27,667/呎
-(24年-03月)</t>
+(24年-03月-24日)</t>
         </is>
       </c>
       <c r="F21" s="22" t="inlineStr">
@@ -9637,7 +12317,7 @@
           <t>E | 209呎 (开放式)
 $543万
 $25,976/呎
-(21年-07月)</t>
+(21年-07月-15日)</t>
         </is>
       </c>
       <c r="G21" s="22" t="inlineStr">
@@ -9645,7 +12325,7 @@
           <t>F | 285呎 (1房)
 $742万
 $26,049/呎
-(21年-07月)</t>
+(21年-07月-08日)</t>
         </is>
       </c>
       <c r="H21" s="22" t="inlineStr">
@@ -9653,7 +12333,7 @@
           <t>G | 211呎 (开放式)
 $555万
 $26,303/呎
-(21年-07月)</t>
+(21年-07月-12日)</t>
         </is>
       </c>
       <c r="I21" s="22" t="inlineStr">
@@ -9661,7 +12341,7 @@
           <t>H | 388呎 (2房)
 $957万
 $24,673/呎
-(21年-07月)</t>
+(21年-07月-13日)</t>
         </is>
       </c>
     </row>
@@ -9676,7 +12356,7 @@
           <t>A | 283呎 (1房)
 $689万
 $24,336/呎
-(21年-07月)</t>
+(21年-07月-11日)</t>
         </is>
       </c>
       <c r="C22" s="22" t="inlineStr">
@@ -9684,7 +12364,7 @@
           <t>B | 277呎 (1房)
 $701万
 $25,292/呎
-(21年-07月)</t>
+(21年-07月-12日)</t>
         </is>
       </c>
       <c r="D22" s="22" t="inlineStr">
@@ -9692,7 +12372,7 @@
           <t>C | 264呎 (1房)
 $635万
 $24,045/呎
-(21年-07月)</t>
+(21年-07月-08日)</t>
         </is>
       </c>
       <c r="E22" s="22" t="inlineStr">
@@ -9700,7 +12380,7 @@
           <t>D | 210呎 (开放式)
 $531万
 $25,281/呎
-(21年-07月)</t>
+(21年-07月-08日)</t>
         </is>
       </c>
       <c r="F22" s="22" t="inlineStr">
@@ -9708,7 +12388,7 @@
           <t>E | 209呎 (开放式)
 $570万
 $27,249/呎
-(24年-03月)</t>
+(24年-03月-19日)</t>
         </is>
       </c>
       <c r="G22" s="22" t="inlineStr">
@@ -9716,7 +12396,7 @@
           <t>F | 285呎 (1房)
 $708万
 $24,842/呎
-(21年-07月)</t>
+(21年-07月-15日)</t>
         </is>
       </c>
       <c r="H22" s="22" t="inlineStr">
@@ -9724,7 +12404,7 @@
           <t>G | 211呎 (开放式)
 $581万
 $27,526/呎
-(21年-07月)</t>
+(21年-07月-04日)</t>
         </is>
       </c>
       <c r="I22" s="22" t="inlineStr">
@@ -9732,7 +12412,7 @@
           <t>H | 388呎 (2房)
 $924万
 $23,807/呎
-(22年-08月)</t>
+(22年-08月-08日)</t>
         </is>
       </c>
     </row>
@@ -9747,7 +12427,7 @@
           <t>A | 283呎 (1房)
 $716万
 $25,318/呎
-(21年-07月)</t>
+(21年-07月-11日)</t>
         </is>
       </c>
       <c r="C23" s="22" t="inlineStr">
@@ -9755,7 +12435,7 @@
           <t>B | 277呎 (1房)
 $672万
 $24,260/呎
-(22年-02月)</t>
+(22年-02月-13日)</t>
         </is>
       </c>
       <c r="D23" s="22" t="inlineStr">
@@ -9763,7 +12443,7 @@
           <t>C | 264呎 (1房)
 $660万
 $25,011/呎
-(21年-07月)</t>
+(21年-07月-07日)</t>
         </is>
       </c>
       <c r="E23" s="22" t="inlineStr">
@@ -9771,7 +12451,7 @@
           <t>D | 209呎 (开放式)
 $531万
 $25,407/呎
-(22年-04月)</t>
+(22年-04月-13日)</t>
         </is>
       </c>
       <c r="F23" s="22" t="inlineStr">
@@ -9779,7 +12459,7 @@
           <t>E | 209呎 (开放式)
 $553万
 $26,459/呎
-(21年-06月)</t>
+(21年-06月-18日)</t>
         </is>
       </c>
       <c r="G23" s="22" t="inlineStr">
@@ -9787,7 +12467,7 @@
           <t>F | 286呎 (1房)
 $718万
 $25,108/呎
-(21年-07月)</t>
+(21年-07月-05日)</t>
         </is>
       </c>
       <c r="H23" s="24" t="inlineStr">
@@ -9803,7 +12483,7 @@
           <t>H | 388呎 (2房)
 $950万
 $24,477/呎
-(21年-07月)</t>
+(21年-07月-13日)</t>
         </is>
       </c>
     </row>
@@ -9818,7 +12498,7 @@
           <t>A | 282呎 (1房)
 $714万
 $25,305/呎
-(21年-07月)</t>
+(21年-07月-11日)</t>
         </is>
       </c>
       <c r="C24" s="22" t="inlineStr">
@@ -9826,7 +12506,7 @@
           <t>B | 277呎 (1房)
 $693万
 $25,007/呎
-(21年-07月)</t>
+(21年-07月-13日)</t>
         </is>
       </c>
       <c r="D24" s="22" t="inlineStr">
@@ -9834,7 +12514,7 @@
           <t>C | 264呎 (1房)
 $658万
 $24,905/呎
-(21年-07月)</t>
+(21年-07月-07日)</t>
         </is>
       </c>
       <c r="E24" s="22" t="inlineStr">
@@ -9842,7 +12522,7 @@
           <t>D | 209呎 (开放式)
 $522万
 $24,995/呎
-(21年-07月)</t>
+(21年-07月-07日)</t>
         </is>
       </c>
       <c r="F24" s="22" t="inlineStr">
@@ -9850,7 +12530,7 @@
           <t>E | 209呎 (开放式)
 $563万
 $26,938/呎
-(24年-03月)</t>
+(24年-03月-21日)</t>
         </is>
       </c>
       <c r="G24" s="22" t="inlineStr">
@@ -9858,7 +12538,7 @@
           <t>F | 286呎 (1房)
 $703万
 $24,566/呎
-(21年-07月)</t>
+(21年-07月-05日)</t>
         </is>
       </c>
       <c r="H24" s="22" t="inlineStr">
@@ -9866,7 +12546,7 @@
           <t>G | 211呎 (开放式)
 $548万
 $25,986/呎
-(21年-07月)</t>
+(21年-07月-05日)</t>
         </is>
       </c>
       <c r="I24" s="22" t="inlineStr">
@@ -9874,7 +12554,7 @@
           <t>H | 388呎 (2房)
 $946万
 $24,376/呎
-(21年-07月)</t>
+(21年-07月-08日)</t>
         </is>
       </c>
     </row>
@@ -9889,7 +12569,7 @@
           <t>A | 282呎 (1房)
 $711万
 $25,199/呎
-(21年-07月)</t>
+(21年-07月-12日)</t>
         </is>
       </c>
       <c r="C25" s="22" t="inlineStr">
@@ -9897,7 +12577,7 @@
           <t>B | 277呎 (1房)
 $658万
 $23,765/呎
-(21年-07月)</t>
+(21年-07月-08日)</t>
         </is>
       </c>
       <c r="D25" s="22" t="inlineStr">
@@ -9905,7 +12585,7 @@
           <t>C | 264呎 (1房)
 $655万
 $24,799/呎
-(21年-07月)</t>
+(21年-07月-15日)</t>
         </is>
       </c>
       <c r="E25" s="22" t="inlineStr">
@@ -9913,7 +12593,7 @@
           <t>D | 209呎 (开放式)
 $524万
 $25,053/呎
-(21年-07月)</t>
+(21年-07月-08日)</t>
         </is>
       </c>
       <c r="F25" s="22" t="inlineStr">
@@ -9921,7 +12601,7 @@
           <t>E | 209呎 (开放式)
 $523万
 $25,033/呎
-(21年-06月)</t>
+(21年-06月-18日)</t>
         </is>
       </c>
       <c r="G25" s="22" t="inlineStr">
@@ -9929,7 +12609,7 @@
           <t>F | 286呎 (1房)
 $733万
 $25,633/呎
-(21年-07月)</t>
+(21年-07月-13日)</t>
         </is>
       </c>
       <c r="H25" s="22" t="inlineStr">
@@ -9937,7 +12617,7 @@
           <t>G | 211呎 (开放式)
 $572万
 $27,109/呎
-(21年-07月)</t>
+(21年-07月-11日)</t>
         </is>
       </c>
       <c r="I25" s="22" t="inlineStr">
@@ -9945,7 +12625,7 @@
           <t>H | 388呎 (2房)
 $899万
 $23,175/呎
-(21年-07月)</t>
+(21年-07月-12日)</t>
         </is>
       </c>
     </row>

--- a/files/九龙-何文田-VAU Residence.xlsx
+++ b/files/九龙-何文田-VAU Residence.xlsx
@@ -1056,14 +1056,14 @@
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t>38%</t>
+          <t>2%</t>
         </is>
       </c>
       <c r="K7" s="5" t="n">
-        <v>5999740</v>
+        <v>9483460</v>
       </c>
       <c r="L7" s="5" t="n">
-        <v>22726</v>
+        <v>35922</v>
       </c>
       <c r="M7" s="3" t="inlineStr">
         <is>
@@ -1692,14 +1692,14 @@
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t>38%</t>
+          <t>9%</t>
         </is>
       </c>
       <c r="K17" s="5" t="n">
-        <v>10276500</v>
+        <v>15083250</v>
       </c>
       <c r="L17" s="5" t="n">
-        <v>20594</v>
+        <v>30227</v>
       </c>
       <c r="M17" s="3" t="inlineStr">
         <is>
@@ -2064,14 +2064,14 @@
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
-          <t>38%</t>
+          <t>17%</t>
         </is>
       </c>
       <c r="K23" s="5" t="n">
-        <v>6074760</v>
+        <v>8132340</v>
       </c>
       <c r="L23" s="5" t="n">
-        <v>21466</v>
+        <v>28736</v>
       </c>
       <c r="M23" s="3" t="inlineStr">
         <is>
@@ -3552,14 +3552,14 @@
       </c>
       <c r="J47" s="3" t="inlineStr">
         <is>
-          <t>38%</t>
+          <t>15%</t>
         </is>
       </c>
       <c r="K47" s="5" t="n">
-        <v>5839160</v>
+        <v>8005300</v>
       </c>
       <c r="L47" s="5" t="n">
-        <v>20633</v>
+        <v>28287</v>
       </c>
       <c r="M47" s="3" t="inlineStr">
         <is>
@@ -6404,14 +6404,14 @@
       </c>
       <c r="J93" s="3" t="inlineStr">
         <is>
-          <t>38%</t>
+          <t>33%</t>
         </is>
       </c>
       <c r="K93" s="5" t="n">
-        <v>5199940</v>
+        <v>5619290</v>
       </c>
       <c r="L93" s="5" t="n">
-        <v>19697</v>
+        <v>21285</v>
       </c>
       <c r="M93" s="3" t="inlineStr">
         <is>
@@ -9628,14 +9628,14 @@
       </c>
       <c r="J145" s="3" t="inlineStr">
         <is>
-          <t>38%</t>
+          <t>10%</t>
         </is>
       </c>
       <c r="K145" s="5" t="n">
-        <v>4062860</v>
+        <v>5897700</v>
       </c>
       <c r="L145" s="5" t="n">
-        <v>19255</v>
+        <v>27951</v>
       </c>
       <c r="M145" s="3" t="inlineStr">
         <is>

--- a/files/九龙-何文田-VAU Residence.xlsx
+++ b/files/九龙-何文田-VAU Residence.xlsx
@@ -11210,7 +11210,7 @@
           <t>F | 384呎 (2房)
 $1306万
 $34,000/呎
-(25年-07月-13日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="H5" s="22" t="inlineStr">
@@ -11218,7 +11218,7 @@
           <t>G | 499呎 (3房)
 $1697万
 $34,000/呎
-(25年-07月-14日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="I5" s="23" t="inlineStr"/>
@@ -11234,7 +11234,7 @@
           <t>A | 282呎 (1房)
 $778万
 $27,603/呎
-(26年-05月-04日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="C6" s="22" t="inlineStr">
@@ -11242,7 +11242,7 @@
           <t>B | 278呎 (1房)
 $766万
 $27,543/呎
-(26年-05月-04日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="D6" s="22" t="inlineStr">
@@ -11250,7 +11250,7 @@
           <t>C | 264呎 (1房)
 $779万
 $29,504/呎
-(26年-05月-19日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="E6" s="22" t="inlineStr">
@@ -11258,7 +11258,7 @@
           <t>D | 210呎 (开放式)
 $581万
 $27,667/呎
-(26年-04月-16日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="F6" s="22" t="inlineStr">
@@ -11266,7 +11266,7 @@
           <t>E | 209呎 (开放式)
 $618万
 $29,589/呎
-(26年-06月-01日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="G6" s="22" t="inlineStr">
@@ -11274,7 +11274,7 @@
           <t>F | 384呎 (2房)
 $1039万
 $27,062/呎
-(25年-07月-08日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="H6" s="22" t="inlineStr">
@@ -11282,7 +11282,7 @@
           <t>G | 499呎 (3房)
 $1272万
 $25,497/呎
-(25年-07月-10日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="I6" s="23" t="inlineStr"/>
@@ -11306,7 +11306,7 @@
           <t>B | 278呎 (1房)
 $670万
 $24,086/呎
-(26年-01月-08日)</t>
+(26年-01月)</t>
         </is>
       </c>
       <c r="D7" s="22" t="inlineStr">
@@ -11314,7 +11314,7 @@
           <t>C | 264呎 (1房)
 $714万
 $27,061/呎
-(26年-04月-26日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="E7" s="22" t="inlineStr">
@@ -11322,7 +11322,7 @@
           <t>D | 210呎 (开放式)
 $504万
 $24,014/呎
-(26年-02月-10日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="F7" s="22" t="inlineStr">
@@ -11330,7 +11330,7 @@
           <t>E | 209呎 (开放式)
 $480万
 $22,967/呎
-(25年-08月-24日)</t>
+(25年-08月)</t>
         </is>
       </c>
       <c r="G7" s="22" t="inlineStr">
@@ -11338,7 +11338,7 @@
           <t>F | 384呎 (2房)
 $1164万
 $30,320/呎
-(26年-04月-27日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="H7" s="20" t="inlineStr">
@@ -11362,7 +11362,7 @@
           <t>A | 282呎 (1房)
 $632万
 $22,429/呎
-(25年-11月-25日)</t>
+(25年-11月)</t>
         </is>
       </c>
       <c r="C8" s="22" t="inlineStr">
@@ -11370,7 +11370,7 @@
           <t>B | 278呎 (1房)
 $601万
 $21,615/呎
-(24年-10月-17日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="D8" s="22" t="inlineStr">
@@ -11378,7 +11378,7 @@
           <t>C | 264呎 (1房)
 $592万
 $22,420/呎
-(25年-05月-20日)</t>
+(25年-05月)</t>
         </is>
       </c>
       <c r="E8" s="22" t="inlineStr">
@@ -11386,7 +11386,7 @@
           <t>D | 210呎 (开放式)
 $470万
 $22,390/呎
-(25年-04月-15日)</t>
+(25年-04月)</t>
         </is>
       </c>
       <c r="F8" s="22" t="inlineStr">
@@ -11394,7 +11394,7 @@
           <t>E | 209呎 (开放式)
 $679万
 $32,507/呎
-(24年-04月-07日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="G8" s="22" t="inlineStr">
@@ -11402,7 +11402,7 @@
           <t>F | 285呎 (1房)
 $862万
 $30,263/呎
-(23年-05月-11日)</t>
+(23年-05月)</t>
         </is>
       </c>
       <c r="H8" s="22" t="inlineStr">
@@ -11410,7 +11410,7 @@
           <t>G | 211呎 (开放式)
 $488万
 $23,147/呎
-(25年-06月-15日)</t>
+(25年-06月)</t>
         </is>
       </c>
       <c r="I8" s="22" t="inlineStr">
@@ -11418,7 +11418,7 @@
           <t>H | 388呎 (2房)
 $855万
 $22,039/呎
-(24年-10月-31日)</t>
+(24年-10月)</t>
         </is>
       </c>
     </row>
@@ -11433,7 +11433,7 @@
           <t>A | 282呎 (1房)
 $591万
 $20,961/呎
-(25年-05月-22日)</t>
+(25年-05月)</t>
         </is>
       </c>
       <c r="C9" s="22" t="inlineStr">
@@ -11441,7 +11441,7 @@
           <t>B | 278呎 (1房)
 $592万
 $21,277/呎
-(24年-09月-02日)</t>
+(24年-09月)</t>
         </is>
       </c>
       <c r="D9" s="22" t="inlineStr">
@@ -11449,7 +11449,7 @@
           <t>C | 264呎 (1房)
 $579万
 $21,928/呎
-(25年-03月-30日)</t>
+(25年-03月)</t>
         </is>
       </c>
       <c r="E9" s="22" t="inlineStr">
@@ -11457,7 +11457,7 @@
           <t>D | 210呎 (开放式)
 $480万
 $22,833/呎
-(25年-07月-23日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="F9" s="22" t="inlineStr">
@@ -11465,7 +11465,7 @@
           <t>E | 209呎 (开放式)
 $479万
 $22,900/呎
-(25年-07月-23日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="G9" s="22" t="inlineStr">
@@ -11473,7 +11473,7 @@
           <t>F | 285呎 (1房)
 $860万
 $30,172/呎
-(24年-04月-09日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="H9" s="22" t="inlineStr">
@@ -11481,7 +11481,7 @@
           <t>G | 211呎 (开放式)
 $522万
 $24,749/呎
-(26年-02月-03日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="I9" s="22" t="inlineStr">
@@ -11489,7 +11489,7 @@
           <t>H | 388呎 (2房)
 $847万
 $21,820/呎
-(25年-02月-20日)</t>
+(25年-02月)</t>
         </is>
       </c>
     </row>
@@ -11512,7 +11512,7 @@
           <t>B | 278呎 (1房)
 $664万
 $23,874/呎
-(25年-11月-18日)</t>
+(25年-11月)</t>
         </is>
       </c>
       <c r="D10" s="22" t="inlineStr">
@@ -11520,7 +11520,7 @@
           <t>C | 264呎 (1房)
 $572万
 $21,667/呎
-(24年-06月-19日)</t>
+(24年-06月)</t>
         </is>
       </c>
       <c r="E10" s="22" t="inlineStr">
@@ -11528,7 +11528,7 @@
           <t>D | 210呎 (开放式)
 $456万
 $21,719/呎
-(25年-03月-19日)</t>
+(25年-03月)</t>
         </is>
       </c>
       <c r="F10" s="22" t="inlineStr">
@@ -11536,7 +11536,7 @@
           <t>E | 209呎 (开放式)
 $451万
 $21,579/呎
-(24年-11月-21日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="G10" s="22" t="inlineStr">
@@ -11544,7 +11544,7 @@
           <t>F | 285呎 (1房)
 $767万
 $26,926/呎
-(26年-02月-10日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="H10" s="22" t="inlineStr">
@@ -11552,7 +11552,7 @@
           <t>G | 211呎 (开放式)
 $641万
 $30,370/呎
-(26年-05月-28日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="I10" s="22" t="inlineStr">
@@ -11560,7 +11560,7 @@
           <t>H | 388呎 (2房)
 $875万
 $22,541/呎
-(26年-01月-25日)</t>
+(26年-01月)</t>
         </is>
       </c>
     </row>
@@ -11575,7 +11575,7 @@
           <t>A | 282呎 (1房)
 $577万
 $20,465/呎
-(25年-04月-08日)</t>
+(25年-04月)</t>
         </is>
       </c>
       <c r="C11" s="22" t="inlineStr">
@@ -11583,7 +11583,7 @@
           <t>B | 278呎 (1房)
 $578万
 $20,773/呎
-(24年-08月-25日)</t>
+(24年-08月)</t>
         </is>
       </c>
       <c r="D11" s="22" t="inlineStr">
@@ -11591,7 +11591,7 @@
           <t>C | 264呎 (1房)
 $565万
 $21,413/呎
-(24年-10月-22日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="E11" s="22" t="inlineStr">
@@ -11599,7 +11599,7 @@
           <t>D | 210呎 (开放式)
 $451万
 $21,462/呎
-(25年-01月-22日)</t>
+(25年-01月)</t>
         </is>
       </c>
       <c r="F11" s="22" t="inlineStr">
@@ -11607,7 +11607,7 @@
           <t>E | 209呎 (开放式)
 $446万
 $21,316/呎
-(24年-08月-07日)</t>
+(24年-08月)</t>
         </is>
       </c>
       <c r="G11" s="22" t="inlineStr">
@@ -11615,7 +11615,7 @@
           <t>F | 285呎 (1房)
 $840万
 $29,488/呎
-(24年-03月-27日)</t>
+(24年-03月)</t>
         </is>
       </c>
       <c r="H11" s="22" t="inlineStr">
@@ -11623,7 +11623,7 @@
           <t>G | 211呎 (开放式)
 $468万
 $22,194/呎
-(25年-04月-09日)</t>
+(25年-04月)</t>
         </is>
       </c>
       <c r="I11" s="22" t="inlineStr">
@@ -11631,7 +11631,7 @@
           <t>H | 388呎 (2房)
 $830万
 $21,387/呎
-(25年-04月-08日)</t>
+(25年-04月)</t>
         </is>
       </c>
     </row>
@@ -11646,7 +11646,7 @@
           <t>A | 282呎 (1房)
 $627万
 $22,245/呎
-(25年-11月-24日)</t>
+(25年-11月)</t>
         </is>
       </c>
       <c r="C12" s="22" t="inlineStr">
@@ -11654,7 +11654,7 @@
           <t>B | 278呎 (1房)
 $660万
 $23,730/呎
-(25年-11月-23日)</t>
+(25年-11月)</t>
         </is>
       </c>
       <c r="D12" s="22" t="inlineStr">
@@ -11662,7 +11662,7 @@
           <t>C | 264呎 (1房)
 $786万
 $29,754/呎
-(24年-04月-21日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="E12" s="22" t="inlineStr">
@@ -11670,7 +11670,7 @@
           <t>D | 210呎 (开放式)
 $445万
 $21,210/呎
-(25年-01月-12日)</t>
+(25年-01月)</t>
         </is>
       </c>
       <c r="F12" s="22" t="inlineStr">
@@ -11678,7 +11678,7 @@
           <t>E | 209呎 (开放式)
 $474万
 $22,694/呎
-(25年-07月-06日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="G12" s="22" t="inlineStr">
@@ -11686,7 +11686,7 @@
           <t>F | 285呎 (1房)
 $786万
 $27,568/呎
-(22年-05月-02日)</t>
+(22年-05月)</t>
         </is>
       </c>
       <c r="H12" s="22" t="inlineStr">
@@ -11694,7 +11694,7 @@
           <t>G | 211呎 (开放式)
 $672万
 $31,834/呎
-(24年-05月-09日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="I12" s="22" t="inlineStr">
@@ -11702,7 +11702,7 @@
           <t>H | 388呎 (2房)
 $821万
 $21,170/呎
-(25年-01月-23日)</t>
+(25年-01月)</t>
         </is>
       </c>
     </row>
@@ -11717,7 +11717,7 @@
           <t>A | 282呎 (1房)
 $635万
 $22,511/呎
-(26年-02月-23日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="C13" s="22" t="inlineStr">
@@ -11725,7 +11725,7 @@
           <t>B | 278呎 (1房)
 $785万
 $28,248/呎
-(26年-06月-14日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="D13" s="22" t="inlineStr">
@@ -11733,7 +11733,7 @@
           <t>C | 264呎 (1房)
 $624万
 $23,652/呎
-(25年-11月-16日)</t>
+(25年-11月)</t>
         </is>
       </c>
       <c r="E13" s="22" t="inlineStr">
@@ -11741,7 +11741,7 @@
           <t>D | 210呎 (开放式)
 $474万
 $22,562/呎
-(25年-07月-03日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="F13" s="22" t="inlineStr">
@@ -11749,7 +11749,7 @@
           <t>E | 209呎 (开放式)
 $496万
 $23,718/呎
-(26年-02月-08日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="G13" s="22" t="inlineStr">
@@ -11757,7 +11757,7 @@
           <t>F | 285呎 (1房)
 $739万
 $25,923/呎
-(23年-01月-10日)</t>
+(23年-01月)</t>
         </is>
       </c>
       <c r="H13" s="22" t="inlineStr">
@@ -11765,7 +11765,7 @@
           <t>G | 211呎 (开放式)
 $516万
 $24,455/呎
-(26年-01月-18日)</t>
+(26年-01月)</t>
         </is>
       </c>
       <c r="I13" s="22" t="inlineStr">
@@ -11773,7 +11773,7 @@
           <t>H | 388呎 (2房)
 $821万
 $21,170/呎
-(24年-08月-11日)</t>
+(24年-08月)</t>
         </is>
       </c>
     </row>
@@ -11788,7 +11788,7 @@
           <t>A | 282呎 (1房)
 $596万
 $21,121/呎
-(25年-06月-29日)</t>
+(25年-06月)</t>
         </is>
       </c>
       <c r="C14" s="22" t="inlineStr">
@@ -11796,7 +11796,7 @@
           <t>B | 278呎 (1房)
 $563万
 $20,259/呎
-(24年-11月-14日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="D14" s="22" t="inlineStr">
@@ -11804,7 +11804,7 @@
           <t>C | 264呎 (1房)
 $551万
 $20,886/呎
-(25年-03月-25日)</t>
+(25年-03月)</t>
         </is>
       </c>
       <c r="E14" s="22" t="inlineStr">
@@ -11812,7 +11812,7 @@
           <t>D | 210呎 (开放式)
 $472万
 $22,495/呎
-(25年-07月-01日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="F14" s="22" t="inlineStr">
@@ -11820,7 +11820,7 @@
           <t>E | 209呎 (开放式)
 $471万
 $22,555/呎
-(25年-07月-02日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="G14" s="22" t="inlineStr">
@@ -11828,7 +11828,7 @@
           <t>F | 285呎 (1房)
 $730万
 $25,600/呎
-(26年-02月-02日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="H14" s="22" t="inlineStr">
@@ -11836,7 +11836,7 @@
           <t>G | 211呎 (开放式)
 $648万
 $30,735/呎
-(24年-04月-09日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="I14" s="22" t="inlineStr">
@@ -11844,7 +11844,7 @@
           <t>H | 388呎 (2房)
 $821万
 $21,170/呎
-(24年-07月-18日)</t>
+(24年-07月)</t>
         </is>
       </c>
     </row>
@@ -11859,7 +11859,7 @@
           <t>A | 282呎 (1房)
 $594万
 $21,057/呎
-(25年-06月-26日)</t>
+(25年-06月)</t>
         </is>
       </c>
       <c r="C15" s="22" t="inlineStr">
@@ -11867,7 +11867,7 @@
           <t>B | 278呎 (1房)
 $559万
 $20,119/呎
-(24年-11月-21日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="D15" s="22" t="inlineStr">
@@ -11875,7 +11875,7 @@
           <t>C | 264呎 (1房)
 $548万
 $20,742/呎
-(24年-12月-05日)</t>
+(24年-12月)</t>
         </is>
       </c>
       <c r="E15" s="22" t="inlineStr">
@@ -11883,7 +11883,7 @@
           <t>D | 210呎 (开放式)
 $430万
 $20,457/呎
-(25年-02月-20日)</t>
+(25年-02月)</t>
         </is>
       </c>
       <c r="F15" s="22" t="inlineStr">
@@ -11891,7 +11891,7 @@
           <t>E | 209呎 (开放式)
 $423万
 $20,230/呎
-(24年-12月-16日)</t>
+(24年-12月)</t>
         </is>
       </c>
       <c r="G15" s="22" t="inlineStr">
@@ -11899,7 +11899,7 @@
           <t>F | 285呎 (1房)
 $744万
 $26,105/呎
-(26年-01月-29日)</t>
+(26年-01月)</t>
         </is>
       </c>
       <c r="H15" s="22" t="inlineStr">
@@ -11907,7 +11907,7 @@
           <t>G | 211呎 (开放式)
 $648万
 $30,711/呎
-(24年-04月-09日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="I15" s="22" t="inlineStr">
@@ -11915,7 +11915,7 @@
           <t>H | 388呎 (2房)
 $930万
 $23,966/呎
-(23年-02月-23日)</t>
+(23年-02月)</t>
         </is>
       </c>
     </row>
@@ -11930,7 +11930,7 @@
           <t>A | 282呎 (1房)
 $548万
 $19,418/呎
-(24年-10月-23日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="C16" s="22" t="inlineStr">
@@ -11938,7 +11938,7 @@
           <t>B | 278呎 (1房)
 $754万
 $27,104/呎
-(21年-10月-10日)</t>
+(21年-10月)</t>
         </is>
       </c>
       <c r="D16" s="24" t="inlineStr">
@@ -11954,7 +11954,7 @@
           <t>D | 210呎 (开放式)
 $428万
 $20,381/呎
-(24年-11月-17日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="F16" s="22" t="inlineStr">
@@ -11962,7 +11962,7 @@
           <t>E | 209呎 (开放式)
 $421万
 $20,148/呎
-(25年-01月-14日)</t>
+(25年-01月)</t>
         </is>
       </c>
       <c r="G16" s="22" t="inlineStr">
@@ -11970,7 +11970,7 @@
           <t>F | 285呎 (1房)
 $783万
 $27,481/呎
-(21年-07月-13日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="H16" s="22" t="inlineStr">
@@ -11978,7 +11978,7 @@
           <t>G | 211呎 (开放式)
 $488万
 $23,114/呎
-(25年-07月-23日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="I16" s="22" t="inlineStr">
@@ -11986,7 +11986,7 @@
           <t>H | 388呎 (2房)
 $991万
 $25,549/呎
-(21年-07月-06日)</t>
+(21年-07月)</t>
         </is>
       </c>
     </row>
@@ -12001,7 +12001,7 @@
           <t>A | 282呎 (1房)
 $734万
 $26,025/呎
-(21年-07月-08日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="C17" s="22" t="inlineStr">
@@ -12009,7 +12009,7 @@
           <t>B | 278呎 (1房)
 $735万
 $26,424/呎
-(21年-07月-14日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="D17" s="22" t="inlineStr">
@@ -12017,7 +12017,7 @@
           <t>C | 264呎 (1房)
 $706万
 $26,723/呎
-(21年-07月-04日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="E17" s="22" t="inlineStr">
@@ -12025,7 +12025,7 @@
           <t>D | 210呎 (开放式)
 $611万
 $29,090/呎
-(24年-03月-25日)</t>
+(24年-03月)</t>
         </is>
       </c>
       <c r="F17" s="22" t="inlineStr">
@@ -12033,7 +12033,7 @@
           <t>E | 209呎 (开放式)
 $428万
 $20,478/呎
-(25年-03月-19日)</t>
+(25年-03月)</t>
         </is>
       </c>
       <c r="G17" s="22" t="inlineStr">
@@ -12041,7 +12041,7 @@
           <t>F | 285呎 (1房)
 $762万
 $26,737/呎
-(21年-07月-12日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="H17" s="22" t="inlineStr">
@@ -12049,7 +12049,7 @@
           <t>G | 211呎 (开放式)
 $486万
 $23,047/呎
-(25年-07月-23日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="I17" s="22" t="inlineStr">
@@ -12057,7 +12057,7 @@
           <t>H | 388呎 (2房)
 $987万
 $25,443/呎
-(21年-07月-07日)</t>
+(21年-07月)</t>
         </is>
       </c>
     </row>
@@ -12072,7 +12072,7 @@
           <t>A | 282呎 (1房)
 $731万
 $25,918/呎
-(21年-07月-12日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="C18" s="22" t="inlineStr">
@@ -12080,7 +12080,7 @@
           <t>B | 277呎 (1房)
 $732万
 $26,408/呎
-(21年-07月-15日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="D18" s="22" t="inlineStr">
@@ -12088,7 +12088,7 @@
           <t>C | 264呎 (1房)
 $698万
 $26,458/呎
-(21年-07月-04日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="E18" s="22" t="inlineStr">
@@ -12096,7 +12096,7 @@
           <t>D | 210呎 (开放式)
 $603万
 $28,700/呎
-(24年-03月-24日)</t>
+(24年-03月)</t>
         </is>
       </c>
       <c r="F18" s="22" t="inlineStr">
@@ -12104,7 +12104,7 @@
           <t>E | 209呎 (开放式)
 $414万
 $19,794/呎
-(24年-10月-23日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="G18" s="22" t="inlineStr">
@@ -12112,7 +12112,7 @@
           <t>F | 285呎 (1房)
 $724万
 $25,418/呎
-(21年-07月-05日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="H18" s="22" t="inlineStr">
@@ -12120,7 +12120,7 @@
           <t>G | 211呎 (开放式)
 $582万
 $27,607/呎
-(21年-07月-08日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="I18" s="22" t="inlineStr">
@@ -12128,7 +12128,7 @@
           <t>H | 388呎 (2房)
 $934万
 $24,075/呎
-(21年-07月-08日)</t>
+(21年-07月)</t>
         </is>
       </c>
     </row>
@@ -12143,7 +12143,7 @@
           <t>A | 282呎 (1房)
 $530万
 $18,777/呎
-(24年-08月-29日)</t>
+(24年-08月)</t>
         </is>
       </c>
       <c r="C19" s="22" t="inlineStr">
@@ -12151,7 +12151,7 @@
           <t>B | 277呎 (1房)
 $696万
 $25,108/呎
-(21年-07月-08日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="D19" s="22" t="inlineStr">
@@ -12159,7 +12159,7 @@
           <t>C | 264呎 (1房)
 $659万
 $24,958/呎
-(21年-07月-04日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="E19" s="22" t="inlineStr">
@@ -12167,7 +12167,7 @@
           <t>D | 210呎 (开放式)
 $578万
 $27,543/呎
-(21年-06月-18日)</t>
+(21年-06月)</t>
         </is>
       </c>
       <c r="F19" s="22" t="inlineStr">
@@ -12175,7 +12175,7 @@
           <t>E | 209呎 (开放式)
 $553万
 $26,450/呎
-(21年-07月-05日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="G19" s="22" t="inlineStr">
@@ -12183,7 +12183,7 @@
           <t>F | 285呎 (1房)
 $756万
 $26,523/呎
-(21年-07月-08日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="H19" s="22" t="inlineStr">
@@ -12191,7 +12191,7 @@
           <t>G | 211呎 (开放式)
 $592万
 $28,047/呎
-(21年-07月-07日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="I19" s="22" t="inlineStr">
@@ -12199,7 +12199,7 @@
           <t>H | 388呎 (2房)
 $970万
 $24,995/呎
-(22年-01月-18日)</t>
+(22年-01月)</t>
         </is>
       </c>
     </row>
@@ -12214,7 +12214,7 @@
           <t>A | 282呎 (1房)
 $527万
 $18,699/呎
-(24年-08月-20日)</t>
+(24年-08月)</t>
         </is>
       </c>
       <c r="C20" s="22" t="inlineStr">
@@ -12222,7 +12222,7 @@
           <t>B | 277呎 (1房)
 $719万
 $25,942/呎
-(21年-07月-12日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="D20" s="22" t="inlineStr">
@@ -12230,7 +12230,7 @@
           <t>C | 264呎 (1房)
 $659万
 $24,951/呎
-(22年-03月-02日)</t>
+(22年-03月)</t>
         </is>
       </c>
       <c r="E20" s="22" t="inlineStr">
@@ -12238,7 +12238,7 @@
           <t>D | 210呎 (开放式)
 $570万
 $27,162/呎
-(21年-07月-20日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="F20" s="22" t="inlineStr">
@@ -12246,7 +12246,7 @@
           <t>E | 209呎 (开放式)
 $590万
 $28,225/呎
-(24年-03月-24日)</t>
+(24年-03月)</t>
         </is>
       </c>
       <c r="G20" s="22" t="inlineStr">
@@ -12254,7 +12254,7 @@
           <t>F | 285呎 (1房)
 $712万
 $24,965/呎
-(21年-06月-18日)</t>
+(21年-06月)</t>
         </is>
       </c>
       <c r="H20" s="22" t="inlineStr">
@@ -12262,7 +12262,7 @@
           <t>G | 211呎 (开放式)
 $557万
 $26,408/呎
-(21年-10月-07日)</t>
+(21年-10月)</t>
         </is>
       </c>
       <c r="I20" s="22" t="inlineStr">
@@ -12270,7 +12270,7 @@
           <t>H | 388呎 (2房)
 $961万
 $24,771/呎
-(21年-07月-12日)</t>
+(21年-07月)</t>
         </is>
       </c>
     </row>
@@ -12285,7 +12285,7 @@
           <t>A | 283呎 (1房)
 $689万
 $24,360/呎
-(22年-01月-26日)</t>
+(22年-01月)</t>
         </is>
       </c>
       <c r="C21" s="22" t="inlineStr">
@@ -12293,7 +12293,7 @@
           <t>B | 278呎 (1房)
 $683万
 $24,576/呎
-(21年-07月-07日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="D21" s="22" t="inlineStr">
@@ -12301,7 +12301,7 @@
           <t>C | 264呎 (1房)
 $610万
 $23,098/呎
-(21年-06月-18日)</t>
+(21年-06月)</t>
         </is>
       </c>
       <c r="E21" s="22" t="inlineStr">
@@ -12309,7 +12309,7 @@
           <t>D | 210呎 (开放式)
 $581万
 $27,667/呎
-(24年-03月-24日)</t>
+(24年-03月)</t>
         </is>
       </c>
       <c r="F21" s="22" t="inlineStr">
@@ -12317,7 +12317,7 @@
           <t>E | 209呎 (开放式)
 $543万
 $25,976/呎
-(21年-07月-15日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="G21" s="22" t="inlineStr">
@@ -12325,7 +12325,7 @@
           <t>F | 285呎 (1房)
 $742万
 $26,049/呎
-(21年-07月-08日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="H21" s="22" t="inlineStr">
@@ -12333,7 +12333,7 @@
           <t>G | 211呎 (开放式)
 $555万
 $26,303/呎
-(21年-07月-12日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="I21" s="22" t="inlineStr">
@@ -12341,7 +12341,7 @@
           <t>H | 388呎 (2房)
 $957万
 $24,673/呎
-(21年-07月-13日)</t>
+(21年-07月)</t>
         </is>
       </c>
     </row>
@@ -12356,7 +12356,7 @@
           <t>A | 283呎 (1房)
 $689万
 $24,336/呎
-(21年-07月-11日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="C22" s="22" t="inlineStr">
@@ -12364,7 +12364,7 @@
           <t>B | 277呎 (1房)
 $701万
 $25,292/呎
-(21年-07月-12日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="D22" s="22" t="inlineStr">
@@ -12372,7 +12372,7 @@
           <t>C | 264呎 (1房)
 $635万
 $24,045/呎
-(21年-07月-08日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="E22" s="22" t="inlineStr">
@@ -12380,7 +12380,7 @@
           <t>D | 210呎 (开放式)
 $531万
 $25,281/呎
-(21年-07月-08日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="F22" s="22" t="inlineStr">
@@ -12388,7 +12388,7 @@
           <t>E | 209呎 (开放式)
 $570万
 $27,249/呎
-(24年-03月-19日)</t>
+(24年-03月)</t>
         </is>
       </c>
       <c r="G22" s="22" t="inlineStr">
@@ -12396,7 +12396,7 @@
           <t>F | 285呎 (1房)
 $708万
 $24,842/呎
-(21年-07月-15日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="H22" s="22" t="inlineStr">
@@ -12404,7 +12404,7 @@
           <t>G | 211呎 (开放式)
 $581万
 $27,526/呎
-(21年-07月-04日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="I22" s="22" t="inlineStr">
@@ -12412,7 +12412,7 @@
           <t>H | 388呎 (2房)
 $924万
 $23,807/呎
-(22年-08月-08日)</t>
+(22年-08月)</t>
         </is>
       </c>
     </row>
@@ -12427,7 +12427,7 @@
           <t>A | 283呎 (1房)
 $716万
 $25,318/呎
-(21年-07月-11日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="C23" s="22" t="inlineStr">
@@ -12435,7 +12435,7 @@
           <t>B | 277呎 (1房)
 $672万
 $24,260/呎
-(22年-02月-13日)</t>
+(22年-02月)</t>
         </is>
       </c>
       <c r="D23" s="22" t="inlineStr">
@@ -12443,7 +12443,7 @@
           <t>C | 264呎 (1房)
 $660万
 $25,011/呎
-(21年-07月-07日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="E23" s="22" t="inlineStr">
@@ -12451,7 +12451,7 @@
           <t>D | 209呎 (开放式)
 $531万
 $25,407/呎
-(22年-04月-13日)</t>
+(22年-04月)</t>
         </is>
       </c>
       <c r="F23" s="22" t="inlineStr">
@@ -12459,7 +12459,7 @@
           <t>E | 209呎 (开放式)
 $553万
 $26,459/呎
-(21年-06月-18日)</t>
+(21年-06月)</t>
         </is>
       </c>
       <c r="G23" s="22" t="inlineStr">
@@ -12467,7 +12467,7 @@
           <t>F | 286呎 (1房)
 $718万
 $25,108/呎
-(21年-07月-05日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="H23" s="24" t="inlineStr">
@@ -12483,7 +12483,7 @@
           <t>H | 388呎 (2房)
 $950万
 $24,477/呎
-(21年-07月-13日)</t>
+(21年-07月)</t>
         </is>
       </c>
     </row>
@@ -12498,7 +12498,7 @@
           <t>A | 282呎 (1房)
 $714万
 $25,305/呎
-(21年-07月-11日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="C24" s="22" t="inlineStr">
@@ -12506,7 +12506,7 @@
           <t>B | 277呎 (1房)
 $693万
 $25,007/呎
-(21年-07月-13日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="D24" s="22" t="inlineStr">
@@ -12514,7 +12514,7 @@
           <t>C | 264呎 (1房)
 $658万
 $24,905/呎
-(21年-07月-07日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="E24" s="22" t="inlineStr">
@@ -12522,7 +12522,7 @@
           <t>D | 209呎 (开放式)
 $522万
 $24,995/呎
-(21年-07月-07日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="F24" s="22" t="inlineStr">
@@ -12530,7 +12530,7 @@
           <t>E | 209呎 (开放式)
 $563万
 $26,938/呎
-(24年-03月-21日)</t>
+(24年-03月)</t>
         </is>
       </c>
       <c r="G24" s="22" t="inlineStr">
@@ -12538,7 +12538,7 @@
           <t>F | 286呎 (1房)
 $703万
 $24,566/呎
-(21年-07月-05日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="H24" s="22" t="inlineStr">
@@ -12546,7 +12546,7 @@
           <t>G | 211呎 (开放式)
 $548万
 $25,986/呎
-(21年-07月-05日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="I24" s="22" t="inlineStr">
@@ -12554,7 +12554,7 @@
           <t>H | 388呎 (2房)
 $946万
 $24,376/呎
-(21年-07月-08日)</t>
+(21年-07月)</t>
         </is>
       </c>
     </row>
@@ -12569,7 +12569,7 @@
           <t>A | 282呎 (1房)
 $711万
 $25,199/呎
-(21年-07月-12日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="C25" s="22" t="inlineStr">
@@ -12577,7 +12577,7 @@
           <t>B | 277呎 (1房)
 $658万
 $23,765/呎
-(21年-07月-08日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="D25" s="22" t="inlineStr">
@@ -12585,7 +12585,7 @@
           <t>C | 264呎 (1房)
 $655万
 $24,799/呎
-(21年-07月-15日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="E25" s="22" t="inlineStr">
@@ -12593,7 +12593,7 @@
           <t>D | 209呎 (开放式)
 $524万
 $25,053/呎
-(21年-07月-08日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="F25" s="22" t="inlineStr">
@@ -12601,7 +12601,7 @@
           <t>E | 209呎 (开放式)
 $523万
 $25,033/呎
-(21年-06月-18日)</t>
+(21年-06月)</t>
         </is>
       </c>
       <c r="G25" s="22" t="inlineStr">
@@ -12609,7 +12609,7 @@
           <t>F | 286呎 (1房)
 $733万
 $25,633/呎
-(21年-07月-13日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="H25" s="22" t="inlineStr">
@@ -12617,7 +12617,7 @@
           <t>G | 211呎 (开放式)
 $572万
 $27,109/呎
-(21年-07月-11日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="I25" s="22" t="inlineStr">
@@ -12625,7 +12625,7 @@
           <t>H | 388呎 (2房)
 $899万
 $23,175/呎
-(21年-07月-12日)</t>
+(21年-07月)</t>
         </is>
       </c>
     </row>

--- a/files/九龙-何文田-VAU Residence.xlsx
+++ b/files/九龙-何文田-VAU Residence.xlsx
@@ -11210,7 +11210,7 @@
           <t>F | 384呎 (2房)
 $1306万
 $34,000/呎
-(25年-07月)</t>
+(25年-07月-13日)</t>
         </is>
       </c>
       <c r="H5" s="22" t="inlineStr">
@@ -11218,7 +11218,7 @@
           <t>G | 499呎 (3房)
 $1697万
 $34,000/呎
-(25年-07月)</t>
+(25年-07月-14日)</t>
         </is>
       </c>
       <c r="I5" s="23" t="inlineStr"/>
@@ -11234,7 +11234,7 @@
           <t>A | 282呎 (1房)
 $778万
 $27,603/呎
-(26年-05月)</t>
+(26年-05月-04日)</t>
         </is>
       </c>
       <c r="C6" s="22" t="inlineStr">
@@ -11242,7 +11242,7 @@
           <t>B | 278呎 (1房)
 $766万
 $27,543/呎
-(26年-05月)</t>
+(26年-05月-04日)</t>
         </is>
       </c>
       <c r="D6" s="22" t="inlineStr">
@@ -11250,7 +11250,7 @@
           <t>C | 264呎 (1房)
 $779万
 $29,504/呎
-(26年-05月)</t>
+(26年-05月-19日)</t>
         </is>
       </c>
       <c r="E6" s="22" t="inlineStr">
@@ -11258,7 +11258,7 @@
           <t>D | 210呎 (开放式)
 $581万
 $27,667/呎
-(26年-04月)</t>
+(26年-04月-16日)</t>
         </is>
       </c>
       <c r="F6" s="22" t="inlineStr">
@@ -11266,7 +11266,7 @@
           <t>E | 209呎 (开放式)
 $618万
 $29,589/呎
-(26年-06月)</t>
+(26年-06月-01日)</t>
         </is>
       </c>
       <c r="G6" s="22" t="inlineStr">
@@ -11274,7 +11274,7 @@
           <t>F | 384呎 (2房)
 $1039万
 $27,062/呎
-(25年-07月)</t>
+(25年-07月-08日)</t>
         </is>
       </c>
       <c r="H6" s="22" t="inlineStr">
@@ -11282,7 +11282,7 @@
           <t>G | 499呎 (3房)
 $1272万
 $25,497/呎
-(25年-07月)</t>
+(25年-07月-10日)</t>
         </is>
       </c>
       <c r="I6" s="23" t="inlineStr"/>
@@ -11306,7 +11306,7 @@
           <t>B | 278呎 (1房)
 $670万
 $24,086/呎
-(26年-01月)</t>
+(26年-01月-08日)</t>
         </is>
       </c>
       <c r="D7" s="22" t="inlineStr">
@@ -11314,7 +11314,7 @@
           <t>C | 264呎 (1房)
 $714万
 $27,061/呎
-(26年-04月)</t>
+(26年-04月-26日)</t>
         </is>
       </c>
       <c r="E7" s="22" t="inlineStr">
@@ -11322,7 +11322,7 @@
           <t>D | 210呎 (开放式)
 $504万
 $24,014/呎
-(26年-02月)</t>
+(26年-02月-10日)</t>
         </is>
       </c>
       <c r="F7" s="22" t="inlineStr">
@@ -11330,7 +11330,7 @@
           <t>E | 209呎 (开放式)
 $480万
 $22,967/呎
-(25年-08月)</t>
+(25年-08月-24日)</t>
         </is>
       </c>
       <c r="G7" s="22" t="inlineStr">
@@ -11338,7 +11338,7 @@
           <t>F | 384呎 (2房)
 $1164万
 $30,320/呎
-(26年-04月)</t>
+(26年-04月-27日)</t>
         </is>
       </c>
       <c r="H7" s="20" t="inlineStr">
@@ -11362,7 +11362,7 @@
           <t>A | 282呎 (1房)
 $632万
 $22,429/呎
-(25年-11月)</t>
+(25年-11月-25日)</t>
         </is>
       </c>
       <c r="C8" s="22" t="inlineStr">
@@ -11370,7 +11370,7 @@
           <t>B | 278呎 (1房)
 $601万
 $21,615/呎
-(24年-10月)</t>
+(24年-10月-17日)</t>
         </is>
       </c>
       <c r="D8" s="22" t="inlineStr">
@@ -11378,7 +11378,7 @@
           <t>C | 264呎 (1房)
 $592万
 $22,420/呎
-(25年-05月)</t>
+(25年-05月-20日)</t>
         </is>
       </c>
       <c r="E8" s="22" t="inlineStr">
@@ -11386,7 +11386,7 @@
           <t>D | 210呎 (开放式)
 $470万
 $22,390/呎
-(25年-04月)</t>
+(25年-04月-15日)</t>
         </is>
       </c>
       <c r="F8" s="22" t="inlineStr">
@@ -11394,7 +11394,7 @@
           <t>E | 209呎 (开放式)
 $679万
 $32,507/呎
-(24年-04月)</t>
+(24年-04月-07日)</t>
         </is>
       </c>
       <c r="G8" s="22" t="inlineStr">
@@ -11402,7 +11402,7 @@
           <t>F | 285呎 (1房)
 $862万
 $30,263/呎
-(23年-05月)</t>
+(23年-05月-11日)</t>
         </is>
       </c>
       <c r="H8" s="22" t="inlineStr">
@@ -11410,7 +11410,7 @@
           <t>G | 211呎 (开放式)
 $488万
 $23,147/呎
-(25年-06月)</t>
+(25年-06月-15日)</t>
         </is>
       </c>
       <c r="I8" s="22" t="inlineStr">
@@ -11418,7 +11418,7 @@
           <t>H | 388呎 (2房)
 $855万
 $22,039/呎
-(24年-10月)</t>
+(24年-10月-31日)</t>
         </is>
       </c>
     </row>
@@ -11433,7 +11433,7 @@
           <t>A | 282呎 (1房)
 $591万
 $20,961/呎
-(25年-05月)</t>
+(25年-05月-22日)</t>
         </is>
       </c>
       <c r="C9" s="22" t="inlineStr">
@@ -11441,7 +11441,7 @@
           <t>B | 278呎 (1房)
 $592万
 $21,277/呎
-(24年-09月)</t>
+(24年-09月-02日)</t>
         </is>
       </c>
       <c r="D9" s="22" t="inlineStr">
@@ -11449,7 +11449,7 @@
           <t>C | 264呎 (1房)
 $579万
 $21,928/呎
-(25年-03月)</t>
+(25年-03月-30日)</t>
         </is>
       </c>
       <c r="E9" s="22" t="inlineStr">
@@ -11457,7 +11457,7 @@
           <t>D | 210呎 (开放式)
 $480万
 $22,833/呎
-(25年-07月)</t>
+(25年-07月-23日)</t>
         </is>
       </c>
       <c r="F9" s="22" t="inlineStr">
@@ -11465,7 +11465,7 @@
           <t>E | 209呎 (开放式)
 $479万
 $22,900/呎
-(25年-07月)</t>
+(25年-07月-23日)</t>
         </is>
       </c>
       <c r="G9" s="22" t="inlineStr">
@@ -11473,7 +11473,7 @@
           <t>F | 285呎 (1房)
 $860万
 $30,172/呎
-(24年-04月)</t>
+(24年-04月-09日)</t>
         </is>
       </c>
       <c r="H9" s="22" t="inlineStr">
@@ -11481,7 +11481,7 @@
           <t>G | 211呎 (开放式)
 $522万
 $24,749/呎
-(26年-02月)</t>
+(26年-02月-03日)</t>
         </is>
       </c>
       <c r="I9" s="22" t="inlineStr">
@@ -11489,7 +11489,7 @@
           <t>H | 388呎 (2房)
 $847万
 $21,820/呎
-(25年-02月)</t>
+(25年-02月-20日)</t>
         </is>
       </c>
     </row>
@@ -11512,7 +11512,7 @@
           <t>B | 278呎 (1房)
 $664万
 $23,874/呎
-(25年-11月)</t>
+(25年-11月-18日)</t>
         </is>
       </c>
       <c r="D10" s="22" t="inlineStr">
@@ -11520,7 +11520,7 @@
           <t>C | 264呎 (1房)
 $572万
 $21,667/呎
-(24年-06月)</t>
+(24年-06月-19日)</t>
         </is>
       </c>
       <c r="E10" s="22" t="inlineStr">
@@ -11528,7 +11528,7 @@
           <t>D | 210呎 (开放式)
 $456万
 $21,719/呎
-(25年-03月)</t>
+(25年-03月-19日)</t>
         </is>
       </c>
       <c r="F10" s="22" t="inlineStr">
@@ -11536,7 +11536,7 @@
           <t>E | 209呎 (开放式)
 $451万
 $21,579/呎
-(24年-11月)</t>
+(24年-11月-21日)</t>
         </is>
       </c>
       <c r="G10" s="22" t="inlineStr">
@@ -11544,7 +11544,7 @@
           <t>F | 285呎 (1房)
 $767万
 $26,926/呎
-(26年-02月)</t>
+(26年-02月-10日)</t>
         </is>
       </c>
       <c r="H10" s="22" t="inlineStr">
@@ -11552,7 +11552,7 @@
           <t>G | 211呎 (开放式)
 $641万
 $30,370/呎
-(26年-05月)</t>
+(26年-05月-28日)</t>
         </is>
       </c>
       <c r="I10" s="22" t="inlineStr">
@@ -11560,7 +11560,7 @@
           <t>H | 388呎 (2房)
 $875万
 $22,541/呎
-(26年-01月)</t>
+(26年-01月-25日)</t>
         </is>
       </c>
     </row>
@@ -11575,7 +11575,7 @@
           <t>A | 282呎 (1房)
 $577万
 $20,465/呎
-(25年-04月)</t>
+(25年-04月-08日)</t>
         </is>
       </c>
       <c r="C11" s="22" t="inlineStr">
@@ -11583,7 +11583,7 @@
           <t>B | 278呎 (1房)
 $578万
 $20,773/呎
-(24年-08月)</t>
+(24年-08月-25日)</t>
         </is>
       </c>
       <c r="D11" s="22" t="inlineStr">
@@ -11591,7 +11591,7 @@
           <t>C | 264呎 (1房)
 $565万
 $21,413/呎
-(24年-10月)</t>
+(24年-10月-22日)</t>
         </is>
       </c>
       <c r="E11" s="22" t="inlineStr">
@@ -11599,7 +11599,7 @@
           <t>D | 210呎 (开放式)
 $451万
 $21,462/呎
-(25年-01月)</t>
+(25年-01月-22日)</t>
         </is>
       </c>
       <c r="F11" s="22" t="inlineStr">
@@ -11607,7 +11607,7 @@
           <t>E | 209呎 (开放式)
 $446万
 $21,316/呎
-(24年-08月)</t>
+(24年-08月-07日)</t>
         </is>
       </c>
       <c r="G11" s="22" t="inlineStr">
@@ -11615,7 +11615,7 @@
           <t>F | 285呎 (1房)
 $840万
 $29,488/呎
-(24年-03月)</t>
+(24年-03月-27日)</t>
         </is>
       </c>
       <c r="H11" s="22" t="inlineStr">
@@ -11623,7 +11623,7 @@
           <t>G | 211呎 (开放式)
 $468万
 $22,194/呎
-(25年-04月)</t>
+(25年-04月-09日)</t>
         </is>
       </c>
       <c r="I11" s="22" t="inlineStr">
@@ -11631,7 +11631,7 @@
           <t>H | 388呎 (2房)
 $830万
 $21,387/呎
-(25年-04月)</t>
+(25年-04月-08日)</t>
         </is>
       </c>
     </row>
@@ -11646,7 +11646,7 @@
           <t>A | 282呎 (1房)
 $627万
 $22,245/呎
-(25年-11月)</t>
+(25年-11月-24日)</t>
         </is>
       </c>
       <c r="C12" s="22" t="inlineStr">
@@ -11654,7 +11654,7 @@
           <t>B | 278呎 (1房)
 $660万
 $23,730/呎
-(25年-11月)</t>
+(25年-11月-23日)</t>
         </is>
       </c>
       <c r="D12" s="22" t="inlineStr">
@@ -11662,7 +11662,7 @@
           <t>C | 264呎 (1房)
 $786万
 $29,754/呎
-(24年-04月)</t>
+(24年-04月-21日)</t>
         </is>
       </c>
       <c r="E12" s="22" t="inlineStr">
@@ -11670,7 +11670,7 @@
           <t>D | 210呎 (开放式)
 $445万
 $21,210/呎
-(25年-01月)</t>
+(25年-01月-12日)</t>
         </is>
       </c>
       <c r="F12" s="22" t="inlineStr">
@@ -11678,7 +11678,7 @@
           <t>E | 209呎 (开放式)
 $474万
 $22,694/呎
-(25年-07月)</t>
+(25年-07月-06日)</t>
         </is>
       </c>
       <c r="G12" s="22" t="inlineStr">
@@ -11686,7 +11686,7 @@
           <t>F | 285呎 (1房)
 $786万
 $27,568/呎
-(22年-05月)</t>
+(22年-05月-02日)</t>
         </is>
       </c>
       <c r="H12" s="22" t="inlineStr">
@@ -11694,7 +11694,7 @@
           <t>G | 211呎 (开放式)
 $672万
 $31,834/呎
-(24年-05月)</t>
+(24年-05月-09日)</t>
         </is>
       </c>
       <c r="I12" s="22" t="inlineStr">
@@ -11702,7 +11702,7 @@
           <t>H | 388呎 (2房)
 $821万
 $21,170/呎
-(25年-01月)</t>
+(25年-01月-23日)</t>
         </is>
       </c>
     </row>
@@ -11717,7 +11717,7 @@
           <t>A | 282呎 (1房)
 $635万
 $22,511/呎
-(26年-02月)</t>
+(26年-02月-23日)</t>
         </is>
       </c>
       <c r="C13" s="22" t="inlineStr">
@@ -11725,7 +11725,7 @@
           <t>B | 278呎 (1房)
 $785万
 $28,248/呎
-(26年-06月)</t>
+(26年-06月-14日)</t>
         </is>
       </c>
       <c r="D13" s="22" t="inlineStr">
@@ -11733,7 +11733,7 @@
           <t>C | 264呎 (1房)
 $624万
 $23,652/呎
-(25年-11月)</t>
+(25年-11月-16日)</t>
         </is>
       </c>
       <c r="E13" s="22" t="inlineStr">
@@ -11741,7 +11741,7 @@
           <t>D | 210呎 (开放式)
 $474万
 $22,562/呎
-(25年-07月)</t>
+(25年-07月-03日)</t>
         </is>
       </c>
       <c r="F13" s="22" t="inlineStr">
@@ -11749,7 +11749,7 @@
           <t>E | 209呎 (开放式)
 $496万
 $23,718/呎
-(26年-02月)</t>
+(26年-02月-08日)</t>
         </is>
       </c>
       <c r="G13" s="22" t="inlineStr">
@@ -11757,7 +11757,7 @@
           <t>F | 285呎 (1房)
 $739万
 $25,923/呎
-(23年-01月)</t>
+(23年-01月-10日)</t>
         </is>
       </c>
       <c r="H13" s="22" t="inlineStr">
@@ -11765,7 +11765,7 @@
           <t>G | 211呎 (开放式)
 $516万
 $24,455/呎
-(26年-01月)</t>
+(26年-01月-18日)</t>
         </is>
       </c>
       <c r="I13" s="22" t="inlineStr">
@@ -11773,7 +11773,7 @@
           <t>H | 388呎 (2房)
 $821万
 $21,170/呎
-(24年-08月)</t>
+(24年-08月-11日)</t>
         </is>
       </c>
     </row>
@@ -11788,7 +11788,7 @@
           <t>A | 282呎 (1房)
 $596万
 $21,121/呎
-(25年-06月)</t>
+(25年-06月-29日)</t>
         </is>
       </c>
       <c r="C14" s="22" t="inlineStr">
@@ -11796,7 +11796,7 @@
           <t>B | 278呎 (1房)
 $563万
 $20,259/呎
-(24年-11月)</t>
+(24年-11月-14日)</t>
         </is>
       </c>
       <c r="D14" s="22" t="inlineStr">
@@ -11804,7 +11804,7 @@
           <t>C | 264呎 (1房)
 $551万
 $20,886/呎
-(25年-03月)</t>
+(25年-03月-25日)</t>
         </is>
       </c>
       <c r="E14" s="22" t="inlineStr">
@@ -11812,7 +11812,7 @@
           <t>D | 210呎 (开放式)
 $472万
 $22,495/呎
-(25年-07月)</t>
+(25年-07月-01日)</t>
         </is>
       </c>
       <c r="F14" s="22" t="inlineStr">
@@ -11820,7 +11820,7 @@
           <t>E | 209呎 (开放式)
 $471万
 $22,555/呎
-(25年-07月)</t>
+(25年-07月-02日)</t>
         </is>
       </c>
       <c r="G14" s="22" t="inlineStr">
@@ -11828,7 +11828,7 @@
           <t>F | 285呎 (1房)
 $730万
 $25,600/呎
-(26年-02月)</t>
+(26年-02月-02日)</t>
         </is>
       </c>
       <c r="H14" s="22" t="inlineStr">
@@ -11836,7 +11836,7 @@
           <t>G | 211呎 (开放式)
 $648万
 $30,735/呎
-(24年-04月)</t>
+(24年-04月-09日)</t>
         </is>
       </c>
       <c r="I14" s="22" t="inlineStr">
@@ -11844,7 +11844,7 @@
           <t>H | 388呎 (2房)
 $821万
 $21,170/呎
-(24年-07月)</t>
+(24年-07月-18日)</t>
         </is>
       </c>
     </row>
@@ -11859,7 +11859,7 @@
           <t>A | 282呎 (1房)
 $594万
 $21,057/呎
-(25年-06月)</t>
+(25年-06月-26日)</t>
         </is>
       </c>
       <c r="C15" s="22" t="inlineStr">
@@ -11867,7 +11867,7 @@
           <t>B | 278呎 (1房)
 $559万
 $20,119/呎
-(24年-11月)</t>
+(24年-11月-21日)</t>
         </is>
       </c>
       <c r="D15" s="22" t="inlineStr">
@@ -11875,7 +11875,7 @@
           <t>C | 264呎 (1房)
 $548万
 $20,742/呎
-(24年-12月)</t>
+(24年-12月-05日)</t>
         </is>
       </c>
       <c r="E15" s="22" t="inlineStr">
@@ -11883,7 +11883,7 @@
           <t>D | 210呎 (开放式)
 $430万
 $20,457/呎
-(25年-02月)</t>
+(25年-02月-20日)</t>
         </is>
       </c>
       <c r="F15" s="22" t="inlineStr">
@@ -11891,7 +11891,7 @@
           <t>E | 209呎 (开放式)
 $423万
 $20,230/呎
-(24年-12月)</t>
+(24年-12月-16日)</t>
         </is>
       </c>
       <c r="G15" s="22" t="inlineStr">
@@ -11899,7 +11899,7 @@
           <t>F | 285呎 (1房)
 $744万
 $26,105/呎
-(26年-01月)</t>
+(26年-01月-29日)</t>
         </is>
       </c>
       <c r="H15" s="22" t="inlineStr">
@@ -11907,7 +11907,7 @@
           <t>G | 211呎 (开放式)
 $648万
 $30,711/呎
-(24年-04月)</t>
+(24年-04月-09日)</t>
         </is>
       </c>
       <c r="I15" s="22" t="inlineStr">
@@ -11915,7 +11915,7 @@
           <t>H | 388呎 (2房)
 $930万
 $23,966/呎
-(23年-02月)</t>
+(23年-02月-23日)</t>
         </is>
       </c>
     </row>
@@ -11930,7 +11930,7 @@
           <t>A | 282呎 (1房)
 $548万
 $19,418/呎
-(24年-10月)</t>
+(24年-10月-23日)</t>
         </is>
       </c>
       <c r="C16" s="22" t="inlineStr">
@@ -11938,7 +11938,7 @@
           <t>B | 278呎 (1房)
 $754万
 $27,104/呎
-(21年-10月)</t>
+(21年-10月-10日)</t>
         </is>
       </c>
       <c r="D16" s="24" t="inlineStr">
@@ -11954,7 +11954,7 @@
           <t>D | 210呎 (开放式)
 $428万
 $20,381/呎
-(24年-11月)</t>
+(24年-11月-17日)</t>
         </is>
       </c>
       <c r="F16" s="22" t="inlineStr">
@@ -11962,7 +11962,7 @@
           <t>E | 209呎 (开放式)
 $421万
 $20,148/呎
-(25年-01月)</t>
+(25年-01月-14日)</t>
         </is>
       </c>
       <c r="G16" s="22" t="inlineStr">
@@ -11970,7 +11970,7 @@
           <t>F | 285呎 (1房)
 $783万
 $27,481/呎
-(21年-07月)</t>
+(21年-07月-13日)</t>
         </is>
       </c>
       <c r="H16" s="22" t="inlineStr">
@@ -11978,7 +11978,7 @@
           <t>G | 211呎 (开放式)
 $488万
 $23,114/呎
-(25年-07月)</t>
+(25年-07月-23日)</t>
         </is>
       </c>
       <c r="I16" s="22" t="inlineStr">
@@ -11986,7 +11986,7 @@
           <t>H | 388呎 (2房)
 $991万
 $25,549/呎
-(21年-07月)</t>
+(21年-07月-06日)</t>
         </is>
       </c>
     </row>
@@ -12001,7 +12001,7 @@
           <t>A | 282呎 (1房)
 $734万
 $26,025/呎
-(21年-07月)</t>
+(21年-07月-08日)</t>
         </is>
       </c>
       <c r="C17" s="22" t="inlineStr">
@@ -12009,7 +12009,7 @@
           <t>B | 278呎 (1房)
 $735万
 $26,424/呎
-(21年-07月)</t>
+(21年-07月-14日)</t>
         </is>
       </c>
       <c r="D17" s="22" t="inlineStr">
@@ -12017,7 +12017,7 @@
           <t>C | 264呎 (1房)
 $706万
 $26,723/呎
-(21年-07月)</t>
+(21年-07月-04日)</t>
         </is>
       </c>
       <c r="E17" s="22" t="inlineStr">
@@ -12025,7 +12025,7 @@
           <t>D | 210呎 (开放式)
 $611万
 $29,090/呎
-(24年-03月)</t>
+(24年-03月-25日)</t>
         </is>
       </c>
       <c r="F17" s="22" t="inlineStr">
@@ -12033,7 +12033,7 @@
           <t>E | 209呎 (开放式)
 $428万
 $20,478/呎
-(25年-03月)</t>
+(25年-03月-19日)</t>
         </is>
       </c>
       <c r="G17" s="22" t="inlineStr">
@@ -12041,7 +12041,7 @@
           <t>F | 285呎 (1房)
 $762万
 $26,737/呎
-(21年-07月)</t>
+(21年-07月-12日)</t>
         </is>
       </c>
       <c r="H17" s="22" t="inlineStr">
@@ -12049,7 +12049,7 @@
           <t>G | 211呎 (开放式)
 $486万
 $23,047/呎
-(25年-07月)</t>
+(25年-07月-23日)</t>
         </is>
       </c>
       <c r="I17" s="22" t="inlineStr">
@@ -12057,7 +12057,7 @@
           <t>H | 388呎 (2房)
 $987万
 $25,443/呎
-(21年-07月)</t>
+(21年-07月-07日)</t>
         </is>
       </c>
     </row>
@@ -12072,7 +12072,7 @@
           <t>A | 282呎 (1房)
 $731万
 $25,918/呎
-(21年-07月)</t>
+(21年-07月-12日)</t>
         </is>
       </c>
       <c r="C18" s="22" t="inlineStr">
@@ -12080,7 +12080,7 @@
           <t>B | 277呎 (1房)
 $732万
 $26,408/呎
-(21年-07月)</t>
+(21年-07月-15日)</t>
         </is>
       </c>
       <c r="D18" s="22" t="inlineStr">
@@ -12088,7 +12088,7 @@
           <t>C | 264呎 (1房)
 $698万
 $26,458/呎
-(21年-07月)</t>
+(21年-07月-04日)</t>
         </is>
       </c>
       <c r="E18" s="22" t="inlineStr">
@@ -12096,7 +12096,7 @@
           <t>D | 210呎 (开放式)
 $603万
 $28,700/呎
-(24年-03月)</t>
+(24年-03月-24日)</t>
         </is>
       </c>
       <c r="F18" s="22" t="inlineStr">
@@ -12104,7 +12104,7 @@
           <t>E | 209呎 (开放式)
 $414万
 $19,794/呎
-(24年-10月)</t>
+(24年-10月-23日)</t>
         </is>
       </c>
       <c r="G18" s="22" t="inlineStr">
@@ -12112,7 +12112,7 @@
           <t>F | 285呎 (1房)
 $724万
 $25,418/呎
-(21年-07月)</t>
+(21年-07月-05日)</t>
         </is>
       </c>
       <c r="H18" s="22" t="inlineStr">
@@ -12120,7 +12120,7 @@
           <t>G | 211呎 (开放式)
 $582万
 $27,607/呎
-(21年-07月)</t>
+(21年-07月-08日)</t>
         </is>
       </c>
       <c r="I18" s="22" t="inlineStr">
@@ -12128,7 +12128,7 @@
           <t>H | 388呎 (2房)
 $934万
 $24,075/呎
-(21年-07月)</t>
+(21年-07月-08日)</t>
         </is>
       </c>
     </row>
@@ -12143,7 +12143,7 @@
           <t>A | 282呎 (1房)
 $530万
 $18,777/呎
-(24年-08月)</t>
+(24年-08月-29日)</t>
         </is>
       </c>
       <c r="C19" s="22" t="inlineStr">
@@ -12151,7 +12151,7 @@
           <t>B | 277呎 (1房)
 $696万
 $25,108/呎
-(21年-07月)</t>
+(21年-07月-08日)</t>
         </is>
       </c>
       <c r="D19" s="22" t="inlineStr">
@@ -12159,7 +12159,7 @@
           <t>C | 264呎 (1房)
 $659万
 $24,958/呎
-(21年-07月)</t>
+(21年-07月-04日)</t>
         </is>
       </c>
       <c r="E19" s="22" t="inlineStr">
@@ -12167,7 +12167,7 @@
           <t>D | 210呎 (开放式)
 $578万
 $27,543/呎
-(21年-06月)</t>
+(21年-06月-18日)</t>
         </is>
       </c>
       <c r="F19" s="22" t="inlineStr">
@@ -12175,7 +12175,7 @@
           <t>E | 209呎 (开放式)
 $553万
 $26,450/呎
-(21年-07月)</t>
+(21年-07月-05日)</t>
         </is>
       </c>
       <c r="G19" s="22" t="inlineStr">
@@ -12183,7 +12183,7 @@
           <t>F | 285呎 (1房)
 $756万
 $26,523/呎
-(21年-07月)</t>
+(21年-07月-08日)</t>
         </is>
       </c>
       <c r="H19" s="22" t="inlineStr">
@@ -12191,7 +12191,7 @@
           <t>G | 211呎 (开放式)
 $592万
 $28,047/呎
-(21年-07月)</t>
+(21年-07月-07日)</t>
         </is>
       </c>
       <c r="I19" s="22" t="inlineStr">
@@ -12199,7 +12199,7 @@
           <t>H | 388呎 (2房)
 $970万
 $24,995/呎
-(22年-01月)</t>
+(22年-01月-18日)</t>
         </is>
       </c>
     </row>
@@ -12214,7 +12214,7 @@
           <t>A | 282呎 (1房)
 $527万
 $18,699/呎
-(24年-08月)</t>
+(24年-08月-20日)</t>
         </is>
       </c>
       <c r="C20" s="22" t="inlineStr">
@@ -12222,7 +12222,7 @@
           <t>B | 277呎 (1房)
 $719万
 $25,942/呎
-(21年-07月)</t>
+(21年-07月-12日)</t>
         </is>
       </c>
       <c r="D20" s="22" t="inlineStr">
@@ -12230,7 +12230,7 @@
           <t>C | 264呎 (1房)
 $659万
 $24,951/呎
-(22年-03月)</t>
+(22年-03月-02日)</t>
         </is>
       </c>
       <c r="E20" s="22" t="inlineStr">
@@ -12238,7 +12238,7 @@
           <t>D | 210呎 (开放式)
 $570万
 $27,162/呎
-(21年-07月)</t>
+(21年-07月-20日)</t>
         </is>
       </c>
       <c r="F20" s="22" t="inlineStr">
@@ -12246,7 +12246,7 @@
           <t>E | 209呎 (开放式)
 $590万
 $28,225/呎
-(24年-03月)</t>
+(24年-03月-24日)</t>
         </is>
       </c>
       <c r="G20" s="22" t="inlineStr">
@@ -12254,7 +12254,7 @@
           <t>F | 285呎 (1房)
 $712万
 $24,965/呎
-(21年-06月)</t>
+(21年-06月-18日)</t>
         </is>
       </c>
       <c r="H20" s="22" t="inlineStr">
@@ -12262,7 +12262,7 @@
           <t>G | 211呎 (开放式)
 $557万
 $26,408/呎
-(21年-10月)</t>
+(21年-10月-07日)</t>
         </is>
       </c>
       <c r="I20" s="22" t="inlineStr">
@@ -12270,7 +12270,7 @@
           <t>H | 388呎 (2房)
 $961万
 $24,771/呎
-(21年-07月)</t>
+(21年-07月-12日)</t>
         </is>
       </c>
     </row>
@@ -12285,7 +12285,7 @@
           <t>A | 283呎 (1房)
 $689万
 $24,360/呎
-(22年-01月)</t>
+(22年-01月-26日)</t>
         </is>
       </c>
       <c r="C21" s="22" t="inlineStr">
@@ -12293,7 +12293,7 @@
           <t>B | 278呎 (1房)
 $683万
 $24,576/呎
-(21年-07月)</t>
+(21年-07月-07日)</t>
         </is>
       </c>
       <c r="D21" s="22" t="inlineStr">
@@ -12301,7 +12301,7 @@
           <t>C | 264呎 (1房)
 $610万
 $23,098/呎
-(21年-06月)</t>
+(21年-06月-18日)</t>
         </is>
       </c>
       <c r="E21" s="22" t="inlineStr">
@@ -12309,7 +12309,7 @@
           <t>D | 210呎 (开放式)
 $581万
 $27,667/呎
-(24年-03月)</t>
+(24年-03月-24日)</t>
         </is>
       </c>
       <c r="F21" s="22" t="inlineStr">
@@ -12317,7 +12317,7 @@
           <t>E | 209呎 (开放式)
 $543万
 $25,976/呎
-(21年-07月)</t>
+(21年-07月-15日)</t>
         </is>
       </c>
       <c r="G21" s="22" t="inlineStr">
@@ -12325,7 +12325,7 @@
           <t>F | 285呎 (1房)
 $742万
 $26,049/呎
-(21年-07月)</t>
+(21年-07月-08日)</t>
         </is>
       </c>
       <c r="H21" s="22" t="inlineStr">
@@ -12333,7 +12333,7 @@
           <t>G | 211呎 (开放式)
 $555万
 $26,303/呎
-(21年-07月)</t>
+(21年-07月-12日)</t>
         </is>
       </c>
       <c r="I21" s="22" t="inlineStr">
@@ -12341,7 +12341,7 @@
           <t>H | 388呎 (2房)
 $957万
 $24,673/呎
-(21年-07月)</t>
+(21年-07月-13日)</t>
         </is>
       </c>
     </row>
@@ -12356,7 +12356,7 @@
           <t>A | 283呎 (1房)
 $689万
 $24,336/呎
-(21年-07月)</t>
+(21年-07月-11日)</t>
         </is>
       </c>
       <c r="C22" s="22" t="inlineStr">
@@ -12364,7 +12364,7 @@
           <t>B | 277呎 (1房)
 $701万
 $25,292/呎
-(21年-07月)</t>
+(21年-07月-12日)</t>
         </is>
       </c>
       <c r="D22" s="22" t="inlineStr">
@@ -12372,7 +12372,7 @@
           <t>C | 264呎 (1房)
 $635万
 $24,045/呎
-(21年-07月)</t>
+(21年-07月-08日)</t>
         </is>
       </c>
       <c r="E22" s="22" t="inlineStr">
@@ -12380,7 +12380,7 @@
           <t>D | 210呎 (开放式)
 $531万
 $25,281/呎
-(21年-07月)</t>
+(21年-07月-08日)</t>
         </is>
       </c>
       <c r="F22" s="22" t="inlineStr">
@@ -12388,7 +12388,7 @@
           <t>E | 209呎 (开放式)
 $570万
 $27,249/呎
-(24年-03月)</t>
+(24年-03月-19日)</t>
         </is>
       </c>
       <c r="G22" s="22" t="inlineStr">
@@ -12396,7 +12396,7 @@
           <t>F | 285呎 (1房)
 $708万
 $24,842/呎
-(21年-07月)</t>
+(21年-07月-15日)</t>
         </is>
       </c>
       <c r="H22" s="22" t="inlineStr">
@@ -12404,7 +12404,7 @@
           <t>G | 211呎 (开放式)
 $581万
 $27,526/呎
-(21年-07月)</t>
+(21年-07月-04日)</t>
         </is>
       </c>
       <c r="I22" s="22" t="inlineStr">
@@ -12412,7 +12412,7 @@
           <t>H | 388呎 (2房)
 $924万
 $23,807/呎
-(22年-08月)</t>
+(22年-08月-08日)</t>
         </is>
       </c>
     </row>
@@ -12427,7 +12427,7 @@
           <t>A | 283呎 (1房)
 $716万
 $25,318/呎
-(21年-07月)</t>
+(21年-07月-11日)</t>
         </is>
       </c>
       <c r="C23" s="22" t="inlineStr">
@@ -12435,7 +12435,7 @@
           <t>B | 277呎 (1房)
 $672万
 $24,260/呎
-(22年-02月)</t>
+(22年-02月-13日)</t>
         </is>
       </c>
       <c r="D23" s="22" t="inlineStr">
@@ -12443,7 +12443,7 @@
           <t>C | 264呎 (1房)
 $660万
 $25,011/呎
-(21年-07月)</t>
+(21年-07月-07日)</t>
         </is>
       </c>
       <c r="E23" s="22" t="inlineStr">
@@ -12451,7 +12451,7 @@
           <t>D | 209呎 (开放式)
 $531万
 $25,407/呎
-(22年-04月)</t>
+(22年-04月-13日)</t>
         </is>
       </c>
       <c r="F23" s="22" t="inlineStr">
@@ -12459,7 +12459,7 @@
           <t>E | 209呎 (开放式)
 $553万
 $26,459/呎
-(21年-06月)</t>
+(21年-06月-18日)</t>
         </is>
       </c>
       <c r="G23" s="22" t="inlineStr">
@@ -12467,7 +12467,7 @@
           <t>F | 286呎 (1房)
 $718万
 $25,108/呎
-(21年-07月)</t>
+(21年-07月-05日)</t>
         </is>
       </c>
       <c r="H23" s="24" t="inlineStr">
@@ -12483,7 +12483,7 @@
           <t>H | 388呎 (2房)
 $950万
 $24,477/呎
-(21年-07月)</t>
+(21年-07月-13日)</t>
         </is>
       </c>
     </row>
@@ -12498,7 +12498,7 @@
           <t>A | 282呎 (1房)
 $714万
 $25,305/呎
-(21年-07月)</t>
+(21年-07月-11日)</t>
         </is>
       </c>
       <c r="C24" s="22" t="inlineStr">
@@ -12506,7 +12506,7 @@
           <t>B | 277呎 (1房)
 $693万
 $25,007/呎
-(21年-07月)</t>
+(21年-07月-13日)</t>
         </is>
       </c>
       <c r="D24" s="22" t="inlineStr">
@@ -12514,7 +12514,7 @@
           <t>C | 264呎 (1房)
 $658万
 $24,905/呎
-(21年-07月)</t>
+(21年-07月-07日)</t>
         </is>
       </c>
       <c r="E24" s="22" t="inlineStr">
@@ -12522,7 +12522,7 @@
           <t>D | 209呎 (开放式)
 $522万
 $24,995/呎
-(21年-07月)</t>
+(21年-07月-07日)</t>
         </is>
       </c>
       <c r="F24" s="22" t="inlineStr">
@@ -12530,7 +12530,7 @@
           <t>E | 209呎 (开放式)
 $563万
 $26,938/呎
-(24年-03月)</t>
+(24年-03月-21日)</t>
         </is>
       </c>
       <c r="G24" s="22" t="inlineStr">
@@ -12538,7 +12538,7 @@
           <t>F | 286呎 (1房)
 $703万
 $24,566/呎
-(21年-07月)</t>
+(21年-07月-05日)</t>
         </is>
       </c>
       <c r="H24" s="22" t="inlineStr">
@@ -12546,7 +12546,7 @@
           <t>G | 211呎 (开放式)
 $548万
 $25,986/呎
-(21年-07月)</t>
+(21年-07月-05日)</t>
         </is>
       </c>
       <c r="I24" s="22" t="inlineStr">
@@ -12554,7 +12554,7 @@
           <t>H | 388呎 (2房)
 $946万
 $24,376/呎
-(21年-07月)</t>
+(21年-07月-08日)</t>
         </is>
       </c>
     </row>
@@ -12569,7 +12569,7 @@
           <t>A | 282呎 (1房)
 $711万
 $25,199/呎
-(21年-07月)</t>
+(21年-07月-12日)</t>
         </is>
       </c>
       <c r="C25" s="22" t="inlineStr">
@@ -12577,7 +12577,7 @@
           <t>B | 277呎 (1房)
 $658万
 $23,765/呎
-(21年-07月)</t>
+(21年-07月-08日)</t>
         </is>
       </c>
       <c r="D25" s="22" t="inlineStr">
@@ -12585,7 +12585,7 @@
           <t>C | 264呎 (1房)
 $655万
 $24,799/呎
-(21年-07月)</t>
+(21年-07月-15日)</t>
         </is>
       </c>
       <c r="E25" s="22" t="inlineStr">
@@ -12593,7 +12593,7 @@
           <t>D | 209呎 (开放式)
 $524万
 $25,053/呎
-(21年-07月)</t>
+(21年-07月-08日)</t>
         </is>
       </c>
       <c r="F25" s="22" t="inlineStr">
@@ -12601,7 +12601,7 @@
           <t>E | 209呎 (开放式)
 $523万
 $25,033/呎
-(21年-06月)</t>
+(21年-06月-18日)</t>
         </is>
       </c>
       <c r="G25" s="22" t="inlineStr">
@@ -12609,7 +12609,7 @@
           <t>F | 286呎 (1房)
 $733万
 $25,633/呎
-(21年-07月)</t>
+(21年-07月-13日)</t>
         </is>
       </c>
       <c r="H25" s="22" t="inlineStr">
@@ -12617,7 +12617,7 @@
           <t>G | 211呎 (开放式)
 $572万
 $27,109/呎
-(21年-07月)</t>
+(21年-07月-11日)</t>
         </is>
       </c>
       <c r="I25" s="22" t="inlineStr">
@@ -12625,7 +12625,7 @@
           <t>H | 388呎 (2房)
 $899万
 $23,175/呎
-(21年-07月)</t>
+(21年-07月-12日)</t>
         </is>
       </c>
     </row>
